--- a/outputs/validation_frame_supp_disp.xlsx
+++ b/outputs/validation_frame_supp_disp.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005143544436268916</v>
+        <v>-0.005143544436265349</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.005143544436260579</v>
+        <v>-0.005143544436263927</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.009992639968869796</v>
+        <v>-0.009992639968869803</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001430013372528314</v>
+        <v>0.0001430013372534397</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0001430013372543053</v>
+        <v>-0.0001430013372536887</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1816844298607e-15</v>
+        <v>-2.459828480256998e-16</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01235981198413286</v>
+        <v>0.01235981198413277</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.001181950344896417</v>
+        <v>-0.001181950344900396</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.005133919027350523</v>
+        <v>-0.005133919027353872</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00124715441483153</v>
+        <v>0.001247154414832138</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0008581353759194087</v>
+        <v>-0.0008581353759201137</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.181563932377305e-15</v>
+        <v>-2.45867092239527e-16</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005268221251806789</v>
+        <v>0.005268221251810945</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001172324935986361</v>
+        <v>-0.001172324935990341</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001172324935996923</v>
+        <v>-0.001172324935992853</v>
       </c>
       <c r="G8" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001962288453499951</v>
+        <v>0.00196228845349925</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001962288453498106</v>
+        <v>-0.001962288453498811</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.18166403535008e-15</v>
+        <v>-2.459196944341733e-16</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01013890013059342</v>
+        <v>0.01013890013059341</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.005133919027358861</v>
+        <v>-0.005133919027355294</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.001181950344906979</v>
+        <v>-0.001181950344902908</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000858135375921254</v>
+        <v>0.0008581353759205526</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.001247154414833003</v>
+        <v>-0.001247154414832387</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.18139457602318e-15</v>
+        <v>-2.45883799833235e-16</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005268221251817284</v>
+        <v>0.005268221251812895</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01030576096286427</v>
+        <v>-0.01030576096285544</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01030576096284246</v>
+        <v>-0.01030576096285178</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.009991111550163006</v>
+        <v>-0.009991111550163018</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00124109203779992</v>
+        <v>0.001241092037800776</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.001241092037801604</v>
+        <v>-0.001241092037801047</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.055103843794704e-15</v>
+        <v>-6.320011768432583e-16</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01767030639391251</v>
+        <v>0.0176703063939128</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.009634190035129281</v>
+        <v>-0.009634190035139751</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01030901918798729</v>
+        <v>-0.0103090191879966</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.034816844246121e-06</v>
+        <v>-6.034816844245296e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009979940318735161</v>
+        <v>0.0009979940318743741</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.00143916279433412</v>
+        <v>-0.001439162794334948</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.05495934852082e-15</v>
+        <v>-6.325385275155652e-16</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01411005069694254</v>
+        <v>0.0141100506969565</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.009637448260274106</v>
+        <v>-0.009637448260284578</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.009637448260301185</v>
+        <v>-0.00963744826029103</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0100031811838515</v>
+        <v>0.01000318118385151</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001196064788409722</v>
+        <v>0.00119606478840903</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.001196064788407717</v>
+        <v>-0.001196064788408546</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.054790642029308e-15</v>
+        <v>-6.310766232131836e-16</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0169063435353835</v>
+        <v>0.01690634353538368</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01030901918800909</v>
+        <v>-0.01030901918800026</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.00963419003515636</v>
+        <v>-0.009634190035146204</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.034816844260094e-06</v>
+        <v>-6.034816844253537e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001439162794336123</v>
+        <v>0.001439162794335432</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0009979940318752018</v>
+        <v>-0.0009979940318746456</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.054355086044638e-15</v>
+        <v>-6.323352839555595e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01411005069697696</v>
+        <v>0.01411005069696358</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01737007367944867</v>
+        <v>-0.01737007367943667</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.01737007367941414</v>
+        <v>-0.0173700736794309</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.009990938226026575</v>
+        <v>-0.009990938226026593</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001204350062740928</v>
+        <v>0.001204350062741668</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.001204350062742015</v>
+        <v>-0.001204350062741899</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.803761237550783e-15</v>
+        <v>-1.012366336751686e-15</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02651900763403545</v>
+        <v>0.02651900763403857</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01735361784199784</v>
+        <v>-0.01735361784201489</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01736938160992134</v>
+        <v>-0.01736938160993809</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.146923437967343e-06</v>
+        <v>-6.146923437965993e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00125937918302127</v>
+        <v>0.001259379183022008</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.00123006073370777</v>
+        <v>-0.001230060733708419</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.803892303683812e-15</v>
+        <v>-1.012110102286476e-15</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02455287167526127</v>
+        <v>0.02455287167528518</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01735292577250504</v>
+        <v>-0.01735292577252209</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01735292577254737</v>
+        <v>-0.01735292577253253</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001285089853989626</v>
+        <v>0.001285089853989261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.001285089853988111</v>
+        <v>-0.001285089853988761</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.803309957801465e-15</v>
+        <v>-1.012571952175807e-15</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02650118332523954</v>
+        <v>0.02650118332524098</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01736938160995587</v>
+        <v>-0.01736938160994386</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.01735361784204018</v>
+        <v>-0.01735361784202533</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.146923437985668e-06</v>
+        <v>-6.146923437976757e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001230060733709285</v>
+        <v>0.001230060733708922</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.001259379183022356</v>
+        <v>-0.001259379183022239</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.804447417211208e-15</v>
+        <v>-1.013382782898572e-15</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02455287167531562</v>
+        <v>0.02455287167529663</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.02482398266159128</v>
+        <v>-0.02482398266158013</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0248239826615519</v>
+        <v>-0.02482398266157276</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.009990935978426553</v>
+        <v>-0.009990935978426577</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001257818715765292</v>
+        <v>0.001257818715765601</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.001257818715765604</v>
+        <v>-0.001257818715765732</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.674836422945595e-15</v>
+        <v>-1.358705779577601e-15</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03650039769768313</v>
+        <v>0.03650039769768974</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.02485967309713104</v>
+        <v>-0.02485967309715188</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.02482409162315708</v>
+        <v>-0.02482409162317794</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.139754862708566e-06</v>
+        <v>-6.139754862707143e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001237953768590255</v>
+        <v>0.001237953768590565</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.001259528070805193</v>
+        <v>-0.001259528070805485</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.67899907152334e-15</v>
+        <v>-1.357769995309901e-15</v>
       </c>
       <c r="K19" t="n">
-        <v>0.03513173649433953</v>
+        <v>0.03513173649436901</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001239663123630873</v>
+        <v>0.001239663123630794</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.001239663123630155</v>
+        <v>-0.001239663123630448</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.676397154560981e-15</v>
+        <v>-1.357742617260905e-15</v>
       </c>
       <c r="K20" t="n">
-        <v>0.03655245338032303</v>
+        <v>0.03655245338032614</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.02482409162319647</v>
+        <v>-0.0248240916231853</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0248596730971825</v>
+        <v>-0.02485967309716625</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.139754862729007e-06</v>
+        <v>-6.139754862719022e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>0.001259528070805909</v>
+        <v>0.00125952807080583</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.001237953768590568</v>
+        <v>-0.001237953768590698</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.677821559011737e-15</v>
+        <v>-1.357962856859783e-15</v>
       </c>
       <c r="K21" t="n">
-        <v>0.03513173649440377</v>
+        <v>0.03513173649438439</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03655245338032303</v>
+        <v>0.03655245338032614</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
     </row>
     <row r="4">
@@ -1289,16 +1289,16 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
     </row>
     <row r="5">
@@ -1311,16 +1311,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01735292577250504</v>
+        <v>-0.01735292577252209</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01735292577254737</v>
+        <v>-0.01735292577253253</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.30374669528852</v>
+        <v>-1.303746695288943</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.303746695289486</v>
+        <v>-1.30374669528911</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.162884918572217</v>
+        <v>-1.162884918571081</v>
       </c>
       <c r="E2" t="n">
-        <v>3.805419096301363</v>
+        <v>3.805419096299786</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.805419096297374</v>
+        <v>-3.805419096299101</v>
       </c>
       <c r="G2" t="n">
-        <v>3.363255684988146e-15</v>
+        <v>7.001050289962223e-16</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.3434724264392463</v>
+        <v>-0.3434724264387863</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3434724264377969</v>
+        <v>0.343472426438173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7734063072796302</v>
+        <v>0.7734063072796055</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.953311546288723</v>
+        <v>-1.953311546290301</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3953971011373766</v>
+        <v>-0.3953971011354749</v>
       </c>
       <c r="G3" t="n">
-        <v>3.362912730612329e-15</v>
+        <v>6.997755702201921e-16</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.303746695288037</v>
+        <v>1.303746695288497</v>
       </c>
       <c r="C4" t="n">
-        <v>1.303746695289277</v>
+        <v>1.303746695288792</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3839276959879498</v>
+        <v>-0.3839276959881772</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.363333541457796</v>
+        <v>-5.363333541455821</v>
       </c>
       <c r="F4" t="n">
-        <v>5.36333354145271</v>
+        <v>5.363333541454612</v>
       </c>
       <c r="G4" t="n">
-        <v>3.363197639073303e-15</v>
+        <v>6.999252841588009e-16</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3434724264387636</v>
+        <v>0.3434724264383396</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3434724264380065</v>
+        <v>-0.3434724264384916</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7734063072808883</v>
+        <v>0.7734063072803354</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3953971011322915</v>
+        <v>0.3953971011342658</v>
       </c>
       <c r="F5" t="n">
-        <v>1.953311546292713</v>
+        <v>1.953311546290985</v>
       </c>
       <c r="G5" t="n">
-        <v>3.362430716373665e-15</v>
+        <v>6.99823122602284e-16</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>7.360031130203976e-06</v>
+        <v>7.360031130197037e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.226671855033996e-06</v>
+        <v>1.226671855032839e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.162884918572228</v>
+        <v>1.162884918571132</v>
       </c>
       <c r="I2" t="n">
-        <v>245.3343710067992</v>
+        <v>245.3343710065679</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.162884918572217</v>
+        <v>-1.162884918571081</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.303746695289486</v>
+        <v>-1.30374669528911</v>
       </c>
       <c r="L2" t="n">
-        <v>1.30374669528852</v>
+        <v>1.303746695288943</v>
       </c>
       <c r="M2" t="n">
-        <v>3.363255684988146e-15</v>
+        <v>7.001050289962223e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.805419096297374</v>
+        <v>-3.805419096299101</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.805419096301363</v>
+        <v>-3.805419096299785</v>
       </c>
       <c r="P2" t="n">
-        <v>1.162884918572217</v>
+        <v>1.162884918571081</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.303746695289486</v>
+        <v>1.30374669528911</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.30374669528852</v>
+        <v>-1.303746695288943</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.363255684988146e-15</v>
+        <v>-7.001050289962223e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>-4.017061075433746</v>
+        <v>-4.01706107543456</v>
       </c>
       <c r="U2" t="n">
-        <v>-4.017061075435553</v>
+        <v>-4.017061075434876</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>-8.158294380586814e-07</v>
+        <v>-8.158294380586554e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.77340630727963</v>
+        <v>-0.7734063072796052</v>
       </c>
       <c r="I3" t="n">
-        <v>-163.1658876117363</v>
+        <v>-163.1658876117311</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7734063072796302</v>
+        <v>0.7734063072796055</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3434724264377969</v>
+        <v>0.3434724264381729</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3434724264392463</v>
+        <v>0.3434724264387864</v>
       </c>
       <c r="M3" t="n">
-        <v>3.362912730612329e-15</v>
+        <v>6.997755702201921e-16</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3953971011373766</v>
+        <v>-0.395397101135475</v>
       </c>
       <c r="O3" t="n">
-        <v>1.953311546288723</v>
+        <v>1.953311546290301</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7734063072796302</v>
+        <v>-0.7734063072796055</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3434724264377969</v>
+        <v>-0.3434724264381729</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.3434724264392463</v>
+        <v>-0.3434724264387864</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.362912730612329e-15</v>
+        <v>-6.997755702201921e-16</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.665437457498101</v>
+        <v>-1.665437457497243</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1075230123380582</v>
+        <v>0.1075230123387366</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>2.429922126505335e-06</v>
+        <v>2.42992212650707e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.049870210842225e-07</v>
+        <v>4.049870210845116e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3839276959878429</v>
+        <v>0.383927695988117</v>
       </c>
       <c r="I4" t="n">
-        <v>80.9974042168445</v>
+        <v>80.99740421690232</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3839276959879498</v>
+        <v>-0.3839276959881772</v>
       </c>
       <c r="K4" t="n">
-        <v>1.303746695289277</v>
+        <v>1.303746695288792</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.303746695288037</v>
+        <v>-1.303746695288497</v>
       </c>
       <c r="M4" t="n">
-        <v>3.363197639073303e-15</v>
+        <v>6.999252841588009e-16</v>
       </c>
       <c r="N4" t="n">
-        <v>5.363333541452711</v>
+        <v>5.363333541454613</v>
       </c>
       <c r="O4" t="n">
-        <v>5.363333541457796</v>
+        <v>5.363333541455821</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3839276959879498</v>
+        <v>0.3839276959881772</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.303746695289277</v>
+        <v>-1.303746695288792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.303746695288037</v>
+        <v>1.303746695288497</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.363197639073303e-15</v>
+        <v>-6.999252841588009e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>2.459146630275513</v>
+        <v>2.459146630276371</v>
       </c>
       <c r="U4" t="n">
-        <v>2.459146630277869</v>
+        <v>2.459146630276932</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.158294380600086e-07</v>
+        <v>-8.158294380594254e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7734063072808882</v>
+        <v>-0.7734063072803353</v>
       </c>
       <c r="I5" t="n">
-        <v>-163.1658876120017</v>
+        <v>-163.1658876118851</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7734063072808883</v>
+        <v>0.7734063072803354</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3434724264380065</v>
+        <v>-0.3434724264384916</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3434724264387636</v>
+        <v>-0.3434724264383395</v>
       </c>
       <c r="M5" t="n">
-        <v>3.362430716373665e-15</v>
+        <v>6.99823122602284e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>1.953311546292713</v>
+        <v>1.953311546290985</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3953971011322915</v>
+        <v>-0.3953971011342658</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7734063072808883</v>
+        <v>-0.7734063072803354</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3434724264380065</v>
+        <v>0.3434724264384916</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3434724264387636</v>
+        <v>0.3434724264383395</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.362430716373665e-15</v>
+        <v>-6.99823122602284e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1075230123398683</v>
+        <v>0.1075230123390525</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.665437457495747</v>
+        <v>-1.665437457496684</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.528418706790366e-06</v>
+        <v>1.528418706785162e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.547364511317277e-07</v>
+        <v>2.547364511308603e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2414901556728778</v>
+        <v>0.2414901556720556</v>
       </c>
       <c r="I6" t="n">
-        <v>50.94729022634553</v>
+        <v>50.94729022617206</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2414901556728637</v>
+        <v>-0.2414901556719542</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2491176456844955</v>
+        <v>0.2491176456848834</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2491176456854803</v>
+        <v>-0.2491176456850503</v>
       </c>
       <c r="M6" t="n">
-        <v>5.332039870427548e-15</v>
+        <v>1.098667551249974e-15</v>
       </c>
       <c r="N6" t="n">
-        <v>1.559940055461441</v>
+        <v>1.559940055460197</v>
       </c>
       <c r="O6" t="n">
-        <v>1.559940055458332</v>
+        <v>1.559940055459679</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2414901556728637</v>
+        <v>0.2414901556719542</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2491176456844955</v>
+        <v>-0.2491176456848834</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2491176456854803</v>
+        <v>0.2491176456850503</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.332039870427548e-15</v>
+        <v>-1.098667551249974e-15</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.06523418134856085</v>
+        <v>-0.06523418134989445</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06523418135135906</v>
+        <v>-0.06523418135037939</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.139840215894032e-06</v>
+        <v>-1.139840215893363e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.89973369315672e-07</v>
+        <v>-1.899733693155606e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.180094754111257</v>
+        <v>-0.1800947541111514</v>
       </c>
       <c r="I7" t="n">
-        <v>-37.99467386313439</v>
+        <v>-37.99467386311211</v>
       </c>
       <c r="J7" t="n">
-        <v>0.180094754111257</v>
+        <v>0.1800947541111514</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3848851442713319</v>
+        <v>-0.3848851442709451</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3848851442698287</v>
+        <v>-0.3848851442702956</v>
       </c>
       <c r="M7" t="n">
-        <v>5.33197156902385e-15</v>
+        <v>1.100526392708724e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.584615722436372</v>
+        <v>1.584615722437863</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.339034116202926</v>
+        <v>-1.339034116201581</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.180094754111257</v>
+        <v>-0.1800947541111514</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3848851442713319</v>
+        <v>0.3848851442709451</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3848851442698287</v>
+        <v>0.3848851442702956</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.33197156902385e-15</v>
+        <v>-1.100526392708724e-15</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7246951431825996</v>
+        <v>0.7246951431839088</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9702767494250653</v>
+        <v>-0.9702767494240909</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>7.512617249960662e-07</v>
+        <v>7.512617249995357e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>1.252102874993444e-07</v>
+        <v>1.252102874999226e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1186993525493785</v>
+        <v>0.1186993525499266</v>
       </c>
       <c r="I8" t="n">
-        <v>25.04205749986887</v>
+        <v>25.04205749998452</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1186993525493563</v>
+        <v>-0.1186993525500384</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2491176456847733</v>
+        <v>-0.2491176456852433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2491176456859986</v>
+        <v>0.2491176456855322</v>
       </c>
       <c r="M8" t="n">
-        <v>5.331206495933188e-15</v>
+        <v>1.096215874217183e-15</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.314358449224885</v>
+        <v>-1.314358449223394</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.314358449221089</v>
+        <v>-1.314358449222493</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1186993525493563</v>
+        <v>0.1186993525500384</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2491176456847733</v>
+        <v>0.2491176456852433</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.2491176456859986</v>
+        <v>-0.2491176456855322</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.331206495933188e-15</v>
+        <v>-1.096215874217183e-15</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1803474248911088</v>
+        <v>-0.1803474248898009</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1803474248875491</v>
+        <v>-0.1803474248889678</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.139840215900042e-06</v>
+        <v>-1.139840215896985e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.899733693166737e-07</v>
+        <v>-1.899733693161641e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1800947541122067</v>
+        <v>-0.1800947541117236</v>
       </c>
       <c r="I9" t="n">
-        <v>-37.99467386333474</v>
+        <v>-37.99467386323282</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1800947541122068</v>
+        <v>0.1800947541117236</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3848851442710549</v>
+        <v>0.384885144270585</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3848851442703483</v>
+        <v>0.3848851442707786</v>
       </c>
       <c r="M9" t="n">
-        <v>5.330733759291841e-15</v>
+        <v>1.099900377886616e-15</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.339034116199818</v>
+        <v>-1.339034116201065</v>
       </c>
       <c r="O9" t="n">
-        <v>1.584615722440167</v>
+        <v>1.584615722438765</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1800947541122068</v>
+        <v>-0.1800947541117236</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3848851442710549</v>
+        <v>-0.384885144270585</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.3848851442703483</v>
+        <v>-0.3848851442707786</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.330733759291841e-15</v>
+        <v>-1.099900377886616e-15</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9702767494222719</v>
+        <v>-0.9702767494236078</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7246951431861609</v>
+        <v>0.7246951431847437</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.733241364303834e-07</v>
+        <v>1.733241364251792e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>2.888735607173056e-08</v>
+        <v>2.88873560708632e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02738521355600057</v>
+        <v>0.02738521355517831</v>
       </c>
       <c r="I10" t="n">
-        <v>5.777471214346112</v>
+        <v>5.777471214172639</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.02738521355581724</v>
+        <v>-0.02738521355513512</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.06709668431254689</v>
+        <v>-0.06709668431189275</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06709668431145799</v>
+        <v>0.06709668431174309</v>
       </c>
       <c r="M10" t="n">
-        <v>4.976947966844225e-15</v>
+        <v>1.082577762816293e-15</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2284791144784704</v>
+        <v>-0.2284791144789988</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2284791144812948</v>
+        <v>-0.2284791144794198</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02738521355581724</v>
+        <v>0.02738521355513512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.06709668431254689</v>
+        <v>0.06709668431189275</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.06709668431145799</v>
+        <v>-0.06709668431174309</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.976947966844225e-15</v>
+        <v>-1.082577762816293e-15</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1741009913902776</v>
+        <v>-0.1741009913914588</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1741009913939884</v>
+        <v>-0.1741009913919385</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.121065937212221e-07</v>
+        <v>-1.12106593720697e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.868443228687035e-08</v>
+        <v>-1.868443228678283e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0177128418079531</v>
+        <v>-0.01771284180787012</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.736886457374071</v>
+        <v>-3.736886457356566</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01771284180795318</v>
+        <v>0.01771284180787014</v>
       </c>
       <c r="K11" t="n">
-        <v>0.07109988505492337</v>
+        <v>0.0710998850555784</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07109988505675269</v>
+        <v>0.07109988505622278</v>
       </c>
       <c r="M11" t="n">
-        <v>4.977732257002361e-15</v>
+        <v>1.080319097424901e-15</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3680351800337569</v>
+        <v>-0.368035180032301</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4067246670141085</v>
+        <v>0.4067246670159843</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.01771284180795318</v>
+        <v>-0.01771284180787014</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.07109988505492337</v>
+        <v>-0.0710998850555784</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.07109988505675269</v>
+        <v>-0.07109988505622278</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.977732257002361e-15</v>
+        <v>-1.080319097424901e-15</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.05856413030676011</v>
+        <v>-0.05856413030504015</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01987464331543176</v>
+        <v>0.01987464331748789</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>5.088905101306718e-08</v>
+        <v>5.08890510148019e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>8.481508502177862e-09</v>
+        <v>8.481508502466983e-09</v>
       </c>
       <c r="H12" t="n">
-        <v>0.008040470060064614</v>
+        <v>0.0080404700603387</v>
       </c>
       <c r="I12" t="n">
-        <v>1.696301700435572</v>
+        <v>1.696301700493397</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.008040470059995641</v>
+        <v>-0.008040470060223015</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06709668431187632</v>
+        <v>0.06709668431150018</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.06709668431071891</v>
+        <v>-0.06709668431124749</v>
       </c>
       <c r="M12" t="n">
-        <v>4.976554975659214e-15</v>
+        <v>1.085794397816698e-15</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2671686014616472</v>
+        <v>0.2671686014630996</v>
       </c>
       <c r="O12" t="n">
-        <v>0.267168601464757</v>
+        <v>0.2671686014638706</v>
       </c>
       <c r="P12" t="n">
-        <v>0.008040470059995641</v>
+        <v>0.008040470060223015</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.06709668431187632</v>
+        <v>-0.06709668431150018</v>
       </c>
       <c r="R12" t="n">
-        <v>0.06709668431071891</v>
+        <v>0.06709668431124749</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.976554975659214e-15</v>
+        <v>-1.085794397816698e-15</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1354115044026627</v>
+        <v>0.1354115044043827</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1354115044064992</v>
+        <v>0.1354115044051305</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.121065937255742e-07</v>
+        <v>-1.121065937232203e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.86844322875957e-08</v>
+        <v>-1.868443228720338e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.01771284180864072</v>
+        <v>-0.0177128418082688</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.736886457519139</v>
+        <v>-3.736886457440675</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01771284180864063</v>
+        <v>0.01771284180826882</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.07109988505559262</v>
+        <v>-0.07109988505597098</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.07109988505601206</v>
+        <v>-0.07109988505572762</v>
       </c>
       <c r="M13" t="n">
-        <v>4.981032019474084e-15</v>
+        <v>1.084519804683958e-15</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4067246670169316</v>
+        <v>0.4067246670164</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3680351800306383</v>
+        <v>-0.36803518003153</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.01771284180864063</v>
+        <v>-0.01771284180826882</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07109988505559262</v>
+        <v>0.07109988505597098</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07109988505601206</v>
+        <v>0.07109988505572762</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.981032019474084e-15</v>
+        <v>-1.084519804683958e-15</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01987464331914257</v>
+        <v>0.01987464331796218</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.05856413030291918</v>
+        <v>-0.05856413030429408</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>2.247600022764473e-09</v>
+        <v>2.247600015825579e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>3.746000037940789e-10</v>
+        <v>3.746000026375966e-10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003551208035967868</v>
+        <v>0.0003551208025004415</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07492000075881577</v>
+        <v>0.07492000052751931</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0003551208037606557</v>
+        <v>-0.0003551208026237873</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01662598616604516</v>
+        <v>0.01662598616628053</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.01662598616620636</v>
+        <v>-0.01662598616640665</v>
       </c>
       <c r="M14" t="n">
-        <v>2.479213989200619e-15</v>
+        <v>9.857353372737588e-16</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08944476173607985</v>
+        <v>0.089444761736857</v>
       </c>
       <c r="O14" t="n">
-        <v>0.089444761736166</v>
+        <v>0.08944476173654792</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0003551208037606557</v>
+        <v>0.0003551208026237873</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01662598616604516</v>
+        <v>-0.01662598616628053</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01662598616620636</v>
+        <v>0.01662598616640665</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.479213989200619e-15</v>
+        <v>-9.857353372737588e-16</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01031115526116544</v>
+        <v>0.01031115526158288</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01031115526010673</v>
+        <v>0.01031115526112991</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>7.168575258776767e-09</v>
+        <v>7.168575258849612e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>1.194762543129461e-09</v>
+        <v>1.194762543141602e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001132634890886729</v>
+        <v>0.001132634890898239</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2389525086258922</v>
+        <v>0.2389525086283204</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.001132634890886774</v>
+        <v>-0.00113263489089821</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.009197914261043216</v>
+        <v>-0.009197914260807849</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.00919791425992933</v>
+        <v>-0.009197914260166584</v>
       </c>
       <c r="M15" t="n">
-        <v>2.490688493081734e-15</v>
+        <v>9.838012339897462e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>0.04939957223187874</v>
+        <v>0.04939957223232838</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.04344854946208265</v>
+        <v>-0.04344854946169363</v>
       </c>
       <c r="P15" t="n">
-        <v>0.001132634890886774</v>
+        <v>0.00113263489089821</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.009197914261043216</v>
+        <v>0.009197914260807849</v>
       </c>
       <c r="R15" t="n">
-        <v>0.00919791425992933</v>
+        <v>0.009197914260166584</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.490688493081734e-15</v>
+        <v>-9.838012339897462e-16</v>
       </c>
       <c r="T15" t="n">
-        <v>0.005787913327693683</v>
+        <v>0.005787913328671124</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.01173893610418197</v>
+        <v>-0.01173893610315879</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.658475053123443e-08</v>
+        <v>-1.658475053296915e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.764125088539071e-09</v>
+        <v>-2.764125088828192e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.002620390583935039</v>
+        <v>-0.002620390584209126</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5528250177078142</v>
+        <v>-0.5528250177656383</v>
       </c>
       <c r="J16" t="n">
-        <v>0.002620390583842891</v>
+        <v>0.002620390584070265</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01662598616656297</v>
+        <v>-0.01662598616658162</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01662598616716049</v>
+        <v>0.01662598616692357</v>
       </c>
       <c r="M16" t="n">
-        <v>2.484940483084779e-15</v>
+        <v>9.82408816011432e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.08349373896636569</v>
+        <v>-0.08349373896592382</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.08349373896516532</v>
+        <v>-0.08349373896501433</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.002620390583842891</v>
+        <v>-0.002620390584070265</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01662598616656297</v>
+        <v>0.01662598616658162</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.01662598616716049</v>
+        <v>-0.01662598616692357</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.484940483084779e-15</v>
+        <v>-9.82408816011432e-16</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.01626217803659191</v>
+        <v>-0.01626217803562113</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.01626217803421071</v>
+        <v>-0.01626217803448071</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>7.168575256660879e-09</v>
+        <v>7.168575257735764e-09</v>
       </c>
       <c r="G17" t="n">
-        <v>1.194762542776813e-09</v>
+        <v>1.194762542955961e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001132634890552419</v>
+        <v>0.001132634890722251</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2389525085553626</v>
+        <v>0.2389525085911921</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.001132634890552375</v>
+        <v>-0.001132634890722239</v>
       </c>
       <c r="K17" t="n">
-        <v>0.009197914260527185</v>
+        <v>0.009197914260510309</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009197914260882456</v>
+        <v>0.009197914260683504</v>
       </c>
       <c r="M17" t="n">
-        <v>2.485757172816889e-15</v>
+        <v>9.807279028126785e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.04344854946217147</v>
+        <v>-0.04344854946139165</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04939957223308333</v>
+        <v>0.04939957223324143</v>
       </c>
       <c r="P17" t="n">
-        <v>0.001132634890552375</v>
+        <v>0.001132634890722239</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.009197914260527185</v>
+        <v>-0.009197914260510309</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.009197914260882456</v>
+        <v>-0.009197914260683504</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.485757172816889e-15</v>
+        <v>-9.807279028126785e-16</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.01173893610312504</v>
+        <v>-0.01173893610271293</v>
       </c>
       <c r="U17" t="n">
-        <v>0.005787913330079775</v>
+        <v>0.005787913329816874</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>9.625408910056074e-06</v>
+        <v>9.625408910055207e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>1.203176113757009e-06</v>
+        <v>1.203176113756901e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>1.140610955841645</v>
+        <v>1.140610955841542</v>
       </c>
       <c r="I18" t="n">
-        <v>240.6352227514018</v>
+        <v>240.6352227513802</v>
       </c>
       <c r="J18" t="n">
         <v>-1.140610955841566</v>
       </c>
       <c r="K18" t="n">
-        <v>0.412253385132467</v>
+        <v>0.4122533851324607</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4606973814500098</v>
+        <v>-0.4606973814495045</v>
       </c>
       <c r="M18" t="n">
-        <v>0.001526536120996663</v>
+        <v>0.001526536120999484</v>
       </c>
       <c r="N18" t="n">
-        <v>2.455594483856218</v>
+        <v>2.455594483854196</v>
       </c>
       <c r="O18" t="n">
-        <v>1.649013540529868</v>
+        <v>1.649013540529843</v>
       </c>
       <c r="P18" t="n">
         <v>1.140610955841566</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.412253385132467</v>
+        <v>-0.4122533851324607</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4606973814500098</v>
+        <v>0.4606973814495045</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.001526536120996663</v>
+        <v>-0.001526536120999484</v>
       </c>
       <c r="T18" t="n">
-        <v>1.229984567743863</v>
+        <v>1.229984567741841</v>
       </c>
       <c r="U18" t="n">
-        <v>1.649013540529868</v>
+        <v>1.649013540529843</v>
       </c>
     </row>
     <row r="19">
@@ -2745,52 +2745,52 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>9.62540891005564e-06</v>
+        <v>9.625408910055207e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>1.203176113756955e-06</v>
+        <v>1.203176113756901e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.140610955841593</v>
+        <v>1.140610955841542</v>
       </c>
       <c r="I19" t="n">
-        <v>240.635222751391</v>
+        <v>240.6352227513802</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.140610955841595</v>
+        <v>-1.140610955841538</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4122533851324677</v>
+        <v>-0.4122533851324608</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1326141717183632</v>
+        <v>0.1326141717189501</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.001526536121003745</v>
+        <v>-0.00152653612100095</v>
       </c>
       <c r="N19" t="n">
-        <v>0.08234827118272525</v>
+        <v>0.08234827118037735</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.649013540529871</v>
+        <v>-1.649013540529843</v>
       </c>
       <c r="P19" t="n">
-        <v>1.140610955841595</v>
+        <v>1.140610955841538</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4122533851324677</v>
+        <v>0.4122533851324608</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.1326141717183632</v>
+        <v>-0.1326141717189501</v>
       </c>
       <c r="S19" t="n">
-        <v>0.001526536121003745</v>
+        <v>0.00152653612100095</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.143261644929629</v>
+        <v>-1.143261644931977</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.649013540529871</v>
+        <v>-1.649013540529843</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>9.625408910055424e-06</v>
+        <v>9.625408910055207e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>1.203176113756928e-06</v>
+        <v>1.203176113756901e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>1.140610955841568</v>
+        <v>1.140610955841542</v>
       </c>
       <c r="I20" t="n">
-        <v>240.6352227513856</v>
+        <v>240.6352227513802</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.140610955841566</v>
+        <v>-1.140610955841538</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4122533851324672</v>
+        <v>0.4122533851324607</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1326141717198984</v>
+        <v>-0.1326141717193148</v>
       </c>
       <c r="M20" t="n">
-        <v>0.001526536120996663</v>
+        <v>0.001526536120999483</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14326164493577</v>
+        <v>1.143261644933435</v>
       </c>
       <c r="O20" t="n">
-        <v>1.649013540529868</v>
+        <v>1.649013540529843</v>
       </c>
       <c r="P20" t="n">
-        <v>1.140610955841566</v>
+        <v>1.140610955841538</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4122533851324672</v>
+        <v>-0.4122533851324607</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1326141717198984</v>
+        <v>0.1326141717193148</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.001526536120996663</v>
+        <v>-0.001526536120999483</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.08234827117658372</v>
+        <v>-0.08234827117891852</v>
       </c>
       <c r="U20" t="n">
-        <v>1.649013540529868</v>
+        <v>1.649013540529843</v>
       </c>
     </row>
     <row r="21">
@@ -2891,40 +2891,40 @@
         <v>240.6352227513802</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.140610955841453</v>
+        <v>-1.140610955841566</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4122533851324676</v>
+        <v>0.4122533851324608</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4606973814487824</v>
+        <v>-0.4606973814492966</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.001526536121003748</v>
+        <v>-0.001526536121000953</v>
       </c>
       <c r="N21" t="n">
-        <v>1.229984567738952</v>
+        <v>1.22998456774101</v>
       </c>
       <c r="O21" t="n">
-        <v>1.649013540529871</v>
+        <v>1.649013540529843</v>
       </c>
       <c r="P21" t="n">
-        <v>1.140610955841453</v>
+        <v>1.140610955841566</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.4122533851324676</v>
+        <v>-0.4122533851324608</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4606973814487824</v>
+        <v>0.4606973814492966</v>
       </c>
       <c r="S21" t="n">
-        <v>0.001526536121003748</v>
+        <v>0.001526536121000953</v>
       </c>
       <c r="T21" t="n">
-        <v>2.455594483851307</v>
+        <v>2.455594483853365</v>
       </c>
       <c r="U21" t="n">
-        <v>1.649013540529871</v>
+        <v>1.649013540529843</v>
       </c>
     </row>
     <row r="22">
@@ -2961,37 +2961,37 @@
         <v>0.386099679661811</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0698853496648788</v>
+        <v>0.06988534966488702</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1070524710594157</v>
+        <v>-0.1070524710587034</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0004228048841367167</v>
+        <v>0.0004228048841396726</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2932904909485095</v>
+        <v>0.2932904909456604</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2795413986595152</v>
+        <v>0.2795413986595481</v>
       </c>
       <c r="P22" t="n">
         <v>-0.386099679661811</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.0698853496648788</v>
+        <v>-0.06988534966488702</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1070524710594157</v>
+        <v>0.1070524710587034</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0004228048841367167</v>
+        <v>-0.0004228048841396726</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5631292775268171</v>
+        <v>0.5631292775239671</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2795413986595152</v>
+        <v>0.2795413986595481</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.258225144825433e-06</v>
+        <v>-3.258225144827168e-06</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.072781431031791e-07</v>
+        <v>-4.07278143103396e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3860996796618138</v>
+        <v>-0.3860996796620194</v>
       </c>
       <c r="I23" t="n">
-        <v>-81.45562862063582</v>
+        <v>-81.45562862067918</v>
       </c>
       <c r="J23" t="n">
-        <v>0.386099679661811</v>
+        <v>0.3860996796620384</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.06988534966487836</v>
+        <v>-0.06988534966488746</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0553294412438885</v>
+        <v>0.05532944124457745</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0004228048841445928</v>
+        <v>-0.0004228048841412851</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3562371582647073</v>
+        <v>-0.3562371582674621</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2795413986595134</v>
+        <v>-0.2795413986595507</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.386099679661811</v>
+        <v>-0.3860996796620384</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.06988534966487836</v>
+        <v>0.06988534966488746</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.0553294412438885</v>
+        <v>-0.05532944124457745</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0004228048841445928</v>
+        <v>0.0004228048841412851</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.08639837168639986</v>
+        <v>-0.08639837168915587</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2795413986595126</v>
+        <v>-0.279541398659549</v>
       </c>
     </row>
     <row r="24">
@@ -3092,40 +3092,40 @@
         <v>-81.45562862063582</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3860996796620384</v>
+        <v>0.386099679661811</v>
       </c>
       <c r="K24" t="n">
-        <v>0.06988534966487858</v>
+        <v>0.06988534966488746</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.05532944124555528</v>
+        <v>-0.05532944124497974</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0004228048841367154</v>
+        <v>0.0004228048841396713</v>
       </c>
       <c r="N24" t="n">
-        <v>0.08639837169306763</v>
+        <v>0.0863983716907657</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2795413986595152</v>
+        <v>0.2795413986595507</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3860996796620384</v>
+        <v>-0.386099679661811</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.06988534966487858</v>
+        <v>-0.06988534966488746</v>
       </c>
       <c r="R24" t="n">
-        <v>0.05532944124555528</v>
+        <v>0.05532944124497974</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0004228048841367154</v>
+        <v>-0.0004228048841396713</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3562371582713735</v>
+        <v>0.3562371582690712</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2795413986595152</v>
+        <v>0.2795413986595481</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.258225144823698e-06</v>
+        <v>-3.258225144825433e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.072781431029623e-07</v>
+        <v>-4.072781431031791e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3860996796616082</v>
+        <v>-0.3860996796618138</v>
       </c>
       <c r="I25" t="n">
-        <v>-81.45562862059245</v>
+        <v>-81.45562862063582</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3860996796615837</v>
+        <v>0.386099679661811</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06988534966487814</v>
+        <v>0.06988534966488746</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1070524710580115</v>
+        <v>-0.1070524710584768</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0004228048841445884</v>
+        <v>-0.0004228048841412838</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5631292775211996</v>
+        <v>0.563129277523061</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2795413986595117</v>
+        <v>0.2795413986595507</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3860996796615837</v>
+        <v>-0.386099679661811</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.06988534966487814</v>
+        <v>-0.06988534966488746</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1070524710580115</v>
+        <v>0.1070524710584768</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0004228048841445884</v>
+        <v>0.0004228048841412838</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2932904909428933</v>
+        <v>0.2932904909447553</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2795413986595126</v>
+        <v>0.2795413986595499</v>
       </c>
     </row>
     <row r="26">
@@ -3229,37 +3229,37 @@
         <v>-0.08201023489709769</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001712435580727645</v>
+        <v>0.001712435580860427</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.01351504637711198</v>
+        <v>-0.01351504637649903</v>
       </c>
       <c r="M26" t="n">
-        <v>5.488239379228569e-05</v>
+        <v>5.488239379391937e-05</v>
       </c>
       <c r="N26" t="n">
-        <v>0.08460134726403878</v>
+        <v>0.08460134726158497</v>
       </c>
       <c r="O26" t="n">
-        <v>0.006849742322909691</v>
+        <v>0.00684974232344171</v>
       </c>
       <c r="P26" t="n">
         <v>0.08201023489709769</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.001712435580727645</v>
+        <v>-0.001712435580860427</v>
       </c>
       <c r="R26" t="n">
-        <v>0.01351504637711198</v>
+        <v>0.01351504637649903</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.488239379228569e-05</v>
+        <v>-5.488239379391937e-05</v>
       </c>
       <c r="T26" t="n">
-        <v>0.02351902375285864</v>
+        <v>0.02351902375040749</v>
       </c>
       <c r="U26" t="n">
-        <v>0.006849742322910579</v>
+        <v>0.00684974232344171</v>
       </c>
     </row>
     <row r="27">
@@ -3293,40 +3293,40 @@
         <v>17.30173732001142</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.08201023489709769</v>
+        <v>-0.08201023489664294</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.001712435580726535</v>
+        <v>-0.001712435580859539</v>
       </c>
       <c r="L27" t="n">
-        <v>0.005330430321729085</v>
+        <v>0.005330430322269208</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.488239379783637e-05</v>
+        <v>-5.488239379548322e-05</v>
       </c>
       <c r="N27" t="n">
-        <v>0.009219440468673401</v>
+        <v>0.009219440466513129</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.006849742322907026</v>
+        <v>-0.006849742323438157</v>
       </c>
       <c r="P27" t="n">
-        <v>0.08201023489709769</v>
+        <v>0.08201023489664294</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.001712435580726535</v>
+        <v>0.001712435580859539</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.005330430321729085</v>
+        <v>-0.005330430322269208</v>
       </c>
       <c r="S27" t="n">
-        <v>5.488239379783637e-05</v>
+        <v>5.488239379548322e-05</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.05186288304250564</v>
+        <v>-0.05186288304466569</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.006849742322907026</v>
+        <v>-0.006849742323439045</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>6.920694928073956e-07</v>
+        <v>6.920694928039262e-07</v>
       </c>
       <c r="G28" t="n">
-        <v>8.650868660092445e-08</v>
+        <v>8.650868660049077e-08</v>
       </c>
       <c r="H28" t="n">
-        <v>0.08201023489767638</v>
+        <v>0.08201023489726525</v>
       </c>
       <c r="I28" t="n">
-        <v>17.30173732018489</v>
+        <v>17.30173732009815</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.08201023489755244</v>
+        <v>-0.08201023489709769</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001712435580726979</v>
+        <v>0.001712435580859539</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.005330430322988522</v>
+        <v>-0.005330430322685431</v>
       </c>
       <c r="M28" t="n">
-        <v>5.488239379228569e-05</v>
+        <v>5.488239379392197e-05</v>
       </c>
       <c r="N28" t="n">
-        <v>0.05186288304754272</v>
+        <v>0.05186288304632969</v>
       </c>
       <c r="O28" t="n">
-        <v>0.006849742322908803</v>
+        <v>0.006849742323439045</v>
       </c>
       <c r="P28" t="n">
-        <v>0.08201023489755244</v>
+        <v>0.08201023489709769</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.001712435580726979</v>
+        <v>-0.001712435580859539</v>
       </c>
       <c r="R28" t="n">
-        <v>0.005330430322988522</v>
+        <v>0.005330430322685431</v>
       </c>
       <c r="S28" t="n">
-        <v>-5.488239379228569e-05</v>
+        <v>-5.488239379392197e-05</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.009219440463635209</v>
+        <v>-0.009219440464847573</v>
       </c>
       <c r="U28" t="n">
-        <v>0.006849742322907026</v>
+        <v>0.006849742323438157</v>
       </c>
     </row>
     <row r="29">
@@ -3430,37 +3430,37 @@
         <v>-0.08201023489755244</v>
       </c>
       <c r="K29" t="n">
-        <v>0.001712435580726979</v>
+        <v>0.001712435580860205</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01351504637620604</v>
+        <v>-0.01351504637630585</v>
       </c>
       <c r="M29" t="n">
-        <v>-5.488239379784028e-05</v>
+        <v>-5.488239379548366e-05</v>
       </c>
       <c r="N29" t="n">
-        <v>0.02351902374923509</v>
+        <v>0.02351902374963499</v>
       </c>
       <c r="O29" t="n">
-        <v>0.006849742322907915</v>
+        <v>0.006849742323440822</v>
       </c>
       <c r="P29" t="n">
         <v>0.08201023489755244</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.001712435580726979</v>
+        <v>-0.001712435580860205</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01351504637620604</v>
+        <v>0.01351504637630585</v>
       </c>
       <c r="S29" t="n">
-        <v>5.488239379784028e-05</v>
+        <v>5.488239379548366e-05</v>
       </c>
       <c r="T29" t="n">
-        <v>0.08460134726041391</v>
+        <v>0.08460134726081225</v>
       </c>
       <c r="U29" t="n">
-        <v>0.006849742322907026</v>
+        <v>0.006849742323439045</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.089616051830333e-07</v>
+        <v>-1.089616051795639e-07</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.362020064787917e-08</v>
+        <v>-1.362020064744549e-08</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.01291195021418945</v>
+        <v>-0.01291195021377832</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.724040129575833</v>
+        <v>-2.724040129489097</v>
       </c>
       <c r="J30" t="n">
-        <v>0.01291195021440217</v>
+        <v>0.01291195021349267</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.003714035953082284</v>
+        <v>-0.003714035952816719</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.0001775604016159837</v>
+        <v>-0.0001775604013612986</v>
       </c>
       <c r="M30" t="n">
-        <v>3.648815565276964e-06</v>
+        <v>3.648815565626944e-06</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.01031480407568131</v>
+        <v>-0.01031480407669871</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.01485614381232736</v>
+        <v>-0.0148561438112651</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.01291195021440217</v>
+        <v>-0.01291195021349267</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.003714035953082284</v>
+        <v>0.003714035952816719</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001775604016159837</v>
+        <v>0.0001775604013612986</v>
       </c>
       <c r="S30" t="n">
-        <v>-3.648815565276964e-06</v>
+        <v>-3.648815565626944e-06</v>
       </c>
       <c r="T30" t="n">
-        <v>0.01173528728861006</v>
+        <v>0.01173528728759021</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.01485614381233091</v>
+        <v>-0.0148561438112651</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.089616051795639e-07</v>
+        <v>-1.089616051760944e-07</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.362020064744549e-08</v>
+        <v>-1.36202006470118e-08</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.01291195021377832</v>
+        <v>-0.01291195021336719</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.724040129489097</v>
+        <v>-2.724040129402361</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01291195021394742</v>
+        <v>0.01291195021349267</v>
       </c>
       <c r="K31" t="n">
-        <v>0.003714035953081396</v>
+        <v>0.003714035952815387</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.001310195292502869</v>
+        <v>-0.001310195292259397</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.648815567473124e-06</v>
+        <v>-3.648815566643059e-06</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.005784264512133763</v>
+        <v>-0.005784264513107429</v>
       </c>
       <c r="O31" t="n">
-        <v>0.01485614381232558</v>
+        <v>0.01485614381126332</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.01291195021394742</v>
+        <v>-0.01291195021349267</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.003714035953081396</v>
+        <v>-0.003714035952815387</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001310195292502869</v>
+        <v>0.001310195292259397</v>
       </c>
       <c r="S31" t="n">
-        <v>3.648815567473124e-06</v>
+        <v>3.648815566643059e-06</v>
       </c>
       <c r="T31" t="n">
-        <v>0.01626582685215805</v>
+        <v>0.01626582685118416</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01485614381232736</v>
+        <v>0.01485614381126332</v>
       </c>
     </row>
     <row r="32">
@@ -3616,52 +3616,52 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.089616051760944e-07</v>
+        <v>-1.089616051691555e-07</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.36202006470118e-08</v>
+        <v>-1.362020064614444e-08</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.01291195021336719</v>
+        <v>-0.01291195021254493</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.724040129402361</v>
+        <v>-2.724040129228888</v>
       </c>
       <c r="J32" t="n">
-        <v>0.01291195021349267</v>
+        <v>0.01291195021258318</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.003714035953082284</v>
+        <v>-0.003714035952815831</v>
       </c>
       <c r="L32" t="n">
-        <v>0.00131019529190779</v>
+        <v>0.001310195291973071</v>
       </c>
       <c r="M32" t="n">
-        <v>3.648815565272193e-06</v>
+        <v>3.648815565620439e-06</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.01626582684977684</v>
+        <v>-0.01626582685003797</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.01485614381232736</v>
+        <v>-0.01485614381126332</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.01291195021349267</v>
+        <v>-0.01291195021258318</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.003714035953082284</v>
+        <v>0.003714035952815831</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.00131019529190779</v>
+        <v>-0.001310195291973071</v>
       </c>
       <c r="S32" t="n">
-        <v>-3.648815565272193e-06</v>
+        <v>-3.648815565620439e-06</v>
       </c>
       <c r="T32" t="n">
-        <v>0.005784264514513193</v>
+        <v>0.005784264514252069</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.01485614381232914</v>
+        <v>-0.01485614381126155</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.089616051830333e-07</v>
+        <v>-1.089616051795639e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.362020064787917e-08</v>
+        <v>-1.362020064744549e-08</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.01291195021418945</v>
+        <v>-0.01291195021377832</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.724040129575833</v>
+        <v>-2.724040129489097</v>
       </c>
       <c r="J33" t="n">
         <v>0.01291195021394742</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.003714035953083616</v>
+        <v>-0.003714035952815831</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.0001775604013539711</v>
+        <v>-0.0001775604012499432</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.648815567470955e-06</v>
+        <v>-3.648815566643926e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>0.01173528728756135</v>
+        <v>0.01173528728714435</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.01485614381233269</v>
+        <v>-0.0148561438112651</v>
       </c>
       <c r="P33" t="n">
         <v>-0.01291195021394742</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003714035953083616</v>
+        <v>0.003714035952815831</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0001775604013539711</v>
+        <v>0.0001775604012499432</v>
       </c>
       <c r="S33" t="n">
-        <v>3.648815567470955e-06</v>
+        <v>3.648815566643926e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.01031480407672802</v>
+        <v>-0.01031480407714414</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.01485614381233624</v>
+        <v>-0.01485614381126332</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>7.360031130203976e-06</v>
+        <v>7.360031130197037e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.226671855033996e-06</v>
+        <v>1.226671855032839e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.162884918572228</v>
+        <v>1.162884918571132</v>
       </c>
       <c r="I2" t="n">
-        <v>245.3343710067992</v>
+        <v>245.3343710065679</v>
       </c>
       <c r="J2" t="n">
         <v>-0.01</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005143544436268916</v>
+        <v>-0.005143544436265349</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.005143544436260579</v>
+        <v>-0.005143544436263927</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.009992639968869796</v>
+        <v>-0.009992639968869803</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001430013372528314</v>
+        <v>0.0001430013372534397</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0001430013372543053</v>
+        <v>-0.0001430013372536887</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1816844298607e-15</v>
+        <v>-2.459828480256998e-16</v>
       </c>
       <c r="V2" t="n">
         <v>-0.01</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.009992639968869796</v>
+        <v>-0.009992639968869803</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.005143544436260579</v>
+        <v>-0.005143544436263927</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.005143544436268916</v>
+        <v>0.005143544436265349</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.1816844298607e-15</v>
+        <v>-2.459828480256998e-16</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.0001430013372543053</v>
+        <v>-0.0001430013372536887</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.0001430013372528314</v>
+        <v>-0.0001430013372534397</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.162884918572217</v>
+        <v>-1.162884918571081</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.303746695289486</v>
+        <v>-1.30374669528911</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.30374669528852</v>
+        <v>1.303746695288943</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.363255684988146e-15</v>
+        <v>7.001050289962223e-16</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3.805419096297374</v>
+        <v>-3.805419096299101</v>
       </c>
       <c r="AM2" t="n">
-        <v>-3.805419096301363</v>
+        <v>-3.805419096299785</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.162884918572217</v>
+        <v>1.162884918571081</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.303746695289486</v>
+        <v>1.30374669528911</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1.30374669528852</v>
+        <v>-1.303746695288943</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-3.363255684988146e-15</v>
+        <v>-7.001050289962223e-16</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.017061075433746</v>
+        <v>-4.01706107543456</v>
       </c>
       <c r="AS2" t="n">
-        <v>-4.017061075435553</v>
+        <v>-4.017061075434876</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>-8.158294380586814e-07</v>
+        <v>-8.158294380586554e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.77340630727963</v>
+        <v>-0.7734063072796052</v>
       </c>
       <c r="I3" t="n">
-        <v>-163.1658876117363</v>
+        <v>-163.1658876117311</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.001181950344896417</v>
+        <v>-0.001181950344900396</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.005133919027350523</v>
+        <v>-0.005133919027353872</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00124715441483153</v>
+        <v>0.001247154414832138</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0008581353759194087</v>
+        <v>-0.0008581353759201137</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.181563932377305e-15</v>
+        <v>-2.45867092239527e-16</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.005133919027350523</v>
+        <v>-0.005133919027353872</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.001181950344896417</v>
+        <v>0.001181950344900396</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.181563932377305e-15</v>
+        <v>-2.45867092239527e-16</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0008581353759194087</v>
+        <v>-0.0008581353759201137</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.00124715441483153</v>
+        <v>-0.001247154414832138</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.7734063072796302</v>
+        <v>0.7734063072796055</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3434724264377969</v>
+        <v>0.3434724264381729</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.3434724264392463</v>
+        <v>0.3434724264387864</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.362912730612329e-15</v>
+        <v>6.997755702201921e-16</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.3953971011373766</v>
+        <v>-0.395397101135475</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.953311546288723</v>
+        <v>1.953311546290301</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.7734063072796302</v>
+        <v>-0.7734063072796055</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.3434724264377969</v>
+        <v>-0.3434724264381729</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.3434724264392463</v>
+        <v>-0.3434724264387864</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-3.362912730612329e-15</v>
+        <v>-6.997755702201921e-16</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.665437457498101</v>
+        <v>-1.665437457497243</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1075230123380582</v>
+        <v>0.1075230123387366</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>2.429922126505335e-06</v>
+        <v>2.42992212650707e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.049870210842225e-07</v>
+        <v>4.049870210845116e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3839276959878429</v>
+        <v>0.383927695988117</v>
       </c>
       <c r="I4" t="n">
-        <v>80.9974042168445</v>
+        <v>80.99740421690232</v>
       </c>
       <c r="J4" t="n">
         <v>0.01</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.001172324935986361</v>
+        <v>-0.001172324935990341</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.001172324935996923</v>
+        <v>-0.001172324935992853</v>
       </c>
       <c r="R4" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001962288453499951</v>
+        <v>0.00196228845349925</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.001962288453498106</v>
+        <v>-0.001962288453498811</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.18166403535008e-15</v>
+        <v>-2.459196944341733e-16</v>
       </c>
       <c r="V4" t="n">
         <v>0.01</v>
@@ -4338,55 +4338,55 @@
         <v>0.01000242992212651</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.001172324935996923</v>
+        <v>-0.001172324935992853</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.001172324935986361</v>
+        <v>0.001172324935990341</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1.18166403535008e-15</v>
+        <v>-2.459196944341733e-16</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.001962288453498106</v>
+        <v>-0.001962288453498811</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.001962288453499951</v>
+        <v>-0.00196228845349925</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.3839276959879498</v>
+        <v>-0.3839276959881772</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.303746695289277</v>
+        <v>1.303746695288792</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1.303746695288037</v>
+        <v>-1.303746695288497</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.363197639073303e-15</v>
+        <v>6.999252841588009e-16</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.363333541452711</v>
+        <v>5.363333541454613</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.363333541457796</v>
+        <v>5.363333541455821</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.3839276959879498</v>
+        <v>0.3839276959881772</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1.303746695289277</v>
+        <v>-1.303746695288792</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.303746695288037</v>
+        <v>1.303746695288497</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-3.363197639073303e-15</v>
+        <v>-6.999252841588009e-16</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.459146630275513</v>
+        <v>2.459146630276371</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.459146630277869</v>
+        <v>2.459146630276932</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.158294380600086e-07</v>
+        <v>-8.158294380594254e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7734063072808882</v>
+        <v>-0.7734063072803353</v>
       </c>
       <c r="I5" t="n">
-        <v>-163.1658876120017</v>
+        <v>-163.1658876118851</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005133919027358861</v>
+        <v>-0.005133919027355294</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.001181950344906979</v>
+        <v>-0.001181950344902908</v>
       </c>
       <c r="R5" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000858135375921254</v>
+        <v>0.0008581353759205526</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.001247154414833003</v>
+        <v>-0.001247154414832387</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.18139457602318e-15</v>
+        <v>-2.45883799833235e-16</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.001181950344906979</v>
+        <v>-0.001181950344902908</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.005133919027358861</v>
+        <v>0.005133919027355294</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.18139457602318e-15</v>
+        <v>-2.45883799833235e-16</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.001247154414833003</v>
+        <v>-0.001247154414832387</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.000858135375921254</v>
+        <v>-0.0008581353759205526</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.7734063072808883</v>
+        <v>0.7734063072803354</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.3434724264380065</v>
+        <v>-0.3434724264384916</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.3434724264387636</v>
+        <v>-0.3434724264383395</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.362430716373665e-15</v>
+        <v>6.99823122602284e-16</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.953311546292713</v>
+        <v>1.953311546290985</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.3953971011322915</v>
+        <v>-0.3953971011342658</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.7734063072808883</v>
+        <v>-0.7734063072803354</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.3434724264380065</v>
+        <v>0.3434724264384916</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.3434724264387636</v>
+        <v>0.3434724264383395</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-3.362430716373665e-15</v>
+        <v>-6.99823122602284e-16</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1075230123398683</v>
+        <v>0.1075230123390525</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1.665437457495747</v>
+        <v>-1.665437457496684</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.528418706790366e-06</v>
+        <v>1.528418706785162e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.547364511317277e-07</v>
+        <v>2.547364511308603e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2414901556728778</v>
+        <v>0.2414901556720556</v>
       </c>
       <c r="I6" t="n">
-        <v>50.94729022634553</v>
+        <v>50.94729022617206</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.005143544436268916</v>
+        <v>-0.005143544436265349</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.005143544436260579</v>
+        <v>-0.005143544436263927</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.009992639968869796</v>
+        <v>-0.009992639968869803</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001430013372528314</v>
+        <v>0.0001430013372534397</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0001430013372543053</v>
+        <v>-0.0001430013372536887</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1816844298607e-15</v>
+        <v>-2.459828480256998e-16</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01030576096286427</v>
+        <v>-0.01030576096285544</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.01030576096284246</v>
+        <v>-0.01030576096285178</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.009991111550163006</v>
+        <v>-0.009991111550163018</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00124109203779992</v>
+        <v>0.001241092037800776</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001241092037801604</v>
+        <v>-0.001241092037801047</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.055103843794704e-15</v>
+        <v>-6.320011768432583e-16</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.009992639968869796</v>
+        <v>-0.009992639968869803</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.005143544436260579</v>
+        <v>-0.005143544436263927</v>
       </c>
       <c r="X6" t="n">
-        <v>0.005143544436268916</v>
+        <v>0.005143544436265349</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.1816844298607e-15</v>
+        <v>-2.459828480256998e-16</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0001430013372543053</v>
+        <v>-0.0001430013372536887</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0001430013372528314</v>
+        <v>-0.0001430013372534397</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.009991111550163006</v>
+        <v>-0.009991111550163018</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.01030576096284246</v>
+        <v>-0.01030576096285178</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.01030576096286427</v>
+        <v>0.01030576096285544</v>
       </c>
       <c r="AE6" t="n">
-        <v>-3.055103843794704e-15</v>
+        <v>-6.320011768432583e-16</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001241092037801604</v>
+        <v>-0.001241092037801047</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.00124109203779992</v>
+        <v>-0.001241092037800776</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.2414901556728637</v>
+        <v>-0.2414901556719542</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.2491176456844955</v>
+        <v>0.2491176456848834</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.2491176456854803</v>
+        <v>-0.2491176456850503</v>
       </c>
       <c r="AK6" t="n">
-        <v>5.332039870427548e-15</v>
+        <v>1.098667551249974e-15</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.559940055461441</v>
+        <v>1.559940055460197</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.559940055458332</v>
+        <v>1.559940055459679</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.2414901556728637</v>
+        <v>0.2414901556719542</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.2491176456844955</v>
+        <v>-0.2491176456848834</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.2491176456854803</v>
+        <v>0.2491176456850503</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-5.332039870427548e-15</v>
+        <v>-1.098667551249974e-15</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.06523418134856085</v>
+        <v>-0.06523418134989445</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.06523418135135906</v>
+        <v>-0.06523418135037939</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.139840215894032e-06</v>
+        <v>-1.139840215893363e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.89973369315672e-07</v>
+        <v>-1.899733693155606e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.180094754111257</v>
+        <v>-0.1800947541111514</v>
       </c>
       <c r="I7" t="n">
-        <v>-37.99467386313439</v>
+        <v>-37.99467386311211</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.001181950344896417</v>
+        <v>-0.001181950344900396</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.005133919027350523</v>
+        <v>-0.005133919027353872</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00124715441483153</v>
+        <v>0.001247154414832138</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0008581353759194087</v>
+        <v>-0.0008581353759201137</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.181563932377305e-15</v>
+        <v>-2.45867092239527e-16</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.009634190035129281</v>
+        <v>-0.009634190035139751</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.01030901918798729</v>
+        <v>-0.0103090191879966</v>
       </c>
       <c r="R7" t="n">
-        <v>-6.034816844246121e-06</v>
+        <v>-6.034816844245296e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0009979940318735161</v>
+        <v>0.0009979940318743741</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.00143916279433412</v>
+        <v>-0.001439162794334948</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.05495934852082e-15</v>
+        <v>-6.325385275155652e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.005133919027350523</v>
+        <v>-0.005133919027353872</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001181950344896417</v>
+        <v>0.001181950344900396</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.181563932377305e-15</v>
+        <v>-2.45867092239527e-16</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0008581353759194087</v>
+        <v>-0.0008581353759201137</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.00124715441483153</v>
+        <v>-0.001247154414832138</v>
       </c>
       <c r="AB7" t="n">
-        <v>-6.034816844246121e-06</v>
+        <v>-6.034816844245296e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.01030901918798729</v>
+        <v>-0.0103090191879966</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.009634190035129281</v>
+        <v>0.009634190035139751</v>
       </c>
       <c r="AE7" t="n">
-        <v>-3.05495934852082e-15</v>
+        <v>-6.325385275155652e-16</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.00143916279433412</v>
+        <v>-0.001439162794334948</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0009979940318735161</v>
+        <v>-0.0009979940318743741</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.180094754111257</v>
+        <v>0.1800947541111514</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.3848851442713319</v>
+        <v>-0.3848851442709451</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.3848851442698287</v>
+        <v>-0.3848851442702956</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.33197156902385e-15</v>
+        <v>1.100526392708724e-15</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.584615722436372</v>
+        <v>1.584615722437863</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1.339034116202926</v>
+        <v>-1.339034116201581</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.180094754111257</v>
+        <v>-0.1800947541111514</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.3848851442713319</v>
+        <v>0.3848851442709451</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.3848851442698287</v>
+        <v>0.3848851442702956</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-5.33197156902385e-15</v>
+        <v>-1.100526392708724e-15</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.7246951431825996</v>
+        <v>0.7246951431839088</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.9702767494250653</v>
+        <v>-0.9702767494240909</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>7.512617249960662e-07</v>
+        <v>7.512617249995357e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>1.252102874993444e-07</v>
+        <v>1.252102874999226e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1186993525493785</v>
+        <v>0.1186993525499266</v>
       </c>
       <c r="I8" t="n">
-        <v>25.04205749986887</v>
+        <v>25.04205749998452</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.001172324935986361</v>
+        <v>-0.001172324935990341</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.001172324935996923</v>
+        <v>-0.001172324935992853</v>
       </c>
       <c r="L8" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001962288453499951</v>
+        <v>0.00196228845349925</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.001962288453498106</v>
+        <v>-0.001962288453498811</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.18166403535008e-15</v>
+        <v>-2.459196944341733e-16</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.009637448260274106</v>
+        <v>-0.009637448260284578</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.009637448260301185</v>
+        <v>-0.00963744826029103</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0100031811838515</v>
+        <v>0.01000318118385151</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001196064788409722</v>
+        <v>0.00119606478840903</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.001196064788407717</v>
+        <v>-0.001196064788408546</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.054790642029308e-15</v>
+        <v>-6.310766232131836e-16</v>
       </c>
       <c r="V8" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.001172324935996923</v>
+        <v>-0.001172324935992853</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001172324935986361</v>
+        <v>0.001172324935990341</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.18166403535008e-15</v>
+        <v>-2.459196944341733e-16</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.001962288453498106</v>
+        <v>-0.001962288453498811</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.001962288453499951</v>
+        <v>-0.00196228845349925</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0100031811838515</v>
+        <v>0.01000318118385151</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.009637448260301185</v>
+        <v>-0.00963744826029103</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.009637448260274106</v>
+        <v>0.009637448260284578</v>
       </c>
       <c r="AE8" t="n">
-        <v>-3.054790642029308e-15</v>
+        <v>-6.310766232131836e-16</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.001196064788407717</v>
+        <v>-0.001196064788408546</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.001196064788409722</v>
+        <v>-0.00119606478840903</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.1186993525493563</v>
+        <v>-0.1186993525500384</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.2491176456847733</v>
+        <v>-0.2491176456852433</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2491176456859986</v>
+        <v>0.2491176456855322</v>
       </c>
       <c r="AK8" t="n">
-        <v>5.331206495933188e-15</v>
+        <v>1.096215874217183e-15</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.314358449224885</v>
+        <v>-1.314358449223394</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1.314358449221089</v>
+        <v>-1.314358449222493</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.1186993525493563</v>
+        <v>0.1186993525500384</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.2491176456847733</v>
+        <v>0.2491176456852433</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.2491176456859986</v>
+        <v>-0.2491176456855322</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-5.331206495933188e-15</v>
+        <v>-1.096215874217183e-15</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.1803474248911088</v>
+        <v>-0.1803474248898009</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.1803474248875491</v>
+        <v>-0.1803474248889678</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.139840215900042e-06</v>
+        <v>-1.139840215896985e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.899733693166737e-07</v>
+        <v>-1.899733693161641e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1800947541122067</v>
+        <v>-0.1800947541117236</v>
       </c>
       <c r="I9" t="n">
-        <v>-37.99467386333474</v>
+        <v>-37.99467386323282</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.005133919027358861</v>
+        <v>-0.005133919027355294</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001181950344906979</v>
+        <v>-0.001181950344902908</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>0.000858135375921254</v>
+        <v>0.0008581353759205526</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.001247154414833003</v>
+        <v>-0.001247154414832387</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.18139457602318e-15</v>
+        <v>-2.45883799833235e-16</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.01030901918800909</v>
+        <v>-0.01030901918800026</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.00963419003515636</v>
+        <v>-0.009634190035146204</v>
       </c>
       <c r="R9" t="n">
-        <v>-6.034816844260094e-06</v>
+        <v>-6.034816844253537e-06</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001439162794336123</v>
+        <v>0.001439162794335432</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0009979940318752018</v>
+        <v>-0.0009979940318746456</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.054355086044638e-15</v>
+        <v>-6.323352839555595e-16</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.001181950344906979</v>
+        <v>-0.001181950344902908</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005133919027358861</v>
+        <v>0.005133919027355294</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.18139457602318e-15</v>
+        <v>-2.45883799833235e-16</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.001247154414833003</v>
+        <v>-0.001247154414832387</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.000858135375921254</v>
+        <v>-0.0008581353759205526</v>
       </c>
       <c r="AB9" t="n">
-        <v>-6.034816844260094e-06</v>
+        <v>-6.034816844253537e-06</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.00963419003515636</v>
+        <v>-0.009634190035146204</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01030901918800909</v>
+        <v>0.01030901918800026</v>
       </c>
       <c r="AE9" t="n">
-        <v>-3.054355086044638e-15</v>
+        <v>-6.323352839555595e-16</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0009979940318752018</v>
+        <v>-0.0009979940318746456</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.001439162794336123</v>
+        <v>-0.001439162794335432</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1800947541122068</v>
+        <v>0.1800947541117236</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.3848851442710549</v>
+        <v>0.384885144270585</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.3848851442703483</v>
+        <v>0.3848851442707786</v>
       </c>
       <c r="AK9" t="n">
-        <v>5.330733759291841e-15</v>
+        <v>1.099900377886616e-15</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.339034116199818</v>
+        <v>-1.339034116201065</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.584615722440167</v>
+        <v>1.584615722438765</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.1800947541122068</v>
+        <v>-0.1800947541117236</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.3848851442710549</v>
+        <v>-0.384885144270585</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.3848851442703483</v>
+        <v>-0.3848851442707786</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-5.330733759291841e-15</v>
+        <v>-1.099900377886616e-15</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.9702767494222719</v>
+        <v>-0.9702767494236078</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.7246951431861609</v>
+        <v>0.7246951431847437</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.733241364303834e-07</v>
+        <v>1.733241364251792e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>2.888735607173056e-08</v>
+        <v>2.88873560708632e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02738521355600057</v>
+        <v>0.02738521355517831</v>
       </c>
       <c r="I10" t="n">
-        <v>5.777471214346112</v>
+        <v>5.777471214172639</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.01030576096286427</v>
+        <v>-0.01030576096285544</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01030576096284246</v>
+        <v>-0.01030576096285178</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.009991111550163006</v>
+        <v>-0.009991111550163018</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00124109203779992</v>
+        <v>0.001241092037800776</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.001241092037801604</v>
+        <v>-0.001241092037801047</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.055103843794704e-15</v>
+        <v>-6.320011768432583e-16</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.01737007367944867</v>
+        <v>-0.01737007367943667</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.01737007367941414</v>
+        <v>-0.0173700736794309</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.009990938226026575</v>
+        <v>-0.009990938226026593</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001204350062740928</v>
+        <v>0.001204350062741668</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.001204350062742015</v>
+        <v>-0.001204350062741899</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.803761237550783e-15</v>
+        <v>-1.012366336751686e-15</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.009991111550163006</v>
+        <v>-0.009991111550163018</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01030576096284246</v>
+        <v>-0.01030576096285178</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01030576096286427</v>
+        <v>0.01030576096285544</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.055103843794704e-15</v>
+        <v>-6.320011768432583e-16</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.001241092037801604</v>
+        <v>-0.001241092037801047</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.00124109203779992</v>
+        <v>-0.001241092037800776</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.009990938226026575</v>
+        <v>-0.009990938226026593</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.01737007367941414</v>
+        <v>-0.0173700736794309</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01737007367944867</v>
+        <v>0.01737007367943667</v>
       </c>
       <c r="AE10" t="n">
-        <v>-4.803761237550783e-15</v>
+        <v>-1.012366336751686e-15</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.001204350062742015</v>
+        <v>-0.001204350062741899</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.001204350062740928</v>
+        <v>-0.001204350062741668</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.02738521355581724</v>
+        <v>-0.02738521355513512</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.06709668431254689</v>
+        <v>-0.06709668431189275</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.06709668431145799</v>
+        <v>0.06709668431174309</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.976947966844225e-15</v>
+        <v>1.082577762816293e-15</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.2284791144784704</v>
+        <v>-0.2284791144789988</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.2284791144812948</v>
+        <v>-0.2284791144794198</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02738521355581724</v>
+        <v>0.02738521355513512</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.06709668431254689</v>
+        <v>0.06709668431189275</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.06709668431145799</v>
+        <v>-0.06709668431174309</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-4.976947966844225e-15</v>
+        <v>-1.082577762816293e-15</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.1741009913902776</v>
+        <v>-0.1741009913914588</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.1741009913939884</v>
+        <v>-0.1741009913919385</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.121065937212221e-07</v>
+        <v>-1.12106593720697e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.868443228687035e-08</v>
+        <v>-1.868443228678283e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0177128418079531</v>
+        <v>-0.01771284180787012</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.736886457374071</v>
+        <v>-3.736886457356566</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.009634190035129281</v>
+        <v>-0.009634190035139751</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01030901918798729</v>
+        <v>-0.0103090191879966</v>
       </c>
       <c r="L11" t="n">
-        <v>-6.034816844246121e-06</v>
+        <v>-6.034816844245296e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0009979940318735161</v>
+        <v>0.0009979940318743741</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.00143916279433412</v>
+        <v>-0.001439162794334948</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.05495934852082e-15</v>
+        <v>-6.325385275155652e-16</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.01735361784199784</v>
+        <v>-0.01735361784201489</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.01736938160992134</v>
+        <v>-0.01736938160993809</v>
       </c>
       <c r="R11" t="n">
-        <v>-6.146923437967343e-06</v>
+        <v>-6.146923437965993e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>0.00125937918302127</v>
+        <v>0.001259379183022008</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.00123006073370777</v>
+        <v>-0.001230060733708419</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.803892303683812e-15</v>
+        <v>-1.012110102286476e-15</v>
       </c>
       <c r="V11" t="n">
-        <v>-6.034816844246121e-06</v>
+        <v>-6.034816844245296e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01030901918798729</v>
+        <v>-0.0103090191879966</v>
       </c>
       <c r="X11" t="n">
-        <v>0.009634190035129281</v>
+        <v>0.009634190035139751</v>
       </c>
       <c r="Y11" t="n">
-        <v>-3.05495934852082e-15</v>
+        <v>-6.325385275155652e-16</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.00143916279433412</v>
+        <v>-0.001439162794334948</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.0009979940318735161</v>
+        <v>-0.0009979940318743741</v>
       </c>
       <c r="AB11" t="n">
-        <v>-6.146923437967343e-06</v>
+        <v>-6.146923437965993e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.01736938160992134</v>
+        <v>-0.01736938160993809</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.01735361784199784</v>
+        <v>0.01735361784201489</v>
       </c>
       <c r="AE11" t="n">
-        <v>-4.803892303683812e-15</v>
+        <v>-1.012110102286476e-15</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.00123006073370777</v>
+        <v>-0.001230060733708419</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.00125937918302127</v>
+        <v>-0.001259379183022008</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.01771284180795318</v>
+        <v>0.01771284180787014</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.07109988505492337</v>
+        <v>0.0710998850555784</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.07109988505675269</v>
+        <v>0.07109988505622278</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.977732257002361e-15</v>
+        <v>1.080319097424901e-15</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.3680351800337569</v>
+        <v>-0.368035180032301</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.4067246670141085</v>
+        <v>0.4067246670159843</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.01771284180795318</v>
+        <v>-0.01771284180787014</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.07109988505492337</v>
+        <v>-0.0710998850555784</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.07109988505675269</v>
+        <v>-0.07109988505622278</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-4.977732257002361e-15</v>
+        <v>-1.080319097424901e-15</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.05856413030676011</v>
+        <v>-0.05856413030504015</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.01987464331543176</v>
+        <v>0.01987464331748789</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>5.088905101306718e-08</v>
+        <v>5.08890510148019e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>8.481508502177862e-09</v>
+        <v>8.481508502466983e-09</v>
       </c>
       <c r="H12" t="n">
-        <v>0.008040470060064614</v>
+        <v>0.0080404700603387</v>
       </c>
       <c r="I12" t="n">
-        <v>1.696301700435572</v>
+        <v>1.696301700493397</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.009637448260274106</v>
+        <v>-0.009637448260284578</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.009637448260301185</v>
+        <v>-0.00963744826029103</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0100031811838515</v>
+        <v>0.01000318118385151</v>
       </c>
       <c r="M12" t="n">
-        <v>0.001196064788409722</v>
+        <v>0.00119606478840903</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.001196064788407717</v>
+        <v>-0.001196064788408546</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.054790642029308e-15</v>
+        <v>-6.310766232131836e-16</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.01735292577250504</v>
+        <v>-0.01735292577252209</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.01735292577254737</v>
+        <v>-0.01735292577253253</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001285089853989626</v>
+        <v>0.001285089853989261</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.001285089853988111</v>
+        <v>-0.001285089853988761</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.803309957801465e-15</v>
+        <v>-1.012571952175807e-15</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0100031811838515</v>
+        <v>0.01000318118385151</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.009637448260301185</v>
+        <v>-0.00963744826029103</v>
       </c>
       <c r="X12" t="n">
-        <v>0.009637448260274106</v>
+        <v>0.009637448260284578</v>
       </c>
       <c r="Y12" t="n">
-        <v>-3.054790642029308e-15</v>
+        <v>-6.310766232131836e-16</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.001196064788407717</v>
+        <v>-0.001196064788408546</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.001196064788409722</v>
+        <v>-0.00119606478840903</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.01735292577254737</v>
+        <v>-0.01735292577253253</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.01735292577250504</v>
+        <v>0.01735292577252209</v>
       </c>
       <c r="AE12" t="n">
-        <v>-4.803309957801465e-15</v>
+        <v>-1.012571952175807e-15</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.001285089853988111</v>
+        <v>-0.001285089853988761</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.001285089853989626</v>
+        <v>-0.001285089853989261</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.008040470059995641</v>
+        <v>-0.008040470060223015</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.06709668431187632</v>
+        <v>0.06709668431150018</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.06709668431071891</v>
+        <v>-0.06709668431124749</v>
       </c>
       <c r="AK12" t="n">
-        <v>4.976554975659214e-15</v>
+        <v>1.085794397816698e-15</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.2671686014616472</v>
+        <v>0.2671686014630996</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.267168601464757</v>
+        <v>0.2671686014638706</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.008040470059995641</v>
+        <v>0.008040470060223015</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.06709668431187632</v>
+        <v>-0.06709668431150018</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.06709668431071891</v>
+        <v>0.06709668431124749</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-4.976554975659214e-15</v>
+        <v>-1.085794397816698e-15</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.1354115044026627</v>
+        <v>0.1354115044043827</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.1354115044064992</v>
+        <v>0.1354115044051305</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.121065937255742e-07</v>
+        <v>-1.121065937232203e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.86844322875957e-08</v>
+        <v>-1.868443228720338e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.01771284180864072</v>
+        <v>-0.0177128418082688</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.736886457519139</v>
+        <v>-3.736886457440675</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.01030901918800909</v>
+        <v>-0.01030901918800026</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.00963419003515636</v>
+        <v>-0.009634190035146204</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.034816844260094e-06</v>
+        <v>-6.034816844253537e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001439162794336123</v>
+        <v>0.001439162794335432</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0009979940318752018</v>
+        <v>-0.0009979940318746456</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.054355086044638e-15</v>
+        <v>-6.323352839555595e-16</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.01736938160995587</v>
+        <v>-0.01736938160994386</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.01735361784204018</v>
+        <v>-0.01735361784202533</v>
       </c>
       <c r="R13" t="n">
-        <v>-6.146923437985668e-06</v>
+        <v>-6.146923437976757e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001230060733709285</v>
+        <v>0.001230060733708922</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.001259379183022356</v>
+        <v>-0.001259379183022239</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.804447417211208e-15</v>
+        <v>-1.013382782898572e-15</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.034816844260094e-06</v>
+        <v>-6.034816844253537e-06</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.00963419003515636</v>
+        <v>-0.009634190035146204</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01030901918800909</v>
+        <v>0.01030901918800026</v>
       </c>
       <c r="Y13" t="n">
-        <v>-3.054355086044638e-15</v>
+        <v>-6.323352839555595e-16</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.0009979940318752018</v>
+        <v>-0.0009979940318746456</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.001439162794336123</v>
+        <v>-0.001439162794335432</v>
       </c>
       <c r="AB13" t="n">
-        <v>-6.146923437985668e-06</v>
+        <v>-6.146923437976757e-06</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.01735361784204018</v>
+        <v>-0.01735361784202533</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01736938160995587</v>
+        <v>0.01736938160994386</v>
       </c>
       <c r="AE13" t="n">
-        <v>-4.804447417211208e-15</v>
+        <v>-1.013382782898572e-15</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.001259379183022356</v>
+        <v>-0.001259379183022239</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.001230060733709285</v>
+        <v>-0.001230060733708922</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01771284180864063</v>
+        <v>0.01771284180826882</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.07109988505559262</v>
+        <v>-0.07109988505597098</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.07109988505601206</v>
+        <v>-0.07109988505572762</v>
       </c>
       <c r="AK13" t="n">
-        <v>4.981032019474084e-15</v>
+        <v>1.084519804683958e-15</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.4067246670169316</v>
+        <v>0.4067246670164</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.3680351800306383</v>
+        <v>-0.36803518003153</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.01771284180864063</v>
+        <v>-0.01771284180826882</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.07109988505559262</v>
+        <v>0.07109988505597098</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.07109988505601206</v>
+        <v>0.07109988505572762</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-4.981032019474084e-15</v>
+        <v>-1.084519804683958e-15</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01987464331914257</v>
+        <v>0.01987464331796218</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.05856413030291918</v>
+        <v>-0.05856413030429408</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>2.247600022764473e-09</v>
+        <v>2.247600015825579e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>3.746000037940789e-10</v>
+        <v>3.746000026375966e-10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003551208035967868</v>
+        <v>0.0003551208025004415</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07492000075881577</v>
+        <v>0.07492000052751931</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.01737007367944867</v>
+        <v>-0.01737007367943667</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01737007367941414</v>
+        <v>-0.0173700736794309</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.009990938226026575</v>
+        <v>-0.009990938226026593</v>
       </c>
       <c r="M14" t="n">
-        <v>0.001204350062740928</v>
+        <v>0.001204350062741668</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.001204350062742015</v>
+        <v>-0.001204350062741899</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.803761237550783e-15</v>
+        <v>-1.012366336751686e-15</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.02482398266159128</v>
+        <v>-0.02482398266158013</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.0248239826615519</v>
+        <v>-0.02482398266157276</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.009990935978426553</v>
+        <v>-0.009990935978426577</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001257818715765292</v>
+        <v>0.001257818715765601</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.001257818715765604</v>
+        <v>-0.001257818715765732</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.674836422945595e-15</v>
+        <v>-1.358705779577601e-15</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.009990938226026575</v>
+        <v>-0.009990938226026593</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.01737007367941414</v>
+        <v>-0.0173700736794309</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01737007367944867</v>
+        <v>0.01737007367943667</v>
       </c>
       <c r="Y14" t="n">
-        <v>-4.803761237550783e-15</v>
+        <v>-1.012366336751686e-15</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.001204350062742015</v>
+        <v>-0.001204350062741899</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.001204350062740928</v>
+        <v>-0.001204350062741668</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.009990935978426553</v>
+        <v>-0.009990935978426577</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.0248239826615519</v>
+        <v>-0.02482398266157276</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.02482398266159128</v>
+        <v>0.02482398266158013</v>
       </c>
       <c r="AE14" t="n">
-        <v>-5.674836422945595e-15</v>
+        <v>-1.358705779577601e-15</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.001257818715765604</v>
+        <v>-0.001257818715765732</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.001257818715765292</v>
+        <v>-0.001257818715765601</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.0003551208037606557</v>
+        <v>-0.0003551208026237873</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.01662598616604516</v>
+        <v>0.01662598616628053</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.01662598616620636</v>
+        <v>-0.01662598616640665</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.479213989200619e-15</v>
+        <v>9.857353372737588e-16</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.08944476173607985</v>
+        <v>0.089444761736857</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.089444761736166</v>
+        <v>0.08944476173654792</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0003551208037606557</v>
+        <v>0.0003551208026237873</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01662598616604516</v>
+        <v>-0.01662598616628053</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.01662598616620636</v>
+        <v>0.01662598616640665</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-2.479213989200619e-15</v>
+        <v>-9.857353372737588e-16</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.01031115526116544</v>
+        <v>0.01031115526158288</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.01031115526010673</v>
+        <v>0.01031115526112991</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>7.168575258776767e-09</v>
+        <v>7.168575258849612e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>1.194762543129461e-09</v>
+        <v>1.194762543141602e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001132634890886729</v>
+        <v>0.001132634890898239</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2389525086258922</v>
+        <v>0.2389525086283204</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.01735361784199784</v>
+        <v>-0.01735361784201489</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01736938160992134</v>
+        <v>-0.01736938160993809</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.146923437967343e-06</v>
+        <v>-6.146923437965993e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>0.00125937918302127</v>
+        <v>0.001259379183022008</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.00123006073370777</v>
+        <v>-0.001230060733708419</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.803892303683812e-15</v>
+        <v>-1.012110102286476e-15</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.02485967309713104</v>
+        <v>-0.02485967309715188</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.02482409162315708</v>
+        <v>-0.02482409162317794</v>
       </c>
       <c r="R15" t="n">
-        <v>-6.139754862708566e-06</v>
+        <v>-6.139754862707143e-06</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001237953768590255</v>
+        <v>0.001237953768590565</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.001259528070805193</v>
+        <v>-0.001259528070805485</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.67899907152334e-15</v>
+        <v>-1.357769995309901e-15</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.146923437967343e-06</v>
+        <v>-6.146923437965993e-06</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.01736938160992134</v>
+        <v>-0.01736938160993809</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01735361784199784</v>
+        <v>0.01735361784201489</v>
       </c>
       <c r="Y15" t="n">
-        <v>-4.803892303683812e-15</v>
+        <v>-1.012110102286476e-15</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.00123006073370777</v>
+        <v>-0.001230060733708419</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.00125937918302127</v>
+        <v>-0.001259379183022008</v>
       </c>
       <c r="AB15" t="n">
-        <v>-6.139754862708566e-06</v>
+        <v>-6.139754862707143e-06</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.02482409162315708</v>
+        <v>-0.02482409162317794</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.02485967309713104</v>
+        <v>0.02485967309715188</v>
       </c>
       <c r="AE15" t="n">
-        <v>-5.67899907152334e-15</v>
+        <v>-1.357769995309901e-15</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.001259528070805193</v>
+        <v>-0.001259528070805485</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.001237953768590255</v>
+        <v>-0.001237953768590565</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.001132634890886774</v>
+        <v>-0.00113263489089821</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.009197914261043216</v>
+        <v>-0.009197914260807849</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.00919791425992933</v>
+        <v>-0.009197914260166584</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.490688493081734e-15</v>
+        <v>9.838012339897462e-16</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.04939957223187874</v>
+        <v>0.04939957223232838</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.04344854946208265</v>
+        <v>-0.04344854946169363</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.001132634890886774</v>
+        <v>0.00113263489089821</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.009197914261043216</v>
+        <v>0.009197914260807849</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.00919791425992933</v>
+        <v>0.009197914260166584</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-2.490688493081734e-15</v>
+        <v>-9.838012339897462e-16</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.005787913327693683</v>
+        <v>0.005787913328671124</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0.01173893610418197</v>
+        <v>-0.01173893610315879</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.658475053123443e-08</v>
+        <v>-1.658475053296915e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.764125088539071e-09</v>
+        <v>-2.764125088828192e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.002620390583935039</v>
+        <v>-0.002620390584209126</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5528250177078142</v>
+        <v>-0.5528250177656383</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.01735292577250504</v>
+        <v>-0.01735292577252209</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01735292577254737</v>
+        <v>-0.01735292577253253</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="M16" t="n">
-        <v>0.001285089853989626</v>
+        <v>0.001285089853989261</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.001285089853988111</v>
+        <v>-0.001285089853988761</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.803309957801465e-15</v>
+        <v>-1.012571952175807e-15</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001239663123630873</v>
+        <v>0.001239663123630794</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.001239663123630155</v>
+        <v>-0.001239663123630448</v>
       </c>
       <c r="U16" t="n">
-        <v>-5.676397154560981e-15</v>
+        <v>-1.357742617260905e-15</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.01735292577254737</v>
+        <v>-0.01735292577253253</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01735292577250504</v>
+        <v>0.01735292577252209</v>
       </c>
       <c r="Y16" t="n">
-        <v>-4.803309957801465e-15</v>
+        <v>-1.012571952175807e-15</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.001285089853988111</v>
+        <v>-0.001285089853988761</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.001285089853989626</v>
+        <v>-0.001285089853989261</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.02485978205873622</v>
+        <v>0.02485978205875706</v>
       </c>
       <c r="AE16" t="n">
-        <v>-5.676397154560981e-15</v>
+        <v>-1.357742617260905e-15</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.001239663123630155</v>
+        <v>-0.001239663123630448</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.001239663123630873</v>
+        <v>-0.001239663123630794</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.002620390583842891</v>
+        <v>0.002620390584070265</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.01662598616656297</v>
+        <v>-0.01662598616658162</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01662598616716049</v>
+        <v>0.01662598616692357</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.484940483084779e-15</v>
+        <v>9.82408816011432e-16</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.08349373896636569</v>
+        <v>-0.08349373896592382</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.08349373896516532</v>
+        <v>-0.08349373896501433</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.002620390583842891</v>
+        <v>-0.002620390584070265</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.01662598616656297</v>
+        <v>0.01662598616658162</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01662598616716049</v>
+        <v>-0.01662598616692357</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-2.484940483084779e-15</v>
+        <v>-9.82408816011432e-16</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.01626217803659191</v>
+        <v>-0.01626217803562113</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0.01626217803421071</v>
+        <v>-0.01626217803448071</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>7.168575256660879e-09</v>
+        <v>7.168575257735764e-09</v>
       </c>
       <c r="G17" t="n">
-        <v>1.194762542776813e-09</v>
+        <v>1.194762542955961e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001132634890552419</v>
+        <v>0.001132634890722251</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2389525085553626</v>
+        <v>0.2389525085911921</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.01736938160995587</v>
+        <v>-0.01736938160994386</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01735361784204018</v>
+        <v>-0.01735361784202533</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.146923437985668e-06</v>
+        <v>-6.146923437976757e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>0.001230060733709285</v>
+        <v>0.001230060733708922</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.001259379183022356</v>
+        <v>-0.001259379183022239</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.804447417211208e-15</v>
+        <v>-1.013382782898572e-15</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.02482409162319647</v>
+        <v>-0.0248240916231853</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.0248596730971825</v>
+        <v>-0.02485967309716625</v>
       </c>
       <c r="R17" t="n">
-        <v>-6.139754862729007e-06</v>
+        <v>-6.139754862719022e-06</v>
       </c>
       <c r="S17" t="n">
-        <v>0.001259528070805909</v>
+        <v>0.00125952807080583</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.001237953768590568</v>
+        <v>-0.001237953768590698</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.677821559011737e-15</v>
+        <v>-1.357962856859783e-15</v>
       </c>
       <c r="V17" t="n">
-        <v>-6.146923437985668e-06</v>
+        <v>-6.146923437976757e-06</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.01735361784204018</v>
+        <v>-0.01735361784202533</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01736938160995587</v>
+        <v>0.01736938160994386</v>
       </c>
       <c r="Y17" t="n">
-        <v>-4.804447417211208e-15</v>
+        <v>-1.013382782898572e-15</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.001259379183022356</v>
+        <v>-0.001259379183022239</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.001230060733709285</v>
+        <v>-0.001230060733708922</v>
       </c>
       <c r="AB17" t="n">
-        <v>-6.139754862729007e-06</v>
+        <v>-6.139754862719022e-06</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.0248596730971825</v>
+        <v>-0.02485967309716625</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.02482409162319647</v>
+        <v>0.0248240916231853</v>
       </c>
       <c r="AE17" t="n">
-        <v>-5.677821559011737e-15</v>
+        <v>-1.357962856859783e-15</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.001237953768590568</v>
+        <v>-0.001237953768590698</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.001259528070805909</v>
+        <v>-0.00125952807080583</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.001132634890552375</v>
+        <v>-0.001132634890722239</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.009197914260527185</v>
+        <v>0.009197914260510309</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.009197914260882456</v>
+        <v>0.009197914260683504</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.485757172816889e-15</v>
+        <v>9.807279028126785e-16</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.04344854946217147</v>
+        <v>-0.04344854946139165</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.04939957223308333</v>
+        <v>0.04939957223324143</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.001132634890552375</v>
+        <v>0.001132634890722239</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.009197914260527185</v>
+        <v>-0.009197914260510309</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.009197914260882456</v>
+        <v>-0.009197914260683504</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-2.485757172816889e-15</v>
+        <v>-9.807279028126785e-16</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0.01173893610312504</v>
+        <v>-0.01173893610271293</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.005787913330079775</v>
+        <v>0.005787913329816874</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>9.625408910056074e-06</v>
+        <v>9.625408910055207e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>1.203176113757009e-06</v>
+        <v>1.203176113756901e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>1.140610955841645</v>
+        <v>1.140610955841542</v>
       </c>
       <c r="I18" t="n">
-        <v>240.6352227514018</v>
+        <v>240.6352227513802</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.005143544436268916</v>
+        <v>-0.005143544436265349</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.005143544436260579</v>
+        <v>-0.005143544436263927</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.009992639968869796</v>
+        <v>-0.009992639968869803</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0001430013372528314</v>
+        <v>0.0001430013372534397</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0001430013372543053</v>
+        <v>-0.0001430013372536887</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1816844298607e-15</v>
+        <v>-2.459828480256998e-16</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.001181950344896417</v>
+        <v>-0.001181950344900396</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.005133919027350523</v>
+        <v>-0.005133919027353872</v>
       </c>
       <c r="R18" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="S18" t="n">
-        <v>0.00124715441483153</v>
+        <v>0.001247154414832138</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0008581353759194087</v>
+        <v>-0.0008581353759201137</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.181563932377305e-15</v>
+        <v>-2.45867092239527e-16</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.005143544436260579</v>
+        <v>-0.005143544436263927</v>
       </c>
       <c r="W18" t="n">
-        <v>0.005143544436268916</v>
+        <v>0.005143544436265349</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.009992639968869796</v>
+        <v>-0.009992639968869803</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.0001430013372543053</v>
+        <v>-0.0001430013372536887</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.0001430013372528314</v>
+        <v>-0.0001430013372534397</v>
       </c>
       <c r="AA18" t="n">
-        <v>-1.1816844298607e-15</v>
+        <v>-2.459828480256998e-16</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.005133919027350523</v>
+        <v>-0.005133919027353872</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.001181950344896417</v>
+        <v>0.001181950344900396</v>
       </c>
       <c r="AD18" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0008581353759194087</v>
+        <v>-0.0008581353759201137</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.00124715441483153</v>
+        <v>-0.001247154414832138</v>
       </c>
       <c r="AG18" t="n">
-        <v>-1.181563932377305e-15</v>
+        <v>-2.45867092239527e-16</v>
       </c>
       <c r="AH18" t="n">
         <v>-1.140610955841566</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.412253385132467</v>
+        <v>0.4122533851324607</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0.4606973814500098</v>
+        <v>-0.4606973814495045</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.001526536120996663</v>
+        <v>0.001526536120999484</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.455594483856218</v>
+        <v>2.455594483854196</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.649013540529868</v>
+        <v>1.649013540529843</v>
       </c>
       <c r="AN18" t="n">
         <v>1.140610955841566</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.412253385132467</v>
+        <v>-0.4122533851324607</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.4606973814500098</v>
+        <v>0.4606973814495045</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0.001526536120996663</v>
+        <v>-0.001526536120999484</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.229984567743863</v>
+        <v>1.229984567741841</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.649013540529868</v>
+        <v>1.649013540529843</v>
       </c>
     </row>
     <row r="19">
@@ -6354,124 +6354,124 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>9.62540891005564e-06</v>
+        <v>9.625408910055207e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>1.203176113756955e-06</v>
+        <v>1.203176113756901e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.140610955841593</v>
+        <v>1.140610955841542</v>
       </c>
       <c r="I19" t="n">
-        <v>240.635222751391</v>
+        <v>240.6352227513802</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.001181950344896417</v>
+        <v>-0.001181950344900396</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.005133919027350523</v>
+        <v>-0.005133919027353872</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="M19" t="n">
-        <v>0.00124715441483153</v>
+        <v>0.001247154414832138</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0008581353759194087</v>
+        <v>-0.0008581353759201137</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.181563932377305e-15</v>
+        <v>-2.45867092239527e-16</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.001172324935986361</v>
+        <v>-0.001172324935990341</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.001172324935996923</v>
+        <v>-0.001172324935992853</v>
       </c>
       <c r="R19" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="S19" t="n">
-        <v>0.001962288453499951</v>
+        <v>0.00196228845349925</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.001962288453498106</v>
+        <v>-0.001962288453498811</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.18166403535008e-15</v>
+        <v>-2.459196944341733e-16</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.001181950344896417</v>
+        <v>-0.001181950344900396</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.005133919027350523</v>
+        <v>-0.005133919027353872</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.894976628352089e-06</v>
+        <v>-4.894976628351932e-06</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.00124715441483153</v>
+        <v>0.001247154414832138</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.0008581353759194087</v>
+        <v>-0.0008581353759201137</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.181563932377305e-15</v>
+        <v>-2.45867092239527e-16</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.001172324935986361</v>
+        <v>-0.001172324935990341</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.001172324935996923</v>
+        <v>-0.001172324935992853</v>
       </c>
       <c r="AD19" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.001962288453499951</v>
+        <v>0.00196228845349925</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.001962288453498106</v>
+        <v>-0.001962288453498811</v>
       </c>
       <c r="AG19" t="n">
-        <v>-1.18166403535008e-15</v>
+        <v>-2.459196944341733e-16</v>
       </c>
       <c r="AH19" t="n">
-        <v>-1.140610955841595</v>
+        <v>-1.140610955841538</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.4122533851324677</v>
+        <v>-0.4122533851324608</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1326141717183632</v>
+        <v>0.1326141717189501</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.001526536121003745</v>
+        <v>-0.00152653612100095</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.08234827118272525</v>
+        <v>0.08234827118037735</v>
       </c>
       <c r="AM19" t="n">
-        <v>-1.649013540529871</v>
+        <v>-1.649013540529843</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.140610955841595</v>
+        <v>1.140610955841538</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.4122533851324677</v>
+        <v>0.4122533851324608</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.1326141717183632</v>
+        <v>-0.1326141717189501</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.001526536121003745</v>
+        <v>0.00152653612100095</v>
       </c>
       <c r="AR19" t="n">
-        <v>-1.143261644929629</v>
+        <v>-1.143261644931977</v>
       </c>
       <c r="AS19" t="n">
-        <v>-1.649013540529871</v>
+        <v>-1.649013540529843</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>9.625408910055424e-06</v>
+        <v>9.625408910055207e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>1.203176113756928e-06</v>
+        <v>1.203176113756901e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>1.140610955841568</v>
+        <v>1.140610955841542</v>
       </c>
       <c r="I20" t="n">
-        <v>240.6352227513856</v>
+        <v>240.6352227513802</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.001172324935986361</v>
+        <v>-0.001172324935990341</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.001172324935996923</v>
+        <v>-0.001172324935992853</v>
       </c>
       <c r="L20" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="M20" t="n">
-        <v>0.001962288453499951</v>
+        <v>0.00196228845349925</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.001962288453498106</v>
+        <v>-0.001962288453498811</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.18166403535008e-15</v>
+        <v>-2.459196944341733e-16</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.005133919027358861</v>
+        <v>-0.005133919027355294</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.001181950344906979</v>
+        <v>-0.001181950344902908</v>
       </c>
       <c r="R20" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="S20" t="n">
-        <v>0.000858135375921254</v>
+        <v>0.0008581353759205526</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.001247154414833003</v>
+        <v>-0.001247154414832387</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.18139457602318e-15</v>
+        <v>-2.45883799833235e-16</v>
       </c>
       <c r="V20" t="n">
-        <v>0.001172324935996923</v>
+        <v>0.001172324935992853</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.001172324935986361</v>
+        <v>-0.001172324935990341</v>
       </c>
       <c r="X20" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.001962288453498106</v>
+        <v>0.001962288453498811</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.001962288453499951</v>
+        <v>0.00196228845349925</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1.18166403535008e-15</v>
+        <v>-2.459196944341733e-16</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.001181950344906979</v>
+        <v>0.001181950344902908</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.005133919027358861</v>
+        <v>-0.005133919027355294</v>
       </c>
       <c r="AD20" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.001247154414833003</v>
+        <v>0.001247154414832387</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.000858135375921254</v>
+        <v>0.0008581353759205526</v>
       </c>
       <c r="AG20" t="n">
-        <v>-1.18139457602318e-15</v>
+        <v>-2.45883799833235e-16</v>
       </c>
       <c r="AH20" t="n">
-        <v>-1.140610955841566</v>
+        <v>-1.140610955841538</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.4122533851324672</v>
+        <v>0.4122533851324607</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.1326141717198984</v>
+        <v>-0.1326141717193148</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.001526536120996663</v>
+        <v>0.001526536120999483</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.14326164493577</v>
+        <v>1.143261644933435</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.649013540529868</v>
+        <v>1.649013540529843</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.140610955841566</v>
+        <v>1.140610955841538</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.4122533851324672</v>
+        <v>-0.4122533851324607</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.1326141717198984</v>
+        <v>0.1326141717193148</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.001526536120996663</v>
+        <v>-0.001526536120999483</v>
       </c>
       <c r="AR20" t="n">
-        <v>-0.08234827117658372</v>
+        <v>-0.08234827117891852</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.649013540529868</v>
+        <v>1.649013540529843</v>
       </c>
     </row>
     <row r="21">
@@ -6644,112 +6644,112 @@
         <v>240.6352227513802</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.005133919027358861</v>
+        <v>-0.005133919027355294</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001181950344906979</v>
+        <v>-0.001181950344902908</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.894976628360052e-06</v>
+        <v>-4.894976628356553e-06</v>
       </c>
       <c r="M21" t="n">
-        <v>0.000858135375921254</v>
+        <v>0.0008581353759205526</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.001247154414833003</v>
+        <v>-0.001247154414832387</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.18139457602318e-15</v>
+        <v>-2.45883799833235e-16</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.005143544436268916</v>
+        <v>-0.005143544436265349</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.005143544436260579</v>
+        <v>-0.005143544436263927</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.009992639968869796</v>
+        <v>-0.009992639968869803</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0001430013372528314</v>
+        <v>0.0001430013372534397</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0001430013372543053</v>
+        <v>-0.0001430013372536887</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1816844298607e-15</v>
+        <v>-2.459828480256998e-16</v>
       </c>
       <c r="V21" t="n">
-        <v>0.005133919027358861</v>
+        <v>0.005133919027355294</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.001181950344906979</v>
+        <v>-0.001181950344902908</v>
       </c>
       <c r="X21" t="n">
-        <v>4.894976628360052e-06</v>
+        <v>4.894976628356553e-06</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.000858135375921254</v>
+        <v>-0.0008581353759205526</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.001247154414833003</v>
+        <v>-0.001247154414832387</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.18139457602318e-15</v>
+        <v>2.45883799833235e-16</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.005143544436268916</v>
+        <v>0.005143544436265349</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.005143544436260579</v>
+        <v>-0.005143544436263927</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.009992639968869796</v>
+        <v>0.009992639968869803</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.0001430013372528314</v>
+        <v>-0.0001430013372534397</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.0001430013372543053</v>
+        <v>-0.0001430013372536887</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.1816844298607e-15</v>
+        <v>2.459828480256998e-16</v>
       </c>
       <c r="AH21" t="n">
-        <v>-1.140610955841453</v>
+        <v>-1.140610955841566</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.4122533851324676</v>
+        <v>0.4122533851324608</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0.4606973814487824</v>
+        <v>-0.4606973814492966</v>
       </c>
       <c r="AK21" t="n">
-        <v>-0.001526536121003748</v>
+        <v>-0.001526536121000953</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.229984567738952</v>
+        <v>1.22998456774101</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.649013540529871</v>
+        <v>1.649013540529843</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.140610955841453</v>
+        <v>1.140610955841566</v>
       </c>
       <c r="AO21" t="n">
-        <v>-0.4122533851324676</v>
+        <v>-0.4122533851324608</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.4606973814487824</v>
+        <v>0.4606973814492966</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.001526536121003748</v>
+        <v>0.001526536121000953</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.455594483851307</v>
+        <v>2.455594483853365</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.649013540529871</v>
+        <v>1.649013540529843</v>
       </c>
     </row>
     <row r="22">
@@ -6783,112 +6783,112 @@
         <v>-81.45562862063582</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.01030576096286427</v>
+        <v>-0.01030576096285544</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.01030576096284246</v>
+        <v>-0.01030576096285178</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.009991111550163006</v>
+        <v>-0.009991111550163018</v>
       </c>
       <c r="M22" t="n">
-        <v>0.00124109203779992</v>
+        <v>0.001241092037800776</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.001241092037801604</v>
+        <v>-0.001241092037801047</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.055103843794704e-15</v>
+        <v>-6.320011768432583e-16</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.009634190035129281</v>
+        <v>-0.009634190035139751</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.01030901918798729</v>
+        <v>-0.0103090191879966</v>
       </c>
       <c r="R22" t="n">
-        <v>-6.034816844246121e-06</v>
+        <v>-6.034816844245296e-06</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0009979940318735161</v>
+        <v>0.0009979940318743741</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.00143916279433412</v>
+        <v>-0.001439162794334948</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.05495934852082e-15</v>
+        <v>-6.325385275155652e-16</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.01030576096284246</v>
+        <v>-0.01030576096285178</v>
       </c>
       <c r="W22" t="n">
-        <v>0.01030576096286427</v>
+        <v>0.01030576096285544</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.009991111550163006</v>
+        <v>-0.009991111550163018</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.001241092037801604</v>
+        <v>-0.001241092037801047</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.00124109203779992</v>
+        <v>-0.001241092037800776</v>
       </c>
       <c r="AA22" t="n">
-        <v>-3.055103843794704e-15</v>
+        <v>-6.320011768432583e-16</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.01030901918798729</v>
+        <v>-0.0103090191879966</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.009634190035129281</v>
+        <v>0.009634190035139751</v>
       </c>
       <c r="AD22" t="n">
-        <v>-6.034816844246121e-06</v>
+        <v>-6.034816844245296e-06</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.00143916279433412</v>
+        <v>-0.001439162794334948</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.0009979940318735161</v>
+        <v>-0.0009979940318743741</v>
       </c>
       <c r="AG22" t="n">
-        <v>-3.05495934852082e-15</v>
+        <v>-6.325385275155652e-16</v>
       </c>
       <c r="AH22" t="n">
         <v>0.386099679661811</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.0698853496648788</v>
+        <v>0.06988534966488702</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0.1070524710594157</v>
+        <v>-0.1070524710587034</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.0004228048841367167</v>
+        <v>0.0004228048841396726</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.2932904909485095</v>
+        <v>0.2932904909456604</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.2795413986595152</v>
+        <v>0.2795413986595481</v>
       </c>
       <c r="AN22" t="n">
         <v>-0.386099679661811</v>
       </c>
       <c r="AO22" t="n">
-        <v>-0.0698853496648788</v>
+        <v>-0.06988534966488702</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.1070524710594157</v>
+        <v>0.1070524710587034</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-0.0004228048841367167</v>
+        <v>-0.0004228048841396726</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.5631292775268171</v>
+        <v>0.5631292775239671</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.2795413986595152</v>
+        <v>0.2795413986595481</v>
       </c>
     </row>
     <row r="23">
@@ -6910,124 +6910,124 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.258225144825433e-06</v>
+        <v>-3.258225144827168e-06</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.072781431031791e-07</v>
+        <v>-4.07278143103396e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3860996796618138</v>
+        <v>-0.3860996796620194</v>
       </c>
       <c r="I23" t="n">
-        <v>-81.45562862063582</v>
+        <v>-81.45562862067918</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.009634190035129281</v>
+        <v>-0.009634190035139751</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.01030901918798729</v>
+        <v>-0.0103090191879966</v>
       </c>
       <c r="L23" t="n">
-        <v>-6.034816844246121e-06</v>
+        <v>-6.034816844245296e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0009979940318735161</v>
+        <v>0.0009979940318743741</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.00143916279433412</v>
+        <v>-0.001439162794334948</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.05495934852082e-15</v>
+        <v>-6.325385275155652e-16</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.009637448260274106</v>
+        <v>-0.009637448260284578</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.009637448260301185</v>
+        <v>-0.00963744826029103</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0100031811838515</v>
+        <v>0.01000318118385151</v>
       </c>
       <c r="S23" t="n">
-        <v>0.001196064788409722</v>
+        <v>0.00119606478840903</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.001196064788407717</v>
+        <v>-0.001196064788408546</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.054790642029308e-15</v>
+        <v>-6.310766232131836e-16</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.009634190035129281</v>
+        <v>-0.009634190035139751</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.01030901918798729</v>
+        <v>-0.0103090191879966</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.034816844246121e-06</v>
+        <v>-6.034816844245296e-06</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.0009979940318735161</v>
+        <v>0.0009979940318743741</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.00143916279433412</v>
+        <v>-0.001439162794334948</v>
       </c>
       <c r="AA23" t="n">
-        <v>-3.05495934852082e-15</v>
+        <v>-6.325385275155652e-16</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.009637448260274106</v>
+        <v>-0.009637448260284578</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.009637448260301185</v>
+        <v>-0.00963744826029103</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.0100031811838515</v>
+        <v>0.01000318118385151</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.001196064788409722</v>
+        <v>0.00119606478840903</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.001196064788407717</v>
+        <v>-0.001196064788408546</v>
       </c>
       <c r="AG23" t="n">
-        <v>-3.054790642029308e-15</v>
+        <v>-6.310766232131836e-16</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.386099679661811</v>
+        <v>0.3860996796620384</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.06988534966487836</v>
+        <v>-0.06988534966488746</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0553294412438885</v>
+        <v>0.05532944124457745</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.0004228048841445928</v>
+        <v>-0.0004228048841412851</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.3562371582647073</v>
+        <v>-0.3562371582674621</v>
       </c>
       <c r="AM23" t="n">
-        <v>-0.2795413986595134</v>
+        <v>-0.2795413986595507</v>
       </c>
       <c r="AN23" t="n">
-        <v>-0.386099679661811</v>
+        <v>-0.3860996796620384</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.06988534966487836</v>
+        <v>0.06988534966488746</v>
       </c>
       <c r="AP23" t="n">
-        <v>-0.0553294412438885</v>
+        <v>-0.05532944124457745</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.0004228048841445928</v>
+        <v>0.0004228048841412851</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.08639837168639986</v>
+        <v>-0.08639837168915587</v>
       </c>
       <c r="AS23" t="n">
-        <v>-0.2795413986595126</v>
+        <v>-0.279541398659549</v>
       </c>
     </row>
     <row r="24">
@@ -7061,112 +7061,112 @@
         <v>-81.45562862063582</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.009637448260274106</v>
+        <v>-0.009637448260284578</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.009637448260301185</v>
+        <v>-0.00963744826029103</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0100031811838515</v>
+        <v>0.01000318118385151</v>
       </c>
       <c r="M24" t="n">
-        <v>0.001196064788409722</v>
+        <v>0.00119606478840903</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.001196064788407717</v>
+        <v>-0.001196064788408546</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.054790642029308e-15</v>
+        <v>-6.310766232131836e-16</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.01030901918800909</v>
+        <v>-0.01030901918800026</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.00963419003515636</v>
+        <v>-0.009634190035146204</v>
       </c>
       <c r="R24" t="n">
-        <v>-6.034816844260094e-06</v>
+        <v>-6.034816844253537e-06</v>
       </c>
       <c r="S24" t="n">
-        <v>0.001439162794336123</v>
+        <v>0.001439162794335432</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0009979940318752018</v>
+        <v>-0.0009979940318746456</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.054355086044638e-15</v>
+        <v>-6.323352839555595e-16</v>
       </c>
       <c r="V24" t="n">
-        <v>0.009637448260301185</v>
+        <v>0.00963744826029103</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.009637448260274106</v>
+        <v>-0.009637448260284578</v>
       </c>
       <c r="X24" t="n">
-        <v>0.0100031811838515</v>
+        <v>0.01000318118385151</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.001196064788407717</v>
+        <v>0.001196064788408546</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.001196064788409722</v>
+        <v>0.00119606478840903</v>
       </c>
       <c r="AA24" t="n">
-        <v>-3.054790642029308e-15</v>
+        <v>-6.310766232131836e-16</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.00963419003515636</v>
+        <v>0.009634190035146204</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.01030901918800909</v>
+        <v>-0.01030901918800026</v>
       </c>
       <c r="AD24" t="n">
-        <v>-6.034816844260094e-06</v>
+        <v>-6.034816844253537e-06</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.0009979940318752018</v>
+        <v>0.0009979940318746456</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.001439162794336123</v>
+        <v>0.001439162794335432</v>
       </c>
       <c r="AG24" t="n">
-        <v>-3.054355086044638e-15</v>
+        <v>-6.323352839555595e-16</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.3860996796620384</v>
+        <v>0.386099679661811</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.06988534966487858</v>
+        <v>0.06988534966488746</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-0.05532944124555528</v>
+        <v>-0.05532944124497974</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.0004228048841367154</v>
+        <v>0.0004228048841396713</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.08639837169306763</v>
+        <v>0.0863983716907657</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.2795413986595152</v>
+        <v>0.2795413986595507</v>
       </c>
       <c r="AN24" t="n">
-        <v>-0.3860996796620384</v>
+        <v>-0.386099679661811</v>
       </c>
       <c r="AO24" t="n">
-        <v>-0.06988534966487858</v>
+        <v>-0.06988534966488746</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.05532944124555528</v>
+        <v>0.05532944124497974</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-0.0004228048841367154</v>
+        <v>-0.0004228048841396713</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.3562371582713735</v>
+        <v>0.3562371582690712</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.2795413986595152</v>
+        <v>0.2795413986595481</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.258225144823698e-06</v>
+        <v>-3.258225144825433e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.072781431029623e-07</v>
+        <v>-4.072781431031791e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3860996796616082</v>
+        <v>-0.3860996796618138</v>
       </c>
       <c r="I25" t="n">
-        <v>-81.45562862059245</v>
+        <v>-81.45562862063582</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.01030901918800909</v>
+        <v>-0.01030901918800026</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.00963419003515636</v>
+        <v>-0.009634190035146204</v>
       </c>
       <c r="L25" t="n">
-        <v>-6.034816844260094e-06</v>
+        <v>-6.034816844253537e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>0.001439162794336123</v>
+        <v>0.001439162794335432</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0009979940318752018</v>
+        <v>-0.0009979940318746456</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.054355086044638e-15</v>
+        <v>-6.323352839555595e-16</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01030576096286427</v>
+        <v>-0.01030576096285544</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.01030576096284246</v>
+        <v>-0.01030576096285178</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.009991111550163006</v>
+        <v>-0.009991111550163018</v>
       </c>
       <c r="S25" t="n">
-        <v>0.00124109203779992</v>
+        <v>0.001241092037800776</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.001241092037801604</v>
+        <v>-0.001241092037801047</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.055103843794704e-15</v>
+        <v>-6.320011768432583e-16</v>
       </c>
       <c r="V25" t="n">
-        <v>0.01030901918800909</v>
+        <v>0.01030901918800026</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.00963419003515636</v>
+        <v>-0.009634190035146204</v>
       </c>
       <c r="X25" t="n">
-        <v>6.034816844260094e-06</v>
+        <v>6.034816844253537e-06</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.001439162794336123</v>
+        <v>-0.001439162794335432</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.0009979940318752018</v>
+        <v>-0.0009979940318746456</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.054355086044638e-15</v>
+        <v>6.323352839555595e-16</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.01030576096286427</v>
+        <v>0.01030576096285544</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.01030576096284246</v>
+        <v>-0.01030576096285178</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.009991111550163006</v>
+        <v>0.009991111550163018</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.00124109203779992</v>
+        <v>-0.001241092037800776</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.001241092037801604</v>
+        <v>-0.001241092037801047</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.055103843794704e-15</v>
+        <v>6.320011768432583e-16</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.3860996796615837</v>
+        <v>0.386099679661811</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.06988534966487814</v>
+        <v>0.06988534966488746</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-0.1070524710580115</v>
+        <v>-0.1070524710584768</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.0004228048841445884</v>
+        <v>-0.0004228048841412838</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.5631292775211996</v>
+        <v>0.563129277523061</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.2795413986595117</v>
+        <v>0.2795413986595507</v>
       </c>
       <c r="AN25" t="n">
-        <v>-0.3860996796615837</v>
+        <v>-0.386099679661811</v>
       </c>
       <c r="AO25" t="n">
-        <v>-0.06988534966487814</v>
+        <v>-0.06988534966488746</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.1070524710580115</v>
+        <v>0.1070524710584768</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.0004228048841445884</v>
+        <v>0.0004228048841412838</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.2932904909428933</v>
+        <v>0.2932904909447553</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.2795413986595126</v>
+        <v>0.2795413986595499</v>
       </c>
     </row>
     <row r="26">
@@ -7339,112 +7339,112 @@
         <v>17.30173732009815</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.01737007367944867</v>
+        <v>-0.01737007367943667</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.01737007367941414</v>
+        <v>-0.0173700736794309</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.009990938226026575</v>
+        <v>-0.009990938226026593</v>
       </c>
       <c r="M26" t="n">
-        <v>0.001204350062740928</v>
+        <v>0.001204350062741668</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.001204350062742015</v>
+        <v>-0.001204350062741899</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.803761237550783e-15</v>
+        <v>-1.012366336751686e-15</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01735361784199784</v>
+        <v>-0.01735361784201489</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.01736938160992134</v>
+        <v>-0.01736938160993809</v>
       </c>
       <c r="R26" t="n">
-        <v>-6.146923437967343e-06</v>
+        <v>-6.146923437965993e-06</v>
       </c>
       <c r="S26" t="n">
-        <v>0.00125937918302127</v>
+        <v>0.001259379183022008</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.00123006073370777</v>
+        <v>-0.001230060733708419</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.803892303683812e-15</v>
+        <v>-1.012110102286476e-15</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.01737007367941414</v>
+        <v>-0.0173700736794309</v>
       </c>
       <c r="W26" t="n">
-        <v>0.01737007367944867</v>
+        <v>0.01737007367943667</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.009990938226026575</v>
+        <v>-0.009990938226026593</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.001204350062742015</v>
+        <v>-0.001204350062741899</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.001204350062740928</v>
+        <v>-0.001204350062741668</v>
       </c>
       <c r="AA26" t="n">
-        <v>-4.803761237550783e-15</v>
+        <v>-1.012366336751686e-15</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.01736938160992134</v>
+        <v>-0.01736938160993809</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.01735361784199784</v>
+        <v>0.01735361784201489</v>
       </c>
       <c r="AD26" t="n">
-        <v>-6.146923437967343e-06</v>
+        <v>-6.146923437965993e-06</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.00123006073370777</v>
+        <v>-0.001230060733708419</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.00125937918302127</v>
+        <v>-0.001259379183022008</v>
       </c>
       <c r="AG26" t="n">
-        <v>-4.803892303683812e-15</v>
+        <v>-1.012110102286476e-15</v>
       </c>
       <c r="AH26" t="n">
         <v>-0.08201023489709769</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.001712435580727645</v>
+        <v>0.001712435580860427</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-0.01351504637711198</v>
+        <v>-0.01351504637649903</v>
       </c>
       <c r="AK26" t="n">
-        <v>5.488239379228569e-05</v>
+        <v>5.488239379391937e-05</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.08460134726403878</v>
+        <v>0.08460134726158497</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.006849742322909691</v>
+        <v>0.00684974232344171</v>
       </c>
       <c r="AN26" t="n">
         <v>0.08201023489709769</v>
       </c>
       <c r="AO26" t="n">
-        <v>-0.001712435580727645</v>
+        <v>-0.001712435580860427</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.01351504637711198</v>
+        <v>0.01351504637649903</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-5.488239379228569e-05</v>
+        <v>-5.488239379391937e-05</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.02351902375285864</v>
+        <v>0.02351902375040749</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.006849742322910579</v>
+        <v>0.00684974232344171</v>
       </c>
     </row>
     <row r="27">
@@ -7478,112 +7478,112 @@
         <v>17.30173732001142</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.01735361784199784</v>
+        <v>-0.01735361784201489</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.01736938160992134</v>
+        <v>-0.01736938160993809</v>
       </c>
       <c r="L27" t="n">
-        <v>-6.146923437967343e-06</v>
+        <v>-6.146923437965993e-06</v>
       </c>
       <c r="M27" t="n">
-        <v>0.00125937918302127</v>
+        <v>0.001259379183022008</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.00123006073370777</v>
+        <v>-0.001230060733708419</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.803892303683812e-15</v>
+        <v>-1.012110102286476e-15</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.01735292577250504</v>
+        <v>-0.01735292577252209</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.01735292577254737</v>
+        <v>-0.01735292577253253</v>
       </c>
       <c r="R27" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="S27" t="n">
-        <v>0.001285089853989626</v>
+        <v>0.001285089853989261</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.001285089853988111</v>
+        <v>-0.001285089853988761</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.803309957801465e-15</v>
+        <v>-1.012571952175807e-15</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.01735361784199784</v>
+        <v>-0.01735361784201489</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.01736938160992134</v>
+        <v>-0.01736938160993809</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.146923437967343e-06</v>
+        <v>-6.146923437965993e-06</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.00125937918302127</v>
+        <v>0.001259379183022008</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.00123006073370777</v>
+        <v>-0.001230060733708419</v>
       </c>
       <c r="AA27" t="n">
-        <v>-4.803892303683812e-15</v>
+        <v>-1.012110102286476e-15</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.01735292577250504</v>
+        <v>-0.01735292577252209</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.01735292577254737</v>
+        <v>-0.01735292577253253</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.001285089853989626</v>
+        <v>0.001285089853989261</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001285089853988111</v>
+        <v>-0.001285089853988761</v>
       </c>
       <c r="AG27" t="n">
-        <v>-4.803309957801465e-15</v>
+        <v>-1.012571952175807e-15</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.08201023489709769</v>
+        <v>-0.08201023489664294</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.001712435580726535</v>
+        <v>-0.001712435580859539</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.005330430321729085</v>
+        <v>0.005330430322269208</v>
       </c>
       <c r="AK27" t="n">
-        <v>-5.488239379783637e-05</v>
+        <v>-5.488239379548322e-05</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.009219440468673401</v>
+        <v>0.009219440466513129</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0.006849742322907026</v>
+        <v>-0.006849742323438157</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.08201023489709769</v>
+        <v>0.08201023489664294</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.001712435580726535</v>
+        <v>0.001712435580859539</v>
       </c>
       <c r="AP27" t="n">
-        <v>-0.005330430321729085</v>
+        <v>-0.005330430322269208</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.488239379783637e-05</v>
+        <v>5.488239379548322e-05</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.05186288304250564</v>
+        <v>-0.05186288304466569</v>
       </c>
       <c r="AS27" t="n">
-        <v>-0.006849742322907026</v>
+        <v>-0.006849742323439045</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>6.920694928073956e-07</v>
+        <v>6.920694928039262e-07</v>
       </c>
       <c r="G28" t="n">
-        <v>8.650868660092445e-08</v>
+        <v>8.650868660049077e-08</v>
       </c>
       <c r="H28" t="n">
-        <v>0.08201023489767638</v>
+        <v>0.08201023489726525</v>
       </c>
       <c r="I28" t="n">
-        <v>17.30173732018489</v>
+        <v>17.30173732009815</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.01735292577250504</v>
+        <v>-0.01735292577252209</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.01735292577254737</v>
+        <v>-0.01735292577253253</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="M28" t="n">
-        <v>0.001285089853989626</v>
+        <v>0.001285089853989261</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.001285089853988111</v>
+        <v>-0.001285089853988761</v>
       </c>
       <c r="O28" t="n">
-        <v>-4.803309957801465e-15</v>
+        <v>-1.012571952175807e-15</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.01736938160995587</v>
+        <v>-0.01736938160994386</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.01735361784204018</v>
+        <v>-0.01735361784202533</v>
       </c>
       <c r="R28" t="n">
-        <v>-6.146923437985668e-06</v>
+        <v>-6.146923437976757e-06</v>
       </c>
       <c r="S28" t="n">
-        <v>0.001230060733709285</v>
+        <v>0.001230060733708922</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.001259379183022356</v>
+        <v>-0.001259379183022239</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.804447417211208e-15</v>
+        <v>-1.013382782898572e-15</v>
       </c>
       <c r="V28" t="n">
-        <v>0.01735292577254737</v>
+        <v>0.01735292577253253</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.01735292577250504</v>
+        <v>-0.01735292577252209</v>
       </c>
       <c r="X28" t="n">
-        <v>0.01000323207290251</v>
+        <v>0.01000323207290252</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.001285089853988111</v>
+        <v>0.001285089853988761</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.001285089853989626</v>
+        <v>0.001285089853989261</v>
       </c>
       <c r="AA28" t="n">
-        <v>-4.803309957801465e-15</v>
+        <v>-1.012571952175807e-15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.01735361784204018</v>
+        <v>0.01735361784202533</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.01736938160995587</v>
+        <v>-0.01736938160994386</v>
       </c>
       <c r="AD28" t="n">
-        <v>-6.146923437985668e-06</v>
+        <v>-6.146923437976757e-06</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.001259379183022356</v>
+        <v>0.001259379183022239</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.001230060733709285</v>
+        <v>0.001230060733708922</v>
       </c>
       <c r="AG28" t="n">
-        <v>-4.804447417211208e-15</v>
+        <v>-1.013382782898572e-15</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.08201023489755244</v>
+        <v>-0.08201023489709769</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.001712435580726979</v>
+        <v>0.001712435580859539</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0.005330430322988522</v>
+        <v>-0.005330430322685431</v>
       </c>
       <c r="AK28" t="n">
-        <v>5.488239379228569e-05</v>
+        <v>5.488239379392197e-05</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.05186288304754272</v>
+        <v>0.05186288304632969</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.006849742322908803</v>
+        <v>0.006849742323439045</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.08201023489755244</v>
+        <v>0.08201023489709769</v>
       </c>
       <c r="AO28" t="n">
-        <v>-0.001712435580726979</v>
+        <v>-0.001712435580859539</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.005330430322988522</v>
+        <v>0.005330430322685431</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-5.488239379228569e-05</v>
+        <v>-5.488239379392197e-05</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.009219440463635209</v>
+        <v>-0.009219440464847573</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.006849742322907026</v>
+        <v>0.006849742323438157</v>
       </c>
     </row>
     <row r="29">
@@ -7756,112 +7756,112 @@
         <v>17.30173732009815</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.01736938160995587</v>
+        <v>-0.01736938160994386</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.01735361784204018</v>
+        <v>-0.01735361784202533</v>
       </c>
       <c r="L29" t="n">
-        <v>-6.146923437985668e-06</v>
+        <v>-6.146923437976757e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>0.001230060733709285</v>
+        <v>0.001230060733708922</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.001259379183022356</v>
+        <v>-0.001259379183022239</v>
       </c>
       <c r="O29" t="n">
-        <v>-4.804447417211208e-15</v>
+        <v>-1.013382782898572e-15</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.01737007367944867</v>
+        <v>-0.01737007367943667</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.01737007367941414</v>
+        <v>-0.0173700736794309</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.009990938226026575</v>
+        <v>-0.009990938226026593</v>
       </c>
       <c r="S29" t="n">
-        <v>0.001204350062740928</v>
+        <v>0.001204350062741668</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.001204350062742015</v>
+        <v>-0.001204350062741899</v>
       </c>
       <c r="U29" t="n">
-        <v>-4.803761237550783e-15</v>
+        <v>-1.012366336751686e-15</v>
       </c>
       <c r="V29" t="n">
-        <v>0.01736938160995587</v>
+        <v>0.01736938160994386</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.01735361784204018</v>
+        <v>-0.01735361784202533</v>
       </c>
       <c r="X29" t="n">
-        <v>6.146923437985668e-06</v>
+        <v>6.146923437976757e-06</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.001230060733709285</v>
+        <v>-0.001230060733708922</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.001259379183022356</v>
+        <v>-0.001259379183022239</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.804447417211208e-15</v>
+        <v>1.013382782898572e-15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.01737007367944867</v>
+        <v>0.01737007367943667</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.01737007367941414</v>
+        <v>-0.0173700736794309</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009990938226026575</v>
+        <v>0.009990938226026593</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.001204350062740928</v>
+        <v>-0.001204350062741668</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001204350062742015</v>
+        <v>-0.001204350062741899</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.803761237550783e-15</v>
+        <v>1.012366336751686e-15</v>
       </c>
       <c r="AH29" t="n">
         <v>-0.08201023489755244</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.001712435580726979</v>
+        <v>0.001712435580860205</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-0.01351504637620604</v>
+        <v>-0.01351504637630585</v>
       </c>
       <c r="AK29" t="n">
-        <v>-5.488239379784028e-05</v>
+        <v>-5.488239379548366e-05</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.02351902374923509</v>
+        <v>0.02351902374963499</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.006849742322907915</v>
+        <v>0.006849742323440822</v>
       </c>
       <c r="AN29" t="n">
         <v>0.08201023489755244</v>
       </c>
       <c r="AO29" t="n">
-        <v>-0.001712435580726979</v>
+        <v>-0.001712435580860205</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.01351504637620604</v>
+        <v>0.01351504637630585</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.488239379784028e-05</v>
+        <v>5.488239379548366e-05</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.08460134726041391</v>
+        <v>0.08460134726081225</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.006849742322907026</v>
+        <v>0.006849742323439045</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.089616051830333e-07</v>
+        <v>-1.089616051795639e-07</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.362020064787917e-08</v>
+        <v>-1.362020064744549e-08</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.01291195021418945</v>
+        <v>-0.01291195021377832</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.724040129575833</v>
+        <v>-2.724040129489097</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.02482398266159128</v>
+        <v>-0.02482398266158013</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0248239826615519</v>
+        <v>-0.02482398266157276</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.009990935978426553</v>
+        <v>-0.009990935978426577</v>
       </c>
       <c r="M30" t="n">
-        <v>0.001257818715765292</v>
+        <v>0.001257818715765601</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.001257818715765604</v>
+        <v>-0.001257818715765732</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.674836422945595e-15</v>
+        <v>-1.358705779577601e-15</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.02485967309713104</v>
+        <v>-0.02485967309715188</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.02482409162315708</v>
+        <v>-0.02482409162317794</v>
       </c>
       <c r="R30" t="n">
-        <v>-6.139754862708566e-06</v>
+        <v>-6.139754862707143e-06</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001237953768590255</v>
+        <v>0.001237953768590565</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.001259528070805193</v>
+        <v>-0.001259528070805485</v>
       </c>
       <c r="U30" t="n">
-        <v>-5.67899907152334e-15</v>
+        <v>-1.357769995309901e-15</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.0248239826615519</v>
+        <v>-0.02482398266157276</v>
       </c>
       <c r="W30" t="n">
-        <v>0.02482398266159128</v>
+        <v>0.02482398266158013</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.009990935978426553</v>
+        <v>-0.009990935978426577</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.001257818715765604</v>
+        <v>-0.001257818715765732</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.001257818715765292</v>
+        <v>-0.001257818715765601</v>
       </c>
       <c r="AA30" t="n">
-        <v>-5.674836422945595e-15</v>
+        <v>-1.358705779577601e-15</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.02482409162315708</v>
+        <v>-0.02482409162317794</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.02485967309713104</v>
+        <v>0.02485967309715188</v>
       </c>
       <c r="AD30" t="n">
-        <v>-6.139754862708566e-06</v>
+        <v>-6.139754862707143e-06</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.001259528070805193</v>
+        <v>-0.001259528070805485</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.001237953768590255</v>
+        <v>-0.001237953768590565</v>
       </c>
       <c r="AG30" t="n">
-        <v>-5.67899907152334e-15</v>
+        <v>-1.357769995309901e-15</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.01291195021440217</v>
+        <v>0.01291195021349267</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.003714035953082284</v>
+        <v>-0.003714035952816719</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0.0001775604016159837</v>
+        <v>-0.0001775604013612986</v>
       </c>
       <c r="AK30" t="n">
-        <v>3.648815565276964e-06</v>
+        <v>3.648815565626944e-06</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.01031480407568131</v>
+        <v>-0.01031480407669871</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.01485614381232736</v>
+        <v>-0.0148561438112651</v>
       </c>
       <c r="AN30" t="n">
-        <v>-0.01291195021440217</v>
+        <v>-0.01291195021349267</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.003714035953082284</v>
+        <v>0.003714035952816719</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.0001775604016159837</v>
+        <v>0.0001775604013612986</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-3.648815565276964e-06</v>
+        <v>-3.648815565626944e-06</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.01173528728861006</v>
+        <v>0.01173528728759021</v>
       </c>
       <c r="AS30" t="n">
-        <v>-0.01485614381233091</v>
+        <v>-0.0148561438112651</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.089616051795639e-07</v>
+        <v>-1.089616051760944e-07</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.362020064744549e-08</v>
+        <v>-1.36202006470118e-08</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.01291195021377832</v>
+        <v>-0.01291195021336719</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.724040129489097</v>
+        <v>-2.724040129402361</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.02485967309713104</v>
+        <v>-0.02485967309715188</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.02482409162315708</v>
+        <v>-0.02482409162317794</v>
       </c>
       <c r="L31" t="n">
-        <v>-6.139754862708566e-06</v>
+        <v>-6.139754862707143e-06</v>
       </c>
       <c r="M31" t="n">
-        <v>0.001237953768590255</v>
+        <v>0.001237953768590565</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.001259528070805193</v>
+        <v>-0.001259528070805485</v>
       </c>
       <c r="O31" t="n">
-        <v>-5.67899907152334e-15</v>
+        <v>-1.357769995309901e-15</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="R31" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001239663123630873</v>
+        <v>0.001239663123630794</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.001239663123630155</v>
+        <v>-0.001239663123630448</v>
       </c>
       <c r="U31" t="n">
-        <v>-5.676397154560981e-15</v>
+        <v>-1.357742617260905e-15</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.02485967309713104</v>
+        <v>-0.02485967309715188</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.02482409162315708</v>
+        <v>-0.02482409162317794</v>
       </c>
       <c r="X31" t="n">
-        <v>-6.139754862708566e-06</v>
+        <v>-6.139754862707143e-06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.001237953768590255</v>
+        <v>0.001237953768590565</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.001259528070805193</v>
+        <v>-0.001259528070805485</v>
       </c>
       <c r="AA31" t="n">
-        <v>-5.67899907152334e-15</v>
+        <v>-1.357769995309901e-15</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.001239663123630873</v>
+        <v>0.001239663123630794</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001239663123630155</v>
+        <v>-0.001239663123630448</v>
       </c>
       <c r="AG31" t="n">
-        <v>-5.676397154560981e-15</v>
+        <v>-1.357742617260905e-15</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.01291195021394742</v>
+        <v>0.01291195021349267</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.003714035953081396</v>
+        <v>0.003714035952815387</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-0.001310195292502869</v>
+        <v>-0.001310195292259397</v>
       </c>
       <c r="AK31" t="n">
-        <v>-3.648815567473124e-06</v>
+        <v>-3.648815566643059e-06</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.005784264512133763</v>
+        <v>-0.005784264513107429</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.01485614381232558</v>
+        <v>0.01485614381126332</v>
       </c>
       <c r="AN31" t="n">
-        <v>-0.01291195021394742</v>
+        <v>-0.01291195021349267</v>
       </c>
       <c r="AO31" t="n">
-        <v>-0.003714035953081396</v>
+        <v>-0.003714035952815387</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.001310195292502869</v>
+        <v>0.001310195292259397</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.648815567473124e-06</v>
+        <v>3.648815566643059e-06</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.01626582685215805</v>
+        <v>0.01626582685118416</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.01485614381232736</v>
+        <v>0.01485614381126332</v>
       </c>
     </row>
     <row r="32">
@@ -8161,124 +8161,124 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.089616051760944e-07</v>
+        <v>-1.089616051691555e-07</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.36202006470118e-08</v>
+        <v>-1.362020064614444e-08</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.01291195021336719</v>
+        <v>-0.01291195021254493</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.724040129402361</v>
+        <v>-2.724040129228888</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.02485978205878767</v>
+        <v>-0.02485978205877142</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
       <c r="M32" t="n">
-        <v>0.001239663123630873</v>
+        <v>0.001239663123630794</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.001239663123630155</v>
+        <v>-0.001239663123630448</v>
       </c>
       <c r="O32" t="n">
-        <v>-5.676397154560981e-15</v>
+        <v>-1.357742617260905e-15</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.02482409162319647</v>
+        <v>-0.0248240916231853</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.0248596730971825</v>
+        <v>-0.02485967309716625</v>
       </c>
       <c r="R32" t="n">
-        <v>-6.139754862729007e-06</v>
+        <v>-6.139754862719022e-06</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001259528070805909</v>
+        <v>0.00125952807080583</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.001237953768590568</v>
+        <v>-0.001237953768590698</v>
       </c>
       <c r="U32" t="n">
-        <v>-5.677821559011737e-15</v>
+        <v>-1.357962856859783e-15</v>
       </c>
       <c r="V32" t="n">
-        <v>0.02485978205878767</v>
+        <v>0.02485978205877142</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.02485978205873622</v>
+        <v>-0.02485978205875706</v>
       </c>
       <c r="X32" t="n">
-        <v>0.01000321548815198</v>
+        <v>0.01000321548815199</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.001239663123630155</v>
+        <v>0.001239663123630448</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.001239663123630873</v>
+        <v>0.001239663123630794</v>
       </c>
       <c r="AA32" t="n">
-        <v>-5.676397154560981e-15</v>
+        <v>-1.357742617260905e-15</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.0248596730971825</v>
+        <v>0.02485967309716625</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.02482409162319647</v>
+        <v>-0.0248240916231853</v>
       </c>
       <c r="AD32" t="n">
-        <v>-6.139754862729007e-06</v>
+        <v>-6.139754862719022e-06</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.001237953768590568</v>
+        <v>0.001237953768590698</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.001259528070805909</v>
+        <v>0.00125952807080583</v>
       </c>
       <c r="AG32" t="n">
-        <v>-5.677821559011737e-15</v>
+        <v>-1.357962856859783e-15</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.01291195021349267</v>
+        <v>0.01291195021258318</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.003714035953082284</v>
+        <v>-0.003714035952815831</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.00131019529190779</v>
+        <v>0.001310195291973071</v>
       </c>
       <c r="AK32" t="n">
-        <v>3.648815565272193e-06</v>
+        <v>3.648815565620439e-06</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.01626582684977684</v>
+        <v>-0.01626582685003797</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.01485614381232736</v>
+        <v>-0.01485614381126332</v>
       </c>
       <c r="AN32" t="n">
-        <v>-0.01291195021349267</v>
+        <v>-0.01291195021258318</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.003714035953082284</v>
+        <v>0.003714035952815831</v>
       </c>
       <c r="AP32" t="n">
-        <v>-0.00131019529190779</v>
+        <v>-0.001310195291973071</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-3.648815565272193e-06</v>
+        <v>-3.648815565620439e-06</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.005784264514513193</v>
+        <v>0.005784264514252069</v>
       </c>
       <c r="AS32" t="n">
-        <v>-0.01485614381232914</v>
+        <v>-0.01485614381126155</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.089616051830333e-07</v>
+        <v>-1.089616051795639e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.362020064787917e-08</v>
+        <v>-1.362020064744549e-08</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.01291195021418945</v>
+        <v>-0.01291195021377832</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.724040129575833</v>
+        <v>-2.724040129489097</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.02482409162319647</v>
+        <v>-0.0248240916231853</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0248596730971825</v>
+        <v>-0.02485967309716625</v>
       </c>
       <c r="L33" t="n">
-        <v>-6.139754862729007e-06</v>
+        <v>-6.139754862719022e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>0.001259528070805909</v>
+        <v>0.00125952807080583</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.001237953768590568</v>
+        <v>-0.001237953768590698</v>
       </c>
       <c r="O33" t="n">
-        <v>-5.677821559011737e-15</v>
+        <v>-1.357962856859783e-15</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.02482398266159128</v>
+        <v>-0.02482398266158013</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.0248239826615519</v>
+        <v>-0.02482398266157276</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.009990935978426553</v>
+        <v>-0.009990935978426577</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001257818715765292</v>
+        <v>0.001257818715765601</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.001257818715765604</v>
+        <v>-0.001257818715765732</v>
       </c>
       <c r="U33" t="n">
-        <v>-5.674836422945595e-15</v>
+        <v>-1.358705779577601e-15</v>
       </c>
       <c r="V33" t="n">
-        <v>0.02482409162319647</v>
+        <v>0.0248240916231853</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.0248596730971825</v>
+        <v>-0.02485967309716625</v>
       </c>
       <c r="X33" t="n">
-        <v>6.139754862729007e-06</v>
+        <v>6.139754862719022e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.001259528070805909</v>
+        <v>-0.00125952807080583</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.001237953768590568</v>
+        <v>-0.001237953768590698</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.677821559011737e-15</v>
+        <v>1.357962856859783e-15</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.02482398266159128</v>
+        <v>0.02482398266158013</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.0248239826615519</v>
+        <v>-0.02482398266157276</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.009990935978426553</v>
+        <v>0.009990935978426577</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.001257818715765292</v>
+        <v>-0.001257818715765601</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001257818715765604</v>
+        <v>-0.001257818715765732</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.674836422945595e-15</v>
+        <v>1.358705779577601e-15</v>
       </c>
       <c r="AH33" t="n">
         <v>0.01291195021394742</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.003714035953083616</v>
+        <v>-0.003714035952815831</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.0001775604013539711</v>
+        <v>-0.0001775604012499432</v>
       </c>
       <c r="AK33" t="n">
-        <v>-3.648815567470955e-06</v>
+        <v>-3.648815566643926e-06</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.01173528728756135</v>
+        <v>0.01173528728714435</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.01485614381233269</v>
+        <v>-0.0148561438112651</v>
       </c>
       <c r="AN33" t="n">
         <v>-0.01291195021394742</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.003714035953083616</v>
+        <v>0.003714035952815831</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.0001775604013539711</v>
+        <v>0.0001775604012499432</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.648815567470955e-06</v>
+        <v>3.648815566643926e-06</v>
       </c>
       <c r="AR33" t="n">
-        <v>-0.01031480407672802</v>
+        <v>-0.01031480407714414</v>
       </c>
       <c r="AS33" t="n">
-        <v>-0.01485614381233624</v>
+        <v>-0.01485614381126332</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validation_frame_supp_disp.xlsx
+++ b/outputs/validation_frame_supp_disp.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005143544436265349</v>
+        <v>-0.005143544436268916</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.005143544436263927</v>
+        <v>-0.005143544436260579</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.009992639968869803</v>
+        <v>-0.009992639968869796</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001430013372534397</v>
+        <v>0.0001430013372528314</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0001430013372536887</v>
+        <v>-0.0001430013372543053</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.459828480256998e-16</v>
+        <v>-1.1816844298607e-15</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01235981198413277</v>
+        <v>0.01235981198413286</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.001181950344900396</v>
+        <v>-0.001181950344896417</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.005133919027353872</v>
+        <v>-0.005133919027350523</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001247154414832138</v>
+        <v>0.00124715441483153</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0008581353759201137</v>
+        <v>-0.0008581353759194087</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.45867092239527e-16</v>
+        <v>-1.181563932377305e-15</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005268221251810945</v>
+        <v>0.005268221251806789</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001172324935990341</v>
+        <v>-0.001172324935986361</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001172324935992853</v>
+        <v>-0.001172324935996923</v>
       </c>
       <c r="G8" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00196228845349925</v>
+        <v>0.001962288453499951</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001962288453498811</v>
+        <v>-0.001962288453498106</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.459196944341733e-16</v>
+        <v>-1.18166403535008e-15</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01013890013059341</v>
+        <v>0.01013890013059342</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.005133919027355294</v>
+        <v>-0.005133919027358861</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.001181950344902908</v>
+        <v>-0.001181950344906979</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0008581353759205526</v>
+        <v>0.000858135375921254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.001247154414832387</v>
+        <v>-0.001247154414833003</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.45883799833235e-16</v>
+        <v>-1.18139457602318e-15</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005268221251812895</v>
+        <v>0.005268221251817284</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01030576096285544</v>
+        <v>-0.01030576096286427</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01030576096285178</v>
+        <v>-0.01030576096284246</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.009991111550163018</v>
+        <v>-0.009991111550163006</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001241092037800776</v>
+        <v>0.00124109203779992</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.001241092037801047</v>
+        <v>-0.001241092037801604</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.320011768432583e-16</v>
+        <v>-3.055103843794704e-15</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0176703063939128</v>
+        <v>0.01767030639391251</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.009634190035139751</v>
+        <v>-0.009634190035129281</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0103090191879966</v>
+        <v>-0.01030901918798729</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.034816844245296e-06</v>
+        <v>-6.034816844246121e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009979940318743741</v>
+        <v>0.0009979940318735161</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.001439162794334948</v>
+        <v>-0.00143916279433412</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.325385275155652e-16</v>
+        <v>-3.05495934852082e-15</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0141100506969565</v>
+        <v>0.01411005069694254</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.009637448260284578</v>
+        <v>-0.009637448260274106</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.00963744826029103</v>
+        <v>-0.009637448260301185</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01000318118385151</v>
+        <v>0.0100031811838515</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00119606478840903</v>
+        <v>0.001196064788409722</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.001196064788408546</v>
+        <v>-0.001196064788407717</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.310766232131836e-16</v>
+        <v>-3.054790642029308e-15</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01690634353538368</v>
+        <v>0.0169063435353835</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01030901918800026</v>
+        <v>-0.01030901918800909</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.009634190035146204</v>
+        <v>-0.00963419003515636</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.034816844253537e-06</v>
+        <v>-6.034816844260094e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001439162794335432</v>
+        <v>0.001439162794336123</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0009979940318746456</v>
+        <v>-0.0009979940318752018</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.323352839555595e-16</v>
+        <v>-3.054355086044638e-15</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01411005069696358</v>
+        <v>0.01411005069697696</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01737007367943667</v>
+        <v>-0.01737007367944867</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0173700736794309</v>
+        <v>-0.01737007367941414</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.009990938226026593</v>
+        <v>-0.009990938226026575</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001204350062741668</v>
+        <v>0.001204350062740928</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.001204350062741899</v>
+        <v>-0.001204350062742015</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.012366336751686e-15</v>
+        <v>-4.803761237550783e-15</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02651900763403857</v>
+        <v>0.02651900763403545</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01735361784201489</v>
+        <v>-0.01735361784199784</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01736938160993809</v>
+        <v>-0.01736938160992134</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.146923437965993e-06</v>
+        <v>-6.146923437967343e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001259379183022008</v>
+        <v>0.00125937918302127</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.001230060733708419</v>
+        <v>-0.00123006073370777</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.012110102286476e-15</v>
+        <v>-4.803892303683812e-15</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02455287167528518</v>
+        <v>0.02455287167526127</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01735292577252209</v>
+        <v>-0.01735292577250504</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01735292577253253</v>
+        <v>-0.01735292577254737</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001285089853989261</v>
+        <v>0.001285089853989626</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.001285089853988761</v>
+        <v>-0.001285089853988111</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.012571952175807e-15</v>
+        <v>-4.803309957801465e-15</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02650118332524098</v>
+        <v>0.02650118332523954</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01736938160994386</v>
+        <v>-0.01736938160995587</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.01735361784202533</v>
+        <v>-0.01735361784204018</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.146923437976757e-06</v>
+        <v>-6.146923437985668e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001230060733708922</v>
+        <v>0.001230060733709285</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.001259379183022239</v>
+        <v>-0.001259379183022356</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.013382782898572e-15</v>
+        <v>-4.804447417211208e-15</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02455287167529663</v>
+        <v>0.02455287167531562</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.02482398266158013</v>
+        <v>-0.02482398266159128</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.02482398266157276</v>
+        <v>-0.0248239826615519</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.009990935978426577</v>
+        <v>-0.009990935978426553</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001257818715765601</v>
+        <v>0.001257818715765292</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.001257818715765732</v>
+        <v>-0.001257818715765604</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.358705779577601e-15</v>
+        <v>-5.674836422945595e-15</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03650039769768974</v>
+        <v>0.03650039769768313</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.02485967309715188</v>
+        <v>-0.02485967309713104</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.02482409162317794</v>
+        <v>-0.02482409162315708</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.139754862707143e-06</v>
+        <v>-6.139754862708566e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001237953768590565</v>
+        <v>0.001237953768590255</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.001259528070805485</v>
+        <v>-0.001259528070805193</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.357769995309901e-15</v>
+        <v>-5.67899907152334e-15</v>
       </c>
       <c r="K19" t="n">
-        <v>0.03513173649436901</v>
+        <v>0.03513173649433953</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001239663123630794</v>
+        <v>0.001239663123630873</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.001239663123630448</v>
+        <v>-0.001239663123630155</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.357742617260905e-15</v>
+        <v>-5.676397154560981e-15</v>
       </c>
       <c r="K20" t="n">
-        <v>0.03655245338032614</v>
+        <v>0.03655245338032303</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0248240916231853</v>
+        <v>-0.02482409162319647</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.02485967309716625</v>
+        <v>-0.0248596730971825</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.139754862719022e-06</v>
+        <v>-6.139754862729007e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00125952807080583</v>
+        <v>0.001259528070805909</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.001237953768590698</v>
+        <v>-0.001237953768590568</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.357962856859783e-15</v>
+        <v>-5.677821559011737e-15</v>
       </c>
       <c r="K21" t="n">
-        <v>0.03513173649438439</v>
+        <v>0.03513173649440377</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03655245338032614</v>
+        <v>0.03655245338032303</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
     </row>
     <row r="4">
@@ -1289,16 +1289,16 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
     </row>
     <row r="5">
@@ -1311,16 +1311,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01735292577252209</v>
+        <v>-0.01735292577250504</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01735292577253253</v>
+        <v>-0.01735292577254737</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.303746695288943</v>
+        <v>-1.30374669528852</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.30374669528911</v>
+        <v>-1.303746695289486</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.162884918571081</v>
+        <v>-1.162884918572217</v>
       </c>
       <c r="E2" t="n">
-        <v>3.805419096299786</v>
+        <v>3.805419096301363</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.805419096299101</v>
+        <v>-3.805419096297374</v>
       </c>
       <c r="G2" t="n">
-        <v>7.001050289962223e-16</v>
+        <v>3.363255684988146e-15</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.3434724264387863</v>
+        <v>-0.3434724264392463</v>
       </c>
       <c r="C3" t="n">
-        <v>0.343472426438173</v>
+        <v>0.3434724264377969</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7734063072796055</v>
+        <v>0.7734063072796302</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.953311546290301</v>
+        <v>-1.953311546288723</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3953971011354749</v>
+        <v>-0.3953971011373766</v>
       </c>
       <c r="G3" t="n">
-        <v>6.997755702201921e-16</v>
+        <v>3.362912730612329e-15</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.303746695288497</v>
+        <v>1.303746695288037</v>
       </c>
       <c r="C4" t="n">
-        <v>1.303746695288792</v>
+        <v>1.303746695289277</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3839276959881772</v>
+        <v>-0.3839276959879498</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.363333541455821</v>
+        <v>-5.363333541457796</v>
       </c>
       <c r="F4" t="n">
-        <v>5.363333541454612</v>
+        <v>5.36333354145271</v>
       </c>
       <c r="G4" t="n">
-        <v>6.999252841588009e-16</v>
+        <v>3.363197639073303e-15</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3434724264383396</v>
+        <v>0.3434724264387636</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3434724264384916</v>
+        <v>-0.3434724264380065</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7734063072803354</v>
+        <v>0.7734063072808883</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3953971011342658</v>
+        <v>0.3953971011322915</v>
       </c>
       <c r="F5" t="n">
-        <v>1.953311546290985</v>
+        <v>1.953311546292713</v>
       </c>
       <c r="G5" t="n">
-        <v>6.99823122602284e-16</v>
+        <v>3.362430716373665e-15</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>7.360031130197037e-06</v>
+        <v>7.360031130203976e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.226671855032839e-06</v>
+        <v>1.226671855033996e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.162884918571132</v>
+        <v>1.162884918572228</v>
       </c>
       <c r="I2" t="n">
-        <v>245.3343710065679</v>
+        <v>245.3343710067992</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.162884918571081</v>
+        <v>-1.162884918572217</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.30374669528911</v>
+        <v>-1.303746695289486</v>
       </c>
       <c r="L2" t="n">
-        <v>1.303746695288943</v>
+        <v>1.30374669528852</v>
       </c>
       <c r="M2" t="n">
-        <v>7.001050289962223e-16</v>
+        <v>3.363255684988146e-15</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.805419096299101</v>
+        <v>-3.805419096297374</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.805419096299785</v>
+        <v>-3.805419096301363</v>
       </c>
       <c r="P2" t="n">
-        <v>1.162884918571081</v>
+        <v>1.162884918572217</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.30374669528911</v>
+        <v>1.303746695289486</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.303746695288943</v>
+        <v>-1.30374669528852</v>
       </c>
       <c r="S2" t="n">
-        <v>-7.001050289962223e-16</v>
+        <v>-3.363255684988146e-15</v>
       </c>
       <c r="T2" t="n">
-        <v>-4.01706107543456</v>
+        <v>-4.017061075433746</v>
       </c>
       <c r="U2" t="n">
-        <v>-4.017061075434876</v>
+        <v>-4.017061075435553</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>-8.158294380586554e-07</v>
+        <v>-8.158294380586814e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7734063072796052</v>
+        <v>-0.77340630727963</v>
       </c>
       <c r="I3" t="n">
-        <v>-163.1658876117311</v>
+        <v>-163.1658876117363</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7734063072796055</v>
+        <v>0.7734063072796302</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3434724264381729</v>
+        <v>0.3434724264377969</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3434724264387864</v>
+        <v>0.3434724264392463</v>
       </c>
       <c r="M3" t="n">
-        <v>6.997755702201921e-16</v>
+        <v>3.362912730612329e-15</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.395397101135475</v>
+        <v>-0.3953971011373766</v>
       </c>
       <c r="O3" t="n">
-        <v>1.953311546290301</v>
+        <v>1.953311546288723</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7734063072796055</v>
+        <v>-0.7734063072796302</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3434724264381729</v>
+        <v>-0.3434724264377969</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.3434724264387864</v>
+        <v>-0.3434724264392463</v>
       </c>
       <c r="S3" t="n">
-        <v>-6.997755702201921e-16</v>
+        <v>-3.362912730612329e-15</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.665437457497243</v>
+        <v>-1.665437457498101</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1075230123387366</v>
+        <v>0.1075230123380582</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>2.42992212650707e-06</v>
+        <v>2.429922126505335e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.049870210845116e-07</v>
+        <v>4.049870210842225e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.383927695988117</v>
+        <v>0.3839276959878429</v>
       </c>
       <c r="I4" t="n">
-        <v>80.99740421690232</v>
+        <v>80.9974042168445</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3839276959881772</v>
+        <v>-0.3839276959879498</v>
       </c>
       <c r="K4" t="n">
-        <v>1.303746695288792</v>
+        <v>1.303746695289277</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.303746695288497</v>
+        <v>-1.303746695288037</v>
       </c>
       <c r="M4" t="n">
-        <v>6.999252841588009e-16</v>
+        <v>3.363197639073303e-15</v>
       </c>
       <c r="N4" t="n">
-        <v>5.363333541454613</v>
+        <v>5.363333541452711</v>
       </c>
       <c r="O4" t="n">
-        <v>5.363333541455821</v>
+        <v>5.363333541457796</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3839276959881772</v>
+        <v>0.3839276959879498</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.303746695288792</v>
+        <v>-1.303746695289277</v>
       </c>
       <c r="R4" t="n">
-        <v>1.303746695288497</v>
+        <v>1.303746695288037</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.999252841588009e-16</v>
+        <v>-3.363197639073303e-15</v>
       </c>
       <c r="T4" t="n">
-        <v>2.459146630276371</v>
+        <v>2.459146630275513</v>
       </c>
       <c r="U4" t="n">
-        <v>2.459146630276932</v>
+        <v>2.459146630277869</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.158294380594254e-07</v>
+        <v>-8.158294380600086e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7734063072803353</v>
+        <v>-0.7734063072808882</v>
       </c>
       <c r="I5" t="n">
-        <v>-163.1658876118851</v>
+        <v>-163.1658876120017</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7734063072803354</v>
+        <v>0.7734063072808883</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3434724264384916</v>
+        <v>-0.3434724264380065</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3434724264383395</v>
+        <v>-0.3434724264387636</v>
       </c>
       <c r="M5" t="n">
-        <v>6.99823122602284e-16</v>
+        <v>3.362430716373665e-15</v>
       </c>
       <c r="N5" t="n">
-        <v>1.953311546290985</v>
+        <v>1.953311546292713</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3953971011342658</v>
+        <v>-0.3953971011322915</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7734063072803354</v>
+        <v>-0.7734063072808883</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3434724264384916</v>
+        <v>0.3434724264380065</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3434724264383395</v>
+        <v>0.3434724264387636</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.99823122602284e-16</v>
+        <v>-3.362430716373665e-15</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1075230123390525</v>
+        <v>0.1075230123398683</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.665437457496684</v>
+        <v>-1.665437457495747</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.528418706785162e-06</v>
+        <v>1.528418706790366e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.547364511308603e-07</v>
+        <v>2.547364511317277e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2414901556720556</v>
+        <v>0.2414901556728778</v>
       </c>
       <c r="I6" t="n">
-        <v>50.94729022617206</v>
+        <v>50.94729022634553</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2414901556719542</v>
+        <v>-0.2414901556728637</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2491176456848834</v>
+        <v>0.2491176456844955</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2491176456850503</v>
+        <v>-0.2491176456854803</v>
       </c>
       <c r="M6" t="n">
-        <v>1.098667551249974e-15</v>
+        <v>5.332039870427548e-15</v>
       </c>
       <c r="N6" t="n">
-        <v>1.559940055460197</v>
+        <v>1.559940055461441</v>
       </c>
       <c r="O6" t="n">
-        <v>1.559940055459679</v>
+        <v>1.559940055458332</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2414901556719542</v>
+        <v>0.2414901556728637</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2491176456848834</v>
+        <v>-0.2491176456844955</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2491176456850503</v>
+        <v>0.2491176456854803</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.098667551249974e-15</v>
+        <v>-5.332039870427548e-15</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.06523418134989445</v>
+        <v>-0.06523418134856085</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06523418135037939</v>
+        <v>-0.06523418135135906</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.139840215893363e-06</v>
+        <v>-1.139840215894032e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.899733693155606e-07</v>
+        <v>-1.89973369315672e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1800947541111514</v>
+        <v>-0.180094754111257</v>
       </c>
       <c r="I7" t="n">
-        <v>-37.99467386311211</v>
+        <v>-37.99467386313439</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1800947541111514</v>
+        <v>0.180094754111257</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3848851442709451</v>
+        <v>-0.3848851442713319</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3848851442702956</v>
+        <v>-0.3848851442698287</v>
       </c>
       <c r="M7" t="n">
-        <v>1.100526392708724e-15</v>
+        <v>5.33197156902385e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.584615722437863</v>
+        <v>1.584615722436372</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.339034116201581</v>
+        <v>-1.339034116202926</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1800947541111514</v>
+        <v>-0.180094754111257</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3848851442709451</v>
+        <v>0.3848851442713319</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3848851442702956</v>
+        <v>0.3848851442698287</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.100526392708724e-15</v>
+        <v>-5.33197156902385e-15</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7246951431839088</v>
+        <v>0.7246951431825996</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9702767494240909</v>
+        <v>-0.9702767494250653</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>7.512617249995357e-07</v>
+        <v>7.512617249960662e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>1.252102874999226e-07</v>
+        <v>1.252102874993444e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1186993525499266</v>
+        <v>0.1186993525493785</v>
       </c>
       <c r="I8" t="n">
-        <v>25.04205749998452</v>
+        <v>25.04205749986887</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1186993525500384</v>
+        <v>-0.1186993525493563</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2491176456852433</v>
+        <v>-0.2491176456847733</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2491176456855322</v>
+        <v>0.2491176456859986</v>
       </c>
       <c r="M8" t="n">
-        <v>1.096215874217183e-15</v>
+        <v>5.331206495933188e-15</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.314358449223394</v>
+        <v>-1.314358449224885</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.314358449222493</v>
+        <v>-1.314358449221089</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1186993525500384</v>
+        <v>0.1186993525493563</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2491176456852433</v>
+        <v>0.2491176456847733</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.2491176456855322</v>
+        <v>-0.2491176456859986</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.096215874217183e-15</v>
+        <v>-5.331206495933188e-15</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1803474248898009</v>
+        <v>-0.1803474248911088</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1803474248889678</v>
+        <v>-0.1803474248875491</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.139840215896985e-06</v>
+        <v>-1.139840215900042e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.899733693161641e-07</v>
+        <v>-1.899733693166737e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1800947541117236</v>
+        <v>-0.1800947541122067</v>
       </c>
       <c r="I9" t="n">
-        <v>-37.99467386323282</v>
+        <v>-37.99467386333474</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1800947541117236</v>
+        <v>0.1800947541122068</v>
       </c>
       <c r="K9" t="n">
-        <v>0.384885144270585</v>
+        <v>0.3848851442710549</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3848851442707786</v>
+        <v>0.3848851442703483</v>
       </c>
       <c r="M9" t="n">
-        <v>1.099900377886616e-15</v>
+        <v>5.330733759291841e-15</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.339034116201065</v>
+        <v>-1.339034116199818</v>
       </c>
       <c r="O9" t="n">
-        <v>1.584615722438765</v>
+        <v>1.584615722440167</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1800947541117236</v>
+        <v>-0.1800947541122068</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.384885144270585</v>
+        <v>-0.3848851442710549</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.3848851442707786</v>
+        <v>-0.3848851442703483</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.099900377886616e-15</v>
+        <v>-5.330733759291841e-15</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9702767494236078</v>
+        <v>-0.9702767494222719</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7246951431847437</v>
+        <v>0.7246951431861609</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.733241364251792e-07</v>
+        <v>1.733241364303834e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>2.88873560708632e-08</v>
+        <v>2.888735607173056e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02738521355517831</v>
+        <v>0.02738521355600057</v>
       </c>
       <c r="I10" t="n">
-        <v>5.777471214172639</v>
+        <v>5.777471214346112</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.02738521355513512</v>
+        <v>-0.02738521355581724</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.06709668431189275</v>
+        <v>-0.06709668431254689</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06709668431174309</v>
+        <v>0.06709668431145799</v>
       </c>
       <c r="M10" t="n">
-        <v>1.082577762816293e-15</v>
+        <v>4.976947966844225e-15</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2284791144789988</v>
+        <v>-0.2284791144784704</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2284791144794198</v>
+        <v>-0.2284791144812948</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02738521355513512</v>
+        <v>0.02738521355581724</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.06709668431189275</v>
+        <v>0.06709668431254689</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.06709668431174309</v>
+        <v>-0.06709668431145799</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.082577762816293e-15</v>
+        <v>-4.976947966844225e-15</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1741009913914588</v>
+        <v>-0.1741009913902776</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1741009913919385</v>
+        <v>-0.1741009913939884</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.12106593720697e-07</v>
+        <v>-1.121065937212221e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.868443228678283e-08</v>
+        <v>-1.868443228687035e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01771284180787012</v>
+        <v>-0.0177128418079531</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.736886457356566</v>
+        <v>-3.736886457374071</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01771284180787014</v>
+        <v>0.01771284180795318</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0710998850555784</v>
+        <v>0.07109988505492337</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07109988505622278</v>
+        <v>0.07109988505675269</v>
       </c>
       <c r="M11" t="n">
-        <v>1.080319097424901e-15</v>
+        <v>4.977732257002361e-15</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.368035180032301</v>
+        <v>-0.3680351800337569</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4067246670159843</v>
+        <v>0.4067246670141085</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.01771284180787014</v>
+        <v>-0.01771284180795318</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.0710998850555784</v>
+        <v>-0.07109988505492337</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.07109988505622278</v>
+        <v>-0.07109988505675269</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.080319097424901e-15</v>
+        <v>-4.977732257002361e-15</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.05856413030504015</v>
+        <v>-0.05856413030676011</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01987464331748789</v>
+        <v>0.01987464331543176</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>5.08890510148019e-08</v>
+        <v>5.088905101306718e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>8.481508502466983e-09</v>
+        <v>8.481508502177862e-09</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0080404700603387</v>
+        <v>0.008040470060064614</v>
       </c>
       <c r="I12" t="n">
-        <v>1.696301700493397</v>
+        <v>1.696301700435572</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.008040470060223015</v>
+        <v>-0.008040470059995641</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06709668431150018</v>
+        <v>0.06709668431187632</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.06709668431124749</v>
+        <v>-0.06709668431071891</v>
       </c>
       <c r="M12" t="n">
-        <v>1.085794397816698e-15</v>
+        <v>4.976554975659214e-15</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2671686014630996</v>
+        <v>0.2671686014616472</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2671686014638706</v>
+        <v>0.267168601464757</v>
       </c>
       <c r="P12" t="n">
-        <v>0.008040470060223015</v>
+        <v>0.008040470059995641</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.06709668431150018</v>
+        <v>-0.06709668431187632</v>
       </c>
       <c r="R12" t="n">
-        <v>0.06709668431124749</v>
+        <v>0.06709668431071891</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.085794397816698e-15</v>
+        <v>-4.976554975659214e-15</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1354115044043827</v>
+        <v>0.1354115044026627</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1354115044051305</v>
+        <v>0.1354115044064992</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.121065937232203e-07</v>
+        <v>-1.121065937255742e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.868443228720338e-08</v>
+        <v>-1.86844322875957e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0177128418082688</v>
+        <v>-0.01771284180864072</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.736886457440675</v>
+        <v>-3.736886457519139</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01771284180826882</v>
+        <v>0.01771284180864063</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.07109988505597098</v>
+        <v>-0.07109988505559262</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.07109988505572762</v>
+        <v>-0.07109988505601206</v>
       </c>
       <c r="M13" t="n">
-        <v>1.084519804683958e-15</v>
+        <v>4.981032019474084e-15</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4067246670164</v>
+        <v>0.4067246670169316</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.36803518003153</v>
+        <v>-0.3680351800306383</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.01771284180826882</v>
+        <v>-0.01771284180864063</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07109988505597098</v>
+        <v>0.07109988505559262</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07109988505572762</v>
+        <v>0.07109988505601206</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.084519804683958e-15</v>
+        <v>-4.981032019474084e-15</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01987464331796218</v>
+        <v>0.01987464331914257</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.05856413030429408</v>
+        <v>-0.05856413030291918</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>2.247600015825579e-09</v>
+        <v>2.247600022764473e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>3.746000026375966e-10</v>
+        <v>3.746000037940789e-10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003551208025004415</v>
+        <v>0.0003551208035967868</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07492000052751931</v>
+        <v>0.07492000075881577</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0003551208026237873</v>
+        <v>-0.0003551208037606557</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01662598616628053</v>
+        <v>0.01662598616604516</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.01662598616640665</v>
+        <v>-0.01662598616620636</v>
       </c>
       <c r="M14" t="n">
-        <v>9.857353372737588e-16</v>
+        <v>2.479213989200619e-15</v>
       </c>
       <c r="N14" t="n">
-        <v>0.089444761736857</v>
+        <v>0.08944476173607985</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08944476173654792</v>
+        <v>0.089444761736166</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0003551208026237873</v>
+        <v>0.0003551208037606557</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01662598616628053</v>
+        <v>-0.01662598616604516</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01662598616640665</v>
+        <v>0.01662598616620636</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.857353372737588e-16</v>
+        <v>-2.479213989200619e-15</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01031115526158288</v>
+        <v>0.01031115526116544</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01031115526112991</v>
+        <v>0.01031115526010673</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>7.168575258849612e-09</v>
+        <v>7.168575258776767e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>1.194762543141602e-09</v>
+        <v>1.194762543129461e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001132634890898239</v>
+        <v>0.001132634890886729</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2389525086283204</v>
+        <v>0.2389525086258922</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.00113263489089821</v>
+        <v>-0.001132634890886774</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.009197914260807849</v>
+        <v>-0.009197914261043216</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.009197914260166584</v>
+        <v>-0.00919791425992933</v>
       </c>
       <c r="M15" t="n">
-        <v>9.838012339897462e-16</v>
+        <v>2.490688493081734e-15</v>
       </c>
       <c r="N15" t="n">
-        <v>0.04939957223232838</v>
+        <v>0.04939957223187874</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.04344854946169363</v>
+        <v>-0.04344854946208265</v>
       </c>
       <c r="P15" t="n">
-        <v>0.00113263489089821</v>
+        <v>0.001132634890886774</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.009197914260807849</v>
+        <v>0.009197914261043216</v>
       </c>
       <c r="R15" t="n">
-        <v>0.009197914260166584</v>
+        <v>0.00919791425992933</v>
       </c>
       <c r="S15" t="n">
-        <v>-9.838012339897462e-16</v>
+        <v>-2.490688493081734e-15</v>
       </c>
       <c r="T15" t="n">
-        <v>0.005787913328671124</v>
+        <v>0.005787913327693683</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.01173893610315879</v>
+        <v>-0.01173893610418197</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.658475053296915e-08</v>
+        <v>-1.658475053123443e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.764125088828192e-09</v>
+        <v>-2.764125088539071e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.002620390584209126</v>
+        <v>-0.002620390583935039</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5528250177656383</v>
+        <v>-0.5528250177078142</v>
       </c>
       <c r="J16" t="n">
-        <v>0.002620390584070265</v>
+        <v>0.002620390583842891</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01662598616658162</v>
+        <v>-0.01662598616656297</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01662598616692357</v>
+        <v>0.01662598616716049</v>
       </c>
       <c r="M16" t="n">
-        <v>9.82408816011432e-16</v>
+        <v>2.484940483084779e-15</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.08349373896592382</v>
+        <v>-0.08349373896636569</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.08349373896501433</v>
+        <v>-0.08349373896516532</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.002620390584070265</v>
+        <v>-0.002620390583842891</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01662598616658162</v>
+        <v>0.01662598616656297</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.01662598616692357</v>
+        <v>-0.01662598616716049</v>
       </c>
       <c r="S16" t="n">
-        <v>-9.82408816011432e-16</v>
+        <v>-2.484940483084779e-15</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.01626217803562113</v>
+        <v>-0.01626217803659191</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.01626217803448071</v>
+        <v>-0.01626217803421071</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>7.168575257735764e-09</v>
+        <v>7.168575256660879e-09</v>
       </c>
       <c r="G17" t="n">
-        <v>1.194762542955961e-09</v>
+        <v>1.194762542776813e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001132634890722251</v>
+        <v>0.001132634890552419</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2389525085911921</v>
+        <v>0.2389525085553626</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.001132634890722239</v>
+        <v>-0.001132634890552375</v>
       </c>
       <c r="K17" t="n">
-        <v>0.009197914260510309</v>
+        <v>0.009197914260527185</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009197914260683504</v>
+        <v>0.009197914260882456</v>
       </c>
       <c r="M17" t="n">
-        <v>9.807279028126785e-16</v>
+        <v>2.485757172816889e-15</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.04344854946139165</v>
+        <v>-0.04344854946217147</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04939957223324143</v>
+        <v>0.04939957223308333</v>
       </c>
       <c r="P17" t="n">
-        <v>0.001132634890722239</v>
+        <v>0.001132634890552375</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.009197914260510309</v>
+        <v>-0.009197914260527185</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.009197914260683504</v>
+        <v>-0.009197914260882456</v>
       </c>
       <c r="S17" t="n">
-        <v>-9.807279028126785e-16</v>
+        <v>-2.485757172816889e-15</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.01173893610271293</v>
+        <v>-0.01173893610312504</v>
       </c>
       <c r="U17" t="n">
-        <v>0.005787913329816874</v>
+        <v>0.005787913330079775</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>9.625408910055207e-06</v>
+        <v>9.625408910056074e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>1.203176113756901e-06</v>
+        <v>1.203176113757009e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>1.140610955841542</v>
+        <v>1.140610955841645</v>
       </c>
       <c r="I18" t="n">
-        <v>240.6352227513802</v>
+        <v>240.6352227514018</v>
       </c>
       <c r="J18" t="n">
         <v>-1.140610955841566</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4122533851324607</v>
+        <v>0.412253385132467</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4606973814495045</v>
+        <v>-0.4606973814500098</v>
       </c>
       <c r="M18" t="n">
-        <v>0.001526536120999484</v>
+        <v>0.001526536120996663</v>
       </c>
       <c r="N18" t="n">
-        <v>2.455594483854196</v>
+        <v>2.455594483856218</v>
       </c>
       <c r="O18" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529868</v>
       </c>
       <c r="P18" t="n">
         <v>1.140610955841566</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4122533851324607</v>
+        <v>-0.412253385132467</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4606973814495045</v>
+        <v>0.4606973814500098</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.001526536120999484</v>
+        <v>-0.001526536120996663</v>
       </c>
       <c r="T18" t="n">
-        <v>1.229984567741841</v>
+        <v>1.229984567743863</v>
       </c>
       <c r="U18" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529868</v>
       </c>
     </row>
     <row r="19">
@@ -2745,52 +2745,52 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>9.625408910055207e-06</v>
+        <v>9.62540891005564e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>1.203176113756901e-06</v>
+        <v>1.203176113756955e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.140610955841542</v>
+        <v>1.140610955841593</v>
       </c>
       <c r="I19" t="n">
-        <v>240.6352227513802</v>
+        <v>240.635222751391</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.140610955841538</v>
+        <v>-1.140610955841595</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4122533851324608</v>
+        <v>-0.4122533851324677</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1326141717189501</v>
+        <v>0.1326141717183632</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.00152653612100095</v>
+        <v>-0.001526536121003745</v>
       </c>
       <c r="N19" t="n">
-        <v>0.08234827118037735</v>
+        <v>0.08234827118272525</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.649013540529843</v>
+        <v>-1.649013540529871</v>
       </c>
       <c r="P19" t="n">
-        <v>1.140610955841538</v>
+        <v>1.140610955841595</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4122533851324608</v>
+        <v>0.4122533851324677</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.1326141717189501</v>
+        <v>-0.1326141717183632</v>
       </c>
       <c r="S19" t="n">
-        <v>0.00152653612100095</v>
+        <v>0.001526536121003745</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.143261644931977</v>
+        <v>-1.143261644929629</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.649013540529843</v>
+        <v>-1.649013540529871</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>9.625408910055207e-06</v>
+        <v>9.625408910055424e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>1.203176113756901e-06</v>
+        <v>1.203176113756928e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>1.140610955841542</v>
+        <v>1.140610955841568</v>
       </c>
       <c r="I20" t="n">
-        <v>240.6352227513802</v>
+        <v>240.6352227513856</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.140610955841538</v>
+        <v>-1.140610955841566</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4122533851324607</v>
+        <v>0.4122533851324672</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1326141717193148</v>
+        <v>-0.1326141717198984</v>
       </c>
       <c r="M20" t="n">
-        <v>0.001526536120999483</v>
+        <v>0.001526536120996663</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143261644933435</v>
+        <v>1.14326164493577</v>
       </c>
       <c r="O20" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529868</v>
       </c>
       <c r="P20" t="n">
-        <v>1.140610955841538</v>
+        <v>1.140610955841566</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4122533851324607</v>
+        <v>-0.4122533851324672</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1326141717193148</v>
+        <v>0.1326141717198984</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.001526536120999483</v>
+        <v>-0.001526536120996663</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.08234827117891852</v>
+        <v>-0.08234827117658372</v>
       </c>
       <c r="U20" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529868</v>
       </c>
     </row>
     <row r="21">
@@ -2891,40 +2891,40 @@
         <v>240.6352227513802</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.140610955841566</v>
+        <v>-1.140610955841453</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4122533851324608</v>
+        <v>0.4122533851324676</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4606973814492966</v>
+        <v>-0.4606973814487824</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.001526536121000953</v>
+        <v>-0.001526536121003748</v>
       </c>
       <c r="N21" t="n">
-        <v>1.22998456774101</v>
+        <v>1.229984567738952</v>
       </c>
       <c r="O21" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529871</v>
       </c>
       <c r="P21" t="n">
-        <v>1.140610955841566</v>
+        <v>1.140610955841453</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.4122533851324608</v>
+        <v>-0.4122533851324676</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4606973814492966</v>
+        <v>0.4606973814487824</v>
       </c>
       <c r="S21" t="n">
-        <v>0.001526536121000953</v>
+        <v>0.001526536121003748</v>
       </c>
       <c r="T21" t="n">
-        <v>2.455594483853365</v>
+        <v>2.455594483851307</v>
       </c>
       <c r="U21" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529871</v>
       </c>
     </row>
     <row r="22">
@@ -2961,37 +2961,37 @@
         <v>0.386099679661811</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06988534966488702</v>
+        <v>0.0698853496648788</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1070524710587034</v>
+        <v>-0.1070524710594157</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0004228048841396726</v>
+        <v>0.0004228048841367167</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2932904909456604</v>
+        <v>0.2932904909485095</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2795413986595481</v>
+        <v>0.2795413986595152</v>
       </c>
       <c r="P22" t="n">
         <v>-0.386099679661811</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.06988534966488702</v>
+        <v>-0.0698853496648788</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1070524710587034</v>
+        <v>0.1070524710594157</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0004228048841396726</v>
+        <v>-0.0004228048841367167</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5631292775239671</v>
+        <v>0.5631292775268171</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2795413986595481</v>
+        <v>0.2795413986595152</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.258225144827168e-06</v>
+        <v>-3.258225144825433e-06</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.07278143103396e-07</v>
+        <v>-4.072781431031791e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3860996796620194</v>
+        <v>-0.3860996796618138</v>
       </c>
       <c r="I23" t="n">
-        <v>-81.45562862067918</v>
+        <v>-81.45562862063582</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3860996796620384</v>
+        <v>0.386099679661811</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.06988534966488746</v>
+        <v>-0.06988534966487836</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05532944124457745</v>
+        <v>0.0553294412438885</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0004228048841412851</v>
+        <v>-0.0004228048841445928</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3562371582674621</v>
+        <v>-0.3562371582647073</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2795413986595507</v>
+        <v>-0.2795413986595134</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3860996796620384</v>
+        <v>-0.386099679661811</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.06988534966488746</v>
+        <v>0.06988534966487836</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.05532944124457745</v>
+        <v>-0.0553294412438885</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0004228048841412851</v>
+        <v>0.0004228048841445928</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.08639837168915587</v>
+        <v>-0.08639837168639986</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.279541398659549</v>
+        <v>-0.2795413986595126</v>
       </c>
     </row>
     <row r="24">
@@ -3092,40 +3092,40 @@
         <v>-81.45562862063582</v>
       </c>
       <c r="J24" t="n">
-        <v>0.386099679661811</v>
+        <v>0.3860996796620384</v>
       </c>
       <c r="K24" t="n">
-        <v>0.06988534966488746</v>
+        <v>0.06988534966487858</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.05532944124497974</v>
+        <v>-0.05532944124555528</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0004228048841396713</v>
+        <v>0.0004228048841367154</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0863983716907657</v>
+        <v>0.08639837169306763</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2795413986595507</v>
+        <v>0.2795413986595152</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.386099679661811</v>
+        <v>-0.3860996796620384</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.06988534966488746</v>
+        <v>-0.06988534966487858</v>
       </c>
       <c r="R24" t="n">
-        <v>0.05532944124497974</v>
+        <v>0.05532944124555528</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0004228048841396713</v>
+        <v>-0.0004228048841367154</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3562371582690712</v>
+        <v>0.3562371582713735</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2795413986595481</v>
+        <v>0.2795413986595152</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.258225144825433e-06</v>
+        <v>-3.258225144823698e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.072781431031791e-07</v>
+        <v>-4.072781431029623e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3860996796618138</v>
+        <v>-0.3860996796616082</v>
       </c>
       <c r="I25" t="n">
-        <v>-81.45562862063582</v>
+        <v>-81.45562862059245</v>
       </c>
       <c r="J25" t="n">
-        <v>0.386099679661811</v>
+        <v>0.3860996796615837</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06988534966488746</v>
+        <v>0.06988534966487814</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1070524710584768</v>
+        <v>-0.1070524710580115</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0004228048841412838</v>
+        <v>-0.0004228048841445884</v>
       </c>
       <c r="N25" t="n">
-        <v>0.563129277523061</v>
+        <v>0.5631292775211996</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2795413986595507</v>
+        <v>0.2795413986595117</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.386099679661811</v>
+        <v>-0.3860996796615837</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.06988534966488746</v>
+        <v>-0.06988534966487814</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1070524710584768</v>
+        <v>0.1070524710580115</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0004228048841412838</v>
+        <v>0.0004228048841445884</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2932904909447553</v>
+        <v>0.2932904909428933</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2795413986595499</v>
+        <v>0.2795413986595126</v>
       </c>
     </row>
     <row r="26">
@@ -3229,37 +3229,37 @@
         <v>-0.08201023489709769</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001712435580860427</v>
+        <v>0.001712435580727645</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.01351504637649903</v>
+        <v>-0.01351504637711198</v>
       </c>
       <c r="M26" t="n">
-        <v>5.488239379391937e-05</v>
+        <v>5.488239379228569e-05</v>
       </c>
       <c r="N26" t="n">
-        <v>0.08460134726158497</v>
+        <v>0.08460134726403878</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00684974232344171</v>
+        <v>0.006849742322909691</v>
       </c>
       <c r="P26" t="n">
         <v>0.08201023489709769</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.001712435580860427</v>
+        <v>-0.001712435580727645</v>
       </c>
       <c r="R26" t="n">
-        <v>0.01351504637649903</v>
+        <v>0.01351504637711198</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.488239379391937e-05</v>
+        <v>-5.488239379228569e-05</v>
       </c>
       <c r="T26" t="n">
-        <v>0.02351902375040749</v>
+        <v>0.02351902375285864</v>
       </c>
       <c r="U26" t="n">
-        <v>0.00684974232344171</v>
+        <v>0.006849742322910579</v>
       </c>
     </row>
     <row r="27">
@@ -3293,40 +3293,40 @@
         <v>17.30173732001142</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.08201023489664294</v>
+        <v>-0.08201023489709769</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.001712435580859539</v>
+        <v>-0.001712435580726535</v>
       </c>
       <c r="L27" t="n">
-        <v>0.005330430322269208</v>
+        <v>0.005330430321729085</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.488239379548322e-05</v>
+        <v>-5.488239379783637e-05</v>
       </c>
       <c r="N27" t="n">
-        <v>0.009219440466513129</v>
+        <v>0.009219440468673401</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.006849742323438157</v>
+        <v>-0.006849742322907026</v>
       </c>
       <c r="P27" t="n">
-        <v>0.08201023489664294</v>
+        <v>0.08201023489709769</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.001712435580859539</v>
+        <v>0.001712435580726535</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.005330430322269208</v>
+        <v>-0.005330430321729085</v>
       </c>
       <c r="S27" t="n">
-        <v>5.488239379548322e-05</v>
+        <v>5.488239379783637e-05</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.05186288304466569</v>
+        <v>-0.05186288304250564</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.006849742323439045</v>
+        <v>-0.006849742322907026</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>6.920694928039262e-07</v>
+        <v>6.920694928073956e-07</v>
       </c>
       <c r="G28" t="n">
-        <v>8.650868660049077e-08</v>
+        <v>8.650868660092445e-08</v>
       </c>
       <c r="H28" t="n">
-        <v>0.08201023489726525</v>
+        <v>0.08201023489767638</v>
       </c>
       <c r="I28" t="n">
-        <v>17.30173732009815</v>
+        <v>17.30173732018489</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.08201023489709769</v>
+        <v>-0.08201023489755244</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001712435580859539</v>
+        <v>0.001712435580726979</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.005330430322685431</v>
+        <v>-0.005330430322988522</v>
       </c>
       <c r="M28" t="n">
-        <v>5.488239379392197e-05</v>
+        <v>5.488239379228569e-05</v>
       </c>
       <c r="N28" t="n">
-        <v>0.05186288304632969</v>
+        <v>0.05186288304754272</v>
       </c>
       <c r="O28" t="n">
-        <v>0.006849742323439045</v>
+        <v>0.006849742322908803</v>
       </c>
       <c r="P28" t="n">
-        <v>0.08201023489709769</v>
+        <v>0.08201023489755244</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.001712435580859539</v>
+        <v>-0.001712435580726979</v>
       </c>
       <c r="R28" t="n">
-        <v>0.005330430322685431</v>
+        <v>0.005330430322988522</v>
       </c>
       <c r="S28" t="n">
-        <v>-5.488239379392197e-05</v>
+        <v>-5.488239379228569e-05</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.009219440464847573</v>
+        <v>-0.009219440463635209</v>
       </c>
       <c r="U28" t="n">
-        <v>0.006849742323438157</v>
+        <v>0.006849742322907026</v>
       </c>
     </row>
     <row r="29">
@@ -3430,37 +3430,37 @@
         <v>-0.08201023489755244</v>
       </c>
       <c r="K29" t="n">
-        <v>0.001712435580860205</v>
+        <v>0.001712435580726979</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01351504637630585</v>
+        <v>-0.01351504637620604</v>
       </c>
       <c r="M29" t="n">
-        <v>-5.488239379548366e-05</v>
+        <v>-5.488239379784028e-05</v>
       </c>
       <c r="N29" t="n">
-        <v>0.02351902374963499</v>
+        <v>0.02351902374923509</v>
       </c>
       <c r="O29" t="n">
-        <v>0.006849742323440822</v>
+        <v>0.006849742322907915</v>
       </c>
       <c r="P29" t="n">
         <v>0.08201023489755244</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.001712435580860205</v>
+        <v>-0.001712435580726979</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01351504637630585</v>
+        <v>0.01351504637620604</v>
       </c>
       <c r="S29" t="n">
-        <v>5.488239379548366e-05</v>
+        <v>5.488239379784028e-05</v>
       </c>
       <c r="T29" t="n">
-        <v>0.08460134726081225</v>
+        <v>0.08460134726041391</v>
       </c>
       <c r="U29" t="n">
-        <v>0.006849742323439045</v>
+        <v>0.006849742322907026</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.089616051795639e-07</v>
+        <v>-1.089616051830333e-07</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.362020064744549e-08</v>
+        <v>-1.362020064787917e-08</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.01291195021377832</v>
+        <v>-0.01291195021418945</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.724040129489097</v>
+        <v>-2.724040129575833</v>
       </c>
       <c r="J30" t="n">
-        <v>0.01291195021349267</v>
+        <v>0.01291195021440217</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.003714035952816719</v>
+        <v>-0.003714035953082284</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.0001775604013612986</v>
+        <v>-0.0001775604016159837</v>
       </c>
       <c r="M30" t="n">
-        <v>3.648815565626944e-06</v>
+        <v>3.648815565276964e-06</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.01031480407669871</v>
+        <v>-0.01031480407568131</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.0148561438112651</v>
+        <v>-0.01485614381232736</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.01291195021349267</v>
+        <v>-0.01291195021440217</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.003714035952816719</v>
+        <v>0.003714035953082284</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001775604013612986</v>
+        <v>0.0001775604016159837</v>
       </c>
       <c r="S30" t="n">
-        <v>-3.648815565626944e-06</v>
+        <v>-3.648815565276964e-06</v>
       </c>
       <c r="T30" t="n">
-        <v>0.01173528728759021</v>
+        <v>0.01173528728861006</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.0148561438112651</v>
+        <v>-0.01485614381233091</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.089616051760944e-07</v>
+        <v>-1.089616051795639e-07</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.36202006470118e-08</v>
+        <v>-1.362020064744549e-08</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.01291195021336719</v>
+        <v>-0.01291195021377832</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.724040129402361</v>
+        <v>-2.724040129489097</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01291195021349267</v>
+        <v>0.01291195021394742</v>
       </c>
       <c r="K31" t="n">
-        <v>0.003714035952815387</v>
+        <v>0.003714035953081396</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.001310195292259397</v>
+        <v>-0.001310195292502869</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.648815566643059e-06</v>
+        <v>-3.648815567473124e-06</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.005784264513107429</v>
+        <v>-0.005784264512133763</v>
       </c>
       <c r="O31" t="n">
-        <v>0.01485614381126332</v>
+        <v>0.01485614381232558</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.01291195021349267</v>
+        <v>-0.01291195021394742</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.003714035952815387</v>
+        <v>-0.003714035953081396</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001310195292259397</v>
+        <v>0.001310195292502869</v>
       </c>
       <c r="S31" t="n">
-        <v>3.648815566643059e-06</v>
+        <v>3.648815567473124e-06</v>
       </c>
       <c r="T31" t="n">
-        <v>0.01626582685118416</v>
+        <v>0.01626582685215805</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01485614381126332</v>
+        <v>0.01485614381232736</v>
       </c>
     </row>
     <row r="32">
@@ -3616,52 +3616,52 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.089616051691555e-07</v>
+        <v>-1.089616051760944e-07</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.362020064614444e-08</v>
+        <v>-1.36202006470118e-08</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.01291195021254493</v>
+        <v>-0.01291195021336719</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.724040129228888</v>
+        <v>-2.724040129402361</v>
       </c>
       <c r="J32" t="n">
-        <v>0.01291195021258318</v>
+        <v>0.01291195021349267</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.003714035952815831</v>
+        <v>-0.003714035953082284</v>
       </c>
       <c r="L32" t="n">
-        <v>0.001310195291973071</v>
+        <v>0.00131019529190779</v>
       </c>
       <c r="M32" t="n">
-        <v>3.648815565620439e-06</v>
+        <v>3.648815565272193e-06</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.01626582685003797</v>
+        <v>-0.01626582684977684</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.01485614381126332</v>
+        <v>-0.01485614381232736</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.01291195021258318</v>
+        <v>-0.01291195021349267</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.003714035952815831</v>
+        <v>0.003714035953082284</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.001310195291973071</v>
+        <v>-0.00131019529190779</v>
       </c>
       <c r="S32" t="n">
-        <v>-3.648815565620439e-06</v>
+        <v>-3.648815565272193e-06</v>
       </c>
       <c r="T32" t="n">
-        <v>0.005784264514252069</v>
+        <v>0.005784264514513193</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.01485614381126155</v>
+        <v>-0.01485614381232914</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.089616051795639e-07</v>
+        <v>-1.089616051830333e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.362020064744549e-08</v>
+        <v>-1.362020064787917e-08</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.01291195021377832</v>
+        <v>-0.01291195021418945</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.724040129489097</v>
+        <v>-2.724040129575833</v>
       </c>
       <c r="J33" t="n">
         <v>0.01291195021394742</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.003714035952815831</v>
+        <v>-0.003714035953083616</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.0001775604012499432</v>
+        <v>-0.0001775604013539711</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.648815566643926e-06</v>
+        <v>-3.648815567470955e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>0.01173528728714435</v>
+        <v>0.01173528728756135</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.0148561438112651</v>
+        <v>-0.01485614381233269</v>
       </c>
       <c r="P33" t="n">
         <v>-0.01291195021394742</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003714035952815831</v>
+        <v>0.003714035953083616</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0001775604012499432</v>
+        <v>0.0001775604013539711</v>
       </c>
       <c r="S33" t="n">
-        <v>3.648815566643926e-06</v>
+        <v>3.648815567470955e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.01031480407714414</v>
+        <v>-0.01031480407672802</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.01485614381126332</v>
+        <v>-0.01485614381233624</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>7.360031130197037e-06</v>
+        <v>7.360031130203976e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.226671855032839e-06</v>
+        <v>1.226671855033996e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.162884918571132</v>
+        <v>1.162884918572228</v>
       </c>
       <c r="I2" t="n">
-        <v>245.3343710065679</v>
+        <v>245.3343710067992</v>
       </c>
       <c r="J2" t="n">
         <v>-0.01</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005143544436265349</v>
+        <v>-0.005143544436268916</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.005143544436263927</v>
+        <v>-0.005143544436260579</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.009992639968869803</v>
+        <v>-0.009992639968869796</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001430013372534397</v>
+        <v>0.0001430013372528314</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0001430013372536887</v>
+        <v>-0.0001430013372543053</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.459828480256998e-16</v>
+        <v>-1.1816844298607e-15</v>
       </c>
       <c r="V2" t="n">
         <v>-0.01</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.009992639968869803</v>
+        <v>-0.009992639968869796</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.005143544436263927</v>
+        <v>-0.005143544436260579</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.005143544436265349</v>
+        <v>0.005143544436268916</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2.459828480256998e-16</v>
+        <v>-1.1816844298607e-15</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.0001430013372536887</v>
+        <v>-0.0001430013372543053</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.0001430013372534397</v>
+        <v>-0.0001430013372528314</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.162884918571081</v>
+        <v>-1.162884918572217</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.30374669528911</v>
+        <v>-1.303746695289486</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.303746695288943</v>
+        <v>1.30374669528852</v>
       </c>
       <c r="AK2" t="n">
-        <v>7.001050289962223e-16</v>
+        <v>3.363255684988146e-15</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3.805419096299101</v>
+        <v>-3.805419096297374</v>
       </c>
       <c r="AM2" t="n">
-        <v>-3.805419096299785</v>
+        <v>-3.805419096301363</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.162884918571081</v>
+        <v>1.162884918572217</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.30374669528911</v>
+        <v>1.303746695289486</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1.303746695288943</v>
+        <v>-1.30374669528852</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-7.001050289962223e-16</v>
+        <v>-3.363255684988146e-15</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.01706107543456</v>
+        <v>-4.017061075433746</v>
       </c>
       <c r="AS2" t="n">
-        <v>-4.017061075434876</v>
+        <v>-4.017061075435553</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>-8.158294380586554e-07</v>
+        <v>-8.158294380586814e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7734063072796052</v>
+        <v>-0.77340630727963</v>
       </c>
       <c r="I3" t="n">
-        <v>-163.1658876117311</v>
+        <v>-163.1658876117363</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.001181950344900396</v>
+        <v>-0.001181950344896417</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.005133919027353872</v>
+        <v>-0.005133919027350523</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001247154414832138</v>
+        <v>0.00124715441483153</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0008581353759201137</v>
+        <v>-0.0008581353759194087</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.45867092239527e-16</v>
+        <v>-1.181563932377305e-15</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.005133919027353872</v>
+        <v>-0.005133919027350523</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.001181950344900396</v>
+        <v>0.001181950344896417</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2.45867092239527e-16</v>
+        <v>-1.181563932377305e-15</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0008581353759201137</v>
+        <v>-0.0008581353759194087</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.001247154414832138</v>
+        <v>-0.00124715441483153</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.7734063072796055</v>
+        <v>0.7734063072796302</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3434724264381729</v>
+        <v>0.3434724264377969</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.3434724264387864</v>
+        <v>0.3434724264392463</v>
       </c>
       <c r="AK3" t="n">
-        <v>6.997755702201921e-16</v>
+        <v>3.362912730612329e-15</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.395397101135475</v>
+        <v>-0.3953971011373766</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.953311546290301</v>
+        <v>1.953311546288723</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.7734063072796055</v>
+        <v>-0.7734063072796302</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.3434724264381729</v>
+        <v>-0.3434724264377969</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.3434724264387864</v>
+        <v>-0.3434724264392463</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-6.997755702201921e-16</v>
+        <v>-3.362912730612329e-15</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.665437457497243</v>
+        <v>-1.665437457498101</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1075230123387366</v>
+        <v>0.1075230123380582</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>2.42992212650707e-06</v>
+        <v>2.429922126505335e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.049870210845116e-07</v>
+        <v>4.049870210842225e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.383927695988117</v>
+        <v>0.3839276959878429</v>
       </c>
       <c r="I4" t="n">
-        <v>80.99740421690232</v>
+        <v>80.9974042168445</v>
       </c>
       <c r="J4" t="n">
         <v>0.01</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.001172324935990341</v>
+        <v>-0.001172324935986361</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.001172324935992853</v>
+        <v>-0.001172324935996923</v>
       </c>
       <c r="R4" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00196228845349925</v>
+        <v>0.001962288453499951</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.001962288453498811</v>
+        <v>-0.001962288453498106</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.459196944341733e-16</v>
+        <v>-1.18166403535008e-15</v>
       </c>
       <c r="V4" t="n">
         <v>0.01</v>
@@ -4338,55 +4338,55 @@
         <v>0.01000242992212651</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.001172324935992853</v>
+        <v>-0.001172324935996923</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.001172324935990341</v>
+        <v>0.001172324935986361</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.459196944341733e-16</v>
+        <v>-1.18166403535008e-15</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.001962288453498811</v>
+        <v>-0.001962288453498106</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.00196228845349925</v>
+        <v>-0.001962288453499951</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.3839276959881772</v>
+        <v>-0.3839276959879498</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.303746695288792</v>
+        <v>1.303746695289277</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1.303746695288497</v>
+        <v>-1.303746695288037</v>
       </c>
       <c r="AK4" t="n">
-        <v>6.999252841588009e-16</v>
+        <v>3.363197639073303e-15</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.363333541454613</v>
+        <v>5.363333541452711</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.363333541455821</v>
+        <v>5.363333541457796</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.3839276959881772</v>
+        <v>0.3839276959879498</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1.303746695288792</v>
+        <v>-1.303746695289277</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.303746695288497</v>
+        <v>1.303746695288037</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-6.999252841588009e-16</v>
+        <v>-3.363197639073303e-15</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.459146630276371</v>
+        <v>2.459146630275513</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.459146630276932</v>
+        <v>2.459146630277869</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.158294380594254e-07</v>
+        <v>-8.158294380600086e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7734063072803353</v>
+        <v>-0.7734063072808882</v>
       </c>
       <c r="I5" t="n">
-        <v>-163.1658876118851</v>
+        <v>-163.1658876120017</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005133919027355294</v>
+        <v>-0.005133919027358861</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.001181950344902908</v>
+        <v>-0.001181950344906979</v>
       </c>
       <c r="R5" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0008581353759205526</v>
+        <v>0.000858135375921254</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.001247154414832387</v>
+        <v>-0.001247154414833003</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.45883799833235e-16</v>
+        <v>-1.18139457602318e-15</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.001181950344902908</v>
+        <v>-0.001181950344906979</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.005133919027355294</v>
+        <v>0.005133919027358861</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2.45883799833235e-16</v>
+        <v>-1.18139457602318e-15</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.001247154414832387</v>
+        <v>-0.001247154414833003</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0008581353759205526</v>
+        <v>-0.000858135375921254</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.7734063072803354</v>
+        <v>0.7734063072808883</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.3434724264384916</v>
+        <v>-0.3434724264380065</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.3434724264383395</v>
+        <v>-0.3434724264387636</v>
       </c>
       <c r="AK5" t="n">
-        <v>6.99823122602284e-16</v>
+        <v>3.362430716373665e-15</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.953311546290985</v>
+        <v>1.953311546292713</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.3953971011342658</v>
+        <v>-0.3953971011322915</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.7734063072803354</v>
+        <v>-0.7734063072808883</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.3434724264384916</v>
+        <v>0.3434724264380065</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.3434724264383395</v>
+        <v>0.3434724264387636</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-6.99823122602284e-16</v>
+        <v>-3.362430716373665e-15</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1075230123390525</v>
+        <v>0.1075230123398683</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1.665437457496684</v>
+        <v>-1.665437457495747</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.528418706785162e-06</v>
+        <v>1.528418706790366e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.547364511308603e-07</v>
+        <v>2.547364511317277e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2414901556720556</v>
+        <v>0.2414901556728778</v>
       </c>
       <c r="I6" t="n">
-        <v>50.94729022617206</v>
+        <v>50.94729022634553</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.005143544436265349</v>
+        <v>-0.005143544436268916</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.005143544436263927</v>
+        <v>-0.005143544436260579</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.009992639968869803</v>
+        <v>-0.009992639968869796</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001430013372534397</v>
+        <v>0.0001430013372528314</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0001430013372536887</v>
+        <v>-0.0001430013372543053</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.459828480256998e-16</v>
+        <v>-1.1816844298607e-15</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01030576096285544</v>
+        <v>-0.01030576096286427</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.01030576096285178</v>
+        <v>-0.01030576096284246</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.009991111550163018</v>
+        <v>-0.009991111550163006</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001241092037800776</v>
+        <v>0.00124109203779992</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001241092037801047</v>
+        <v>-0.001241092037801604</v>
       </c>
       <c r="U6" t="n">
-        <v>-6.320011768432583e-16</v>
+        <v>-3.055103843794704e-15</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.009992639968869803</v>
+        <v>-0.009992639968869796</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.005143544436263927</v>
+        <v>-0.005143544436260579</v>
       </c>
       <c r="X6" t="n">
-        <v>0.005143544436265349</v>
+        <v>0.005143544436268916</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.459828480256998e-16</v>
+        <v>-1.1816844298607e-15</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0001430013372536887</v>
+        <v>-0.0001430013372543053</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0001430013372534397</v>
+        <v>-0.0001430013372528314</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.009991111550163018</v>
+        <v>-0.009991111550163006</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.01030576096285178</v>
+        <v>-0.01030576096284246</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.01030576096285544</v>
+        <v>0.01030576096286427</v>
       </c>
       <c r="AE6" t="n">
-        <v>-6.320011768432583e-16</v>
+        <v>-3.055103843794704e-15</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001241092037801047</v>
+        <v>-0.001241092037801604</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001241092037800776</v>
+        <v>-0.00124109203779992</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.2414901556719542</v>
+        <v>-0.2414901556728637</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.2491176456848834</v>
+        <v>0.2491176456844955</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.2491176456850503</v>
+        <v>-0.2491176456854803</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.098667551249974e-15</v>
+        <v>5.332039870427548e-15</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.559940055460197</v>
+        <v>1.559940055461441</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.559940055459679</v>
+        <v>1.559940055458332</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.2414901556719542</v>
+        <v>0.2414901556728637</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.2491176456848834</v>
+        <v>-0.2491176456844955</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.2491176456850503</v>
+        <v>0.2491176456854803</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.098667551249974e-15</v>
+        <v>-5.332039870427548e-15</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.06523418134989445</v>
+        <v>-0.06523418134856085</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.06523418135037939</v>
+        <v>-0.06523418135135906</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.139840215893363e-06</v>
+        <v>-1.139840215894032e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.899733693155606e-07</v>
+        <v>-1.89973369315672e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1800947541111514</v>
+        <v>-0.180094754111257</v>
       </c>
       <c r="I7" t="n">
-        <v>-37.99467386311211</v>
+        <v>-37.99467386313439</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.001181950344900396</v>
+        <v>-0.001181950344896417</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.005133919027353872</v>
+        <v>-0.005133919027350523</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001247154414832138</v>
+        <v>0.00124715441483153</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0008581353759201137</v>
+        <v>-0.0008581353759194087</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.45867092239527e-16</v>
+        <v>-1.181563932377305e-15</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.009634190035139751</v>
+        <v>-0.009634190035129281</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0103090191879966</v>
+        <v>-0.01030901918798729</v>
       </c>
       <c r="R7" t="n">
-        <v>-6.034816844245296e-06</v>
+        <v>-6.034816844246121e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0009979940318743741</v>
+        <v>0.0009979940318735161</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.001439162794334948</v>
+        <v>-0.00143916279433412</v>
       </c>
       <c r="U7" t="n">
-        <v>-6.325385275155652e-16</v>
+        <v>-3.05495934852082e-15</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.005133919027353872</v>
+        <v>-0.005133919027350523</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001181950344900396</v>
+        <v>0.001181950344896417</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.45867092239527e-16</v>
+        <v>-1.181563932377305e-15</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0008581353759201137</v>
+        <v>-0.0008581353759194087</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.001247154414832138</v>
+        <v>-0.00124715441483153</v>
       </c>
       <c r="AB7" t="n">
-        <v>-6.034816844245296e-06</v>
+        <v>-6.034816844246121e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0103090191879966</v>
+        <v>-0.01030901918798729</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.009634190035139751</v>
+        <v>0.009634190035129281</v>
       </c>
       <c r="AE7" t="n">
-        <v>-6.325385275155652e-16</v>
+        <v>-3.05495934852082e-15</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.001439162794334948</v>
+        <v>-0.00143916279433412</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0009979940318743741</v>
+        <v>-0.0009979940318735161</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1800947541111514</v>
+        <v>0.180094754111257</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.3848851442709451</v>
+        <v>-0.3848851442713319</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.3848851442702956</v>
+        <v>-0.3848851442698287</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.100526392708724e-15</v>
+        <v>5.33197156902385e-15</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.584615722437863</v>
+        <v>1.584615722436372</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1.339034116201581</v>
+        <v>-1.339034116202926</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1800947541111514</v>
+        <v>-0.180094754111257</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.3848851442709451</v>
+        <v>0.3848851442713319</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.3848851442702956</v>
+        <v>0.3848851442698287</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.100526392708724e-15</v>
+        <v>-5.33197156902385e-15</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.7246951431839088</v>
+        <v>0.7246951431825996</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.9702767494240909</v>
+        <v>-0.9702767494250653</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>7.512617249995357e-07</v>
+        <v>7.512617249960662e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>1.252102874999226e-07</v>
+        <v>1.252102874993444e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1186993525499266</v>
+        <v>0.1186993525493785</v>
       </c>
       <c r="I8" t="n">
-        <v>25.04205749998452</v>
+        <v>25.04205749986887</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.001172324935990341</v>
+        <v>-0.001172324935986361</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.001172324935992853</v>
+        <v>-0.001172324935996923</v>
       </c>
       <c r="L8" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00196228845349925</v>
+        <v>0.001962288453499951</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.001962288453498811</v>
+        <v>-0.001962288453498106</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.459196944341733e-16</v>
+        <v>-1.18166403535008e-15</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.009637448260284578</v>
+        <v>-0.009637448260274106</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.00963744826029103</v>
+        <v>-0.009637448260301185</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01000318118385151</v>
+        <v>0.0100031811838515</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00119606478840903</v>
+        <v>0.001196064788409722</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.001196064788408546</v>
+        <v>-0.001196064788407717</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.310766232131836e-16</v>
+        <v>-3.054790642029308e-15</v>
       </c>
       <c r="V8" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.001172324935992853</v>
+        <v>-0.001172324935996923</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001172324935990341</v>
+        <v>0.001172324935986361</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.459196944341733e-16</v>
+        <v>-1.18166403535008e-15</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.001962288453498811</v>
+        <v>-0.001962288453498106</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.00196228845349925</v>
+        <v>-0.001962288453499951</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01000318118385151</v>
+        <v>0.0100031811838515</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.00963744826029103</v>
+        <v>-0.009637448260301185</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.009637448260284578</v>
+        <v>0.009637448260274106</v>
       </c>
       <c r="AE8" t="n">
-        <v>-6.310766232131836e-16</v>
+        <v>-3.054790642029308e-15</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.001196064788408546</v>
+        <v>-0.001196064788407717</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.00119606478840903</v>
+        <v>-0.001196064788409722</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.1186993525500384</v>
+        <v>-0.1186993525493563</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.2491176456852433</v>
+        <v>-0.2491176456847733</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2491176456855322</v>
+        <v>0.2491176456859986</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.096215874217183e-15</v>
+        <v>5.331206495933188e-15</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.314358449223394</v>
+        <v>-1.314358449224885</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1.314358449222493</v>
+        <v>-1.314358449221089</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.1186993525500384</v>
+        <v>0.1186993525493563</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.2491176456852433</v>
+        <v>0.2491176456847733</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.2491176456855322</v>
+        <v>-0.2491176456859986</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.096215874217183e-15</v>
+        <v>-5.331206495933188e-15</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.1803474248898009</v>
+        <v>-0.1803474248911088</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.1803474248889678</v>
+        <v>-0.1803474248875491</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.139840215896985e-06</v>
+        <v>-1.139840215900042e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.899733693161641e-07</v>
+        <v>-1.899733693166737e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1800947541117236</v>
+        <v>-0.1800947541122067</v>
       </c>
       <c r="I9" t="n">
-        <v>-37.99467386323282</v>
+        <v>-37.99467386333474</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.005133919027355294</v>
+        <v>-0.005133919027358861</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001181950344902908</v>
+        <v>-0.001181950344906979</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0008581353759205526</v>
+        <v>0.000858135375921254</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.001247154414832387</v>
+        <v>-0.001247154414833003</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.45883799833235e-16</v>
+        <v>-1.18139457602318e-15</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.01030901918800026</v>
+        <v>-0.01030901918800909</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.009634190035146204</v>
+        <v>-0.00963419003515636</v>
       </c>
       <c r="R9" t="n">
-        <v>-6.034816844253537e-06</v>
+        <v>-6.034816844260094e-06</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001439162794335432</v>
+        <v>0.001439162794336123</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0009979940318746456</v>
+        <v>-0.0009979940318752018</v>
       </c>
       <c r="U9" t="n">
-        <v>-6.323352839555595e-16</v>
+        <v>-3.054355086044638e-15</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.001181950344902908</v>
+        <v>-0.001181950344906979</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005133919027355294</v>
+        <v>0.005133919027358861</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.45883799833235e-16</v>
+        <v>-1.18139457602318e-15</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.001247154414832387</v>
+        <v>-0.001247154414833003</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.0008581353759205526</v>
+        <v>-0.000858135375921254</v>
       </c>
       <c r="AB9" t="n">
-        <v>-6.034816844253537e-06</v>
+        <v>-6.034816844260094e-06</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.009634190035146204</v>
+        <v>-0.00963419003515636</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01030901918800026</v>
+        <v>0.01030901918800909</v>
       </c>
       <c r="AE9" t="n">
-        <v>-6.323352839555595e-16</v>
+        <v>-3.054355086044638e-15</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0009979940318746456</v>
+        <v>-0.0009979940318752018</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.001439162794335432</v>
+        <v>-0.001439162794336123</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1800947541117236</v>
+        <v>0.1800947541122068</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.384885144270585</v>
+        <v>0.3848851442710549</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.3848851442707786</v>
+        <v>0.3848851442703483</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.099900377886616e-15</v>
+        <v>5.330733759291841e-15</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.339034116201065</v>
+        <v>-1.339034116199818</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.584615722438765</v>
+        <v>1.584615722440167</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.1800947541117236</v>
+        <v>-0.1800947541122068</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.384885144270585</v>
+        <v>-0.3848851442710549</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.3848851442707786</v>
+        <v>-0.3848851442703483</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.099900377886616e-15</v>
+        <v>-5.330733759291841e-15</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.9702767494236078</v>
+        <v>-0.9702767494222719</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.7246951431847437</v>
+        <v>0.7246951431861609</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.733241364251792e-07</v>
+        <v>1.733241364303834e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>2.88873560708632e-08</v>
+        <v>2.888735607173056e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02738521355517831</v>
+        <v>0.02738521355600057</v>
       </c>
       <c r="I10" t="n">
-        <v>5.777471214172639</v>
+        <v>5.777471214346112</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.01030576096285544</v>
+        <v>-0.01030576096286427</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01030576096285178</v>
+        <v>-0.01030576096284246</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.009991111550163018</v>
+        <v>-0.009991111550163006</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001241092037800776</v>
+        <v>0.00124109203779992</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.001241092037801047</v>
+        <v>-0.001241092037801604</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.320011768432583e-16</v>
+        <v>-3.055103843794704e-15</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.01737007367943667</v>
+        <v>-0.01737007367944867</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0173700736794309</v>
+        <v>-0.01737007367941414</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.009990938226026593</v>
+        <v>-0.009990938226026575</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001204350062741668</v>
+        <v>0.001204350062740928</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.001204350062741899</v>
+        <v>-0.001204350062742015</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.012366336751686e-15</v>
+        <v>-4.803761237550783e-15</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.009991111550163018</v>
+        <v>-0.009991111550163006</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01030576096285178</v>
+        <v>-0.01030576096284246</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01030576096285544</v>
+        <v>0.01030576096286427</v>
       </c>
       <c r="Y10" t="n">
-        <v>-6.320011768432583e-16</v>
+        <v>-3.055103843794704e-15</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.001241092037801047</v>
+        <v>-0.001241092037801604</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.001241092037800776</v>
+        <v>-0.00124109203779992</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.009990938226026593</v>
+        <v>-0.009990938226026575</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.0173700736794309</v>
+        <v>-0.01737007367941414</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01737007367943667</v>
+        <v>0.01737007367944867</v>
       </c>
       <c r="AE10" t="n">
-        <v>-1.012366336751686e-15</v>
+        <v>-4.803761237550783e-15</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.001204350062741899</v>
+        <v>-0.001204350062742015</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.001204350062741668</v>
+        <v>-0.001204350062740928</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.02738521355513512</v>
+        <v>-0.02738521355581724</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.06709668431189275</v>
+        <v>-0.06709668431254689</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.06709668431174309</v>
+        <v>0.06709668431145799</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.082577762816293e-15</v>
+        <v>4.976947966844225e-15</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.2284791144789988</v>
+        <v>-0.2284791144784704</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.2284791144794198</v>
+        <v>-0.2284791144812948</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02738521355513512</v>
+        <v>0.02738521355581724</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.06709668431189275</v>
+        <v>0.06709668431254689</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.06709668431174309</v>
+        <v>-0.06709668431145799</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.082577762816293e-15</v>
+        <v>-4.976947966844225e-15</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.1741009913914588</v>
+        <v>-0.1741009913902776</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.1741009913919385</v>
+        <v>-0.1741009913939884</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.12106593720697e-07</v>
+        <v>-1.121065937212221e-07</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.868443228678283e-08</v>
+        <v>-1.868443228687035e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01771284180787012</v>
+        <v>-0.0177128418079531</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.736886457356566</v>
+        <v>-3.736886457374071</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.009634190035139751</v>
+        <v>-0.009634190035129281</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0103090191879966</v>
+        <v>-0.01030901918798729</v>
       </c>
       <c r="L11" t="n">
-        <v>-6.034816844245296e-06</v>
+        <v>-6.034816844246121e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0009979940318743741</v>
+        <v>0.0009979940318735161</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.001439162794334948</v>
+        <v>-0.00143916279433412</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.325385275155652e-16</v>
+        <v>-3.05495934852082e-15</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.01735361784201489</v>
+        <v>-0.01735361784199784</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.01736938160993809</v>
+        <v>-0.01736938160992134</v>
       </c>
       <c r="R11" t="n">
-        <v>-6.146923437965993e-06</v>
+        <v>-6.146923437967343e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001259379183022008</v>
+        <v>0.00125937918302127</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.001230060733708419</v>
+        <v>-0.00123006073370777</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.012110102286476e-15</v>
+        <v>-4.803892303683812e-15</v>
       </c>
       <c r="V11" t="n">
-        <v>-6.034816844245296e-06</v>
+        <v>-6.034816844246121e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0103090191879966</v>
+        <v>-0.01030901918798729</v>
       </c>
       <c r="X11" t="n">
-        <v>0.009634190035139751</v>
+        <v>0.009634190035129281</v>
       </c>
       <c r="Y11" t="n">
-        <v>-6.325385275155652e-16</v>
+        <v>-3.05495934852082e-15</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.001439162794334948</v>
+        <v>-0.00143916279433412</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.0009979940318743741</v>
+        <v>-0.0009979940318735161</v>
       </c>
       <c r="AB11" t="n">
-        <v>-6.146923437965993e-06</v>
+        <v>-6.146923437967343e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.01736938160993809</v>
+        <v>-0.01736938160992134</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.01735361784201489</v>
+        <v>0.01735361784199784</v>
       </c>
       <c r="AE11" t="n">
-        <v>-1.012110102286476e-15</v>
+        <v>-4.803892303683812e-15</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.001230060733708419</v>
+        <v>-0.00123006073370777</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.001259379183022008</v>
+        <v>-0.00125937918302127</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.01771284180787014</v>
+        <v>0.01771284180795318</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0710998850555784</v>
+        <v>0.07109988505492337</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.07109988505622278</v>
+        <v>0.07109988505675269</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.080319097424901e-15</v>
+        <v>4.977732257002361e-15</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.368035180032301</v>
+        <v>-0.3680351800337569</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.4067246670159843</v>
+        <v>0.4067246670141085</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.01771284180787014</v>
+        <v>-0.01771284180795318</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0710998850555784</v>
+        <v>-0.07109988505492337</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.07109988505622278</v>
+        <v>-0.07109988505675269</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.080319097424901e-15</v>
+        <v>-4.977732257002361e-15</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.05856413030504015</v>
+        <v>-0.05856413030676011</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.01987464331748789</v>
+        <v>0.01987464331543176</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>5.08890510148019e-08</v>
+        <v>5.088905101306718e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>8.481508502466983e-09</v>
+        <v>8.481508502177862e-09</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0080404700603387</v>
+        <v>0.008040470060064614</v>
       </c>
       <c r="I12" t="n">
-        <v>1.696301700493397</v>
+        <v>1.696301700435572</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.009637448260284578</v>
+        <v>-0.009637448260274106</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.00963744826029103</v>
+        <v>-0.009637448260301185</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01000318118385151</v>
+        <v>0.0100031811838515</v>
       </c>
       <c r="M12" t="n">
-        <v>0.00119606478840903</v>
+        <v>0.001196064788409722</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.001196064788408546</v>
+        <v>-0.001196064788407717</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.310766232131836e-16</v>
+        <v>-3.054790642029308e-15</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.01735292577252209</v>
+        <v>-0.01735292577250504</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.01735292577253253</v>
+        <v>-0.01735292577254737</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001285089853989261</v>
+        <v>0.001285089853989626</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.001285089853988761</v>
+        <v>-0.001285089853988111</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.012571952175807e-15</v>
+        <v>-4.803309957801465e-15</v>
       </c>
       <c r="V12" t="n">
-        <v>0.01000318118385151</v>
+        <v>0.0100031811838515</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.00963744826029103</v>
+        <v>-0.009637448260301185</v>
       </c>
       <c r="X12" t="n">
-        <v>0.009637448260284578</v>
+        <v>0.009637448260274106</v>
       </c>
       <c r="Y12" t="n">
-        <v>-6.310766232131836e-16</v>
+        <v>-3.054790642029308e-15</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.001196064788408546</v>
+        <v>-0.001196064788407717</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.00119606478840903</v>
+        <v>-0.001196064788409722</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.01735292577253253</v>
+        <v>-0.01735292577254737</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.01735292577252209</v>
+        <v>0.01735292577250504</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.012571952175807e-15</v>
+        <v>-4.803309957801465e-15</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.001285089853988761</v>
+        <v>-0.001285089853988111</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.001285089853989261</v>
+        <v>-0.001285089853989626</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.008040470060223015</v>
+        <v>-0.008040470059995641</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.06709668431150018</v>
+        <v>0.06709668431187632</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.06709668431124749</v>
+        <v>-0.06709668431071891</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.085794397816698e-15</v>
+        <v>4.976554975659214e-15</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.2671686014630996</v>
+        <v>0.2671686014616472</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2671686014638706</v>
+        <v>0.267168601464757</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.008040470060223015</v>
+        <v>0.008040470059995641</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.06709668431150018</v>
+        <v>-0.06709668431187632</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.06709668431124749</v>
+        <v>0.06709668431071891</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.085794397816698e-15</v>
+        <v>-4.976554975659214e-15</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.1354115044043827</v>
+        <v>0.1354115044026627</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.1354115044051305</v>
+        <v>0.1354115044064992</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.121065937232203e-07</v>
+        <v>-1.121065937255742e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.868443228720338e-08</v>
+        <v>-1.86844322875957e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0177128418082688</v>
+        <v>-0.01771284180864072</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.736886457440675</v>
+        <v>-3.736886457519139</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.01030901918800026</v>
+        <v>-0.01030901918800909</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.009634190035146204</v>
+        <v>-0.00963419003515636</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.034816844253537e-06</v>
+        <v>-6.034816844260094e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001439162794335432</v>
+        <v>0.001439162794336123</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0009979940318746456</v>
+        <v>-0.0009979940318752018</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.323352839555595e-16</v>
+        <v>-3.054355086044638e-15</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.01736938160994386</v>
+        <v>-0.01736938160995587</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.01735361784202533</v>
+        <v>-0.01735361784204018</v>
       </c>
       <c r="R13" t="n">
-        <v>-6.146923437976757e-06</v>
+        <v>-6.146923437985668e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001230060733708922</v>
+        <v>0.001230060733709285</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.001259379183022239</v>
+        <v>-0.001259379183022356</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.013382782898572e-15</v>
+        <v>-4.804447417211208e-15</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.034816844253537e-06</v>
+        <v>-6.034816844260094e-06</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.009634190035146204</v>
+        <v>-0.00963419003515636</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01030901918800026</v>
+        <v>0.01030901918800909</v>
       </c>
       <c r="Y13" t="n">
-        <v>-6.323352839555595e-16</v>
+        <v>-3.054355086044638e-15</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.0009979940318746456</v>
+        <v>-0.0009979940318752018</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.001439162794335432</v>
+        <v>-0.001439162794336123</v>
       </c>
       <c r="AB13" t="n">
-        <v>-6.146923437976757e-06</v>
+        <v>-6.146923437985668e-06</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.01735361784202533</v>
+        <v>-0.01735361784204018</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01736938160994386</v>
+        <v>0.01736938160995587</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1.013382782898572e-15</v>
+        <v>-4.804447417211208e-15</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.001259379183022239</v>
+        <v>-0.001259379183022356</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.001230060733708922</v>
+        <v>-0.001230060733709285</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01771284180826882</v>
+        <v>0.01771284180864063</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.07109988505597098</v>
+        <v>-0.07109988505559262</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.07109988505572762</v>
+        <v>-0.07109988505601206</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.084519804683958e-15</v>
+        <v>4.981032019474084e-15</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.4067246670164</v>
+        <v>0.4067246670169316</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.36803518003153</v>
+        <v>-0.3680351800306383</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.01771284180826882</v>
+        <v>-0.01771284180864063</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.07109988505597098</v>
+        <v>0.07109988505559262</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.07109988505572762</v>
+        <v>0.07109988505601206</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-1.084519804683958e-15</v>
+        <v>-4.981032019474084e-15</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01987464331796218</v>
+        <v>0.01987464331914257</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.05856413030429408</v>
+        <v>-0.05856413030291918</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>2.247600015825579e-09</v>
+        <v>2.247600022764473e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>3.746000026375966e-10</v>
+        <v>3.746000037940789e-10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003551208025004415</v>
+        <v>0.0003551208035967868</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07492000052751931</v>
+        <v>0.07492000075881577</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.01737007367943667</v>
+        <v>-0.01737007367944867</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0173700736794309</v>
+        <v>-0.01737007367941414</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.009990938226026593</v>
+        <v>-0.009990938226026575</v>
       </c>
       <c r="M14" t="n">
-        <v>0.001204350062741668</v>
+        <v>0.001204350062740928</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.001204350062741899</v>
+        <v>-0.001204350062742015</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.012366336751686e-15</v>
+        <v>-4.803761237550783e-15</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.02482398266158013</v>
+        <v>-0.02482398266159128</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.02482398266157276</v>
+        <v>-0.0248239826615519</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.009990935978426577</v>
+        <v>-0.009990935978426553</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001257818715765601</v>
+        <v>0.001257818715765292</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.001257818715765732</v>
+        <v>-0.001257818715765604</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.358705779577601e-15</v>
+        <v>-5.674836422945595e-15</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.009990938226026593</v>
+        <v>-0.009990938226026575</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0173700736794309</v>
+        <v>-0.01737007367941414</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01737007367943667</v>
+        <v>0.01737007367944867</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1.012366336751686e-15</v>
+        <v>-4.803761237550783e-15</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.001204350062741899</v>
+        <v>-0.001204350062742015</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.001204350062741668</v>
+        <v>-0.001204350062740928</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.009990935978426577</v>
+        <v>-0.009990935978426553</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.02482398266157276</v>
+        <v>-0.0248239826615519</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.02482398266158013</v>
+        <v>0.02482398266159128</v>
       </c>
       <c r="AE14" t="n">
-        <v>-1.358705779577601e-15</v>
+        <v>-5.674836422945595e-15</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.001257818715765732</v>
+        <v>-0.001257818715765604</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.001257818715765601</v>
+        <v>-0.001257818715765292</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.0003551208026237873</v>
+        <v>-0.0003551208037606557</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.01662598616628053</v>
+        <v>0.01662598616604516</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.01662598616640665</v>
+        <v>-0.01662598616620636</v>
       </c>
       <c r="AK14" t="n">
-        <v>9.857353372737588e-16</v>
+        <v>2.479213989200619e-15</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.089444761736857</v>
+        <v>0.08944476173607985</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.08944476173654792</v>
+        <v>0.089444761736166</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0003551208026237873</v>
+        <v>0.0003551208037606557</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01662598616628053</v>
+        <v>-0.01662598616604516</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.01662598616640665</v>
+        <v>0.01662598616620636</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-9.857353372737588e-16</v>
+        <v>-2.479213989200619e-15</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.01031115526158288</v>
+        <v>0.01031115526116544</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.01031115526112991</v>
+        <v>0.01031115526010673</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>7.168575258849612e-09</v>
+        <v>7.168575258776767e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>1.194762543141602e-09</v>
+        <v>1.194762543129461e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001132634890898239</v>
+        <v>0.001132634890886729</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2389525086283204</v>
+        <v>0.2389525086258922</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.01735361784201489</v>
+        <v>-0.01735361784199784</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01736938160993809</v>
+        <v>-0.01736938160992134</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.146923437965993e-06</v>
+        <v>-6.146923437967343e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>0.001259379183022008</v>
+        <v>0.00125937918302127</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.001230060733708419</v>
+        <v>-0.00123006073370777</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.012110102286476e-15</v>
+        <v>-4.803892303683812e-15</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.02485967309715188</v>
+        <v>-0.02485967309713104</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.02482409162317794</v>
+        <v>-0.02482409162315708</v>
       </c>
       <c r="R15" t="n">
-        <v>-6.139754862707143e-06</v>
+        <v>-6.139754862708566e-06</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001237953768590565</v>
+        <v>0.001237953768590255</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.001259528070805485</v>
+        <v>-0.001259528070805193</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.357769995309901e-15</v>
+        <v>-5.67899907152334e-15</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.146923437965993e-06</v>
+        <v>-6.146923437967343e-06</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.01736938160993809</v>
+        <v>-0.01736938160992134</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01735361784201489</v>
+        <v>0.01735361784199784</v>
       </c>
       <c r="Y15" t="n">
-        <v>-1.012110102286476e-15</v>
+        <v>-4.803892303683812e-15</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.001230060733708419</v>
+        <v>-0.00123006073370777</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.001259379183022008</v>
+        <v>-0.00125937918302127</v>
       </c>
       <c r="AB15" t="n">
-        <v>-6.139754862707143e-06</v>
+        <v>-6.139754862708566e-06</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.02482409162317794</v>
+        <v>-0.02482409162315708</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.02485967309715188</v>
+        <v>0.02485967309713104</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.357769995309901e-15</v>
+        <v>-5.67899907152334e-15</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.001259528070805485</v>
+        <v>-0.001259528070805193</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.001237953768590565</v>
+        <v>-0.001237953768590255</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.00113263489089821</v>
+        <v>-0.001132634890886774</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.009197914260807849</v>
+        <v>-0.009197914261043216</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.009197914260166584</v>
+        <v>-0.00919791425992933</v>
       </c>
       <c r="AK15" t="n">
-        <v>9.838012339897462e-16</v>
+        <v>2.490688493081734e-15</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.04939957223232838</v>
+        <v>0.04939957223187874</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.04344854946169363</v>
+        <v>-0.04344854946208265</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.00113263489089821</v>
+        <v>0.001132634890886774</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.009197914260807849</v>
+        <v>0.009197914261043216</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.009197914260166584</v>
+        <v>0.00919791425992933</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-9.838012339897462e-16</v>
+        <v>-2.490688493081734e-15</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.005787913328671124</v>
+        <v>0.005787913327693683</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0.01173893610315879</v>
+        <v>-0.01173893610418197</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.658475053296915e-08</v>
+        <v>-1.658475053123443e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.764125088828192e-09</v>
+        <v>-2.764125088539071e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.002620390584209126</v>
+        <v>-0.002620390583935039</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5528250177656383</v>
+        <v>-0.5528250177078142</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.01735292577252209</v>
+        <v>-0.01735292577250504</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01735292577253253</v>
+        <v>-0.01735292577254737</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="M16" t="n">
-        <v>0.001285089853989261</v>
+        <v>0.001285089853989626</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.001285089853988761</v>
+        <v>-0.001285089853988111</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.012571952175807e-15</v>
+        <v>-4.803309957801465e-15</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001239663123630794</v>
+        <v>0.001239663123630873</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.001239663123630448</v>
+        <v>-0.001239663123630155</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.357742617260905e-15</v>
+        <v>-5.676397154560981e-15</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.01735292577253253</v>
+        <v>-0.01735292577254737</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01735292577252209</v>
+        <v>0.01735292577250504</v>
       </c>
       <c r="Y16" t="n">
-        <v>-1.012571952175807e-15</v>
+        <v>-4.803309957801465e-15</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.001285089853988761</v>
+        <v>-0.001285089853988111</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.001285089853989261</v>
+        <v>-0.001285089853989626</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.02485978205875706</v>
+        <v>0.02485978205873622</v>
       </c>
       <c r="AE16" t="n">
-        <v>-1.357742617260905e-15</v>
+        <v>-5.676397154560981e-15</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.001239663123630448</v>
+        <v>-0.001239663123630155</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.001239663123630794</v>
+        <v>-0.001239663123630873</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.002620390584070265</v>
+        <v>0.002620390583842891</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.01662598616658162</v>
+        <v>-0.01662598616656297</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01662598616692357</v>
+        <v>0.01662598616716049</v>
       </c>
       <c r="AK16" t="n">
-        <v>9.82408816011432e-16</v>
+        <v>2.484940483084779e-15</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.08349373896592382</v>
+        <v>-0.08349373896636569</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.08349373896501433</v>
+        <v>-0.08349373896516532</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.002620390584070265</v>
+        <v>-0.002620390583842891</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.01662598616658162</v>
+        <v>0.01662598616656297</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01662598616692357</v>
+        <v>-0.01662598616716049</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-9.82408816011432e-16</v>
+        <v>-2.484940483084779e-15</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.01626217803562113</v>
+        <v>-0.01626217803659191</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0.01626217803448071</v>
+        <v>-0.01626217803421071</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>7.168575257735764e-09</v>
+        <v>7.168575256660879e-09</v>
       </c>
       <c r="G17" t="n">
-        <v>1.194762542955961e-09</v>
+        <v>1.194762542776813e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001132634890722251</v>
+        <v>0.001132634890552419</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2389525085911921</v>
+        <v>0.2389525085553626</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.01736938160994386</v>
+        <v>-0.01736938160995587</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01735361784202533</v>
+        <v>-0.01735361784204018</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.146923437976757e-06</v>
+        <v>-6.146923437985668e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>0.001230060733708922</v>
+        <v>0.001230060733709285</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.001259379183022239</v>
+        <v>-0.001259379183022356</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.013382782898572e-15</v>
+        <v>-4.804447417211208e-15</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.0248240916231853</v>
+        <v>-0.02482409162319647</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.02485967309716625</v>
+        <v>-0.0248596730971825</v>
       </c>
       <c r="R17" t="n">
-        <v>-6.139754862719022e-06</v>
+        <v>-6.139754862729007e-06</v>
       </c>
       <c r="S17" t="n">
-        <v>0.00125952807080583</v>
+        <v>0.001259528070805909</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.001237953768590698</v>
+        <v>-0.001237953768590568</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.357962856859783e-15</v>
+        <v>-5.677821559011737e-15</v>
       </c>
       <c r="V17" t="n">
-        <v>-6.146923437976757e-06</v>
+        <v>-6.146923437985668e-06</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.01735361784202533</v>
+        <v>-0.01735361784204018</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01736938160994386</v>
+        <v>0.01736938160995587</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1.013382782898572e-15</v>
+        <v>-4.804447417211208e-15</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.001259379183022239</v>
+        <v>-0.001259379183022356</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.001230060733708922</v>
+        <v>-0.001230060733709285</v>
       </c>
       <c r="AB17" t="n">
-        <v>-6.139754862719022e-06</v>
+        <v>-6.139754862729007e-06</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.02485967309716625</v>
+        <v>-0.0248596730971825</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0248240916231853</v>
+        <v>0.02482409162319647</v>
       </c>
       <c r="AE17" t="n">
-        <v>-1.357962856859783e-15</v>
+        <v>-5.677821559011737e-15</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.001237953768590698</v>
+        <v>-0.001237953768590568</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.00125952807080583</v>
+        <v>-0.001259528070805909</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.001132634890722239</v>
+        <v>-0.001132634890552375</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.009197914260510309</v>
+        <v>0.009197914260527185</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.009197914260683504</v>
+        <v>0.009197914260882456</v>
       </c>
       <c r="AK17" t="n">
-        <v>9.807279028126785e-16</v>
+        <v>2.485757172816889e-15</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.04344854946139165</v>
+        <v>-0.04344854946217147</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.04939957223324143</v>
+        <v>0.04939957223308333</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.001132634890722239</v>
+        <v>0.001132634890552375</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.009197914260510309</v>
+        <v>-0.009197914260527185</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.009197914260683504</v>
+        <v>-0.009197914260882456</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-9.807279028126785e-16</v>
+        <v>-2.485757172816889e-15</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0.01173893610271293</v>
+        <v>-0.01173893610312504</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.005787913329816874</v>
+        <v>0.005787913330079775</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>9.625408910055207e-06</v>
+        <v>9.625408910056074e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>1.203176113756901e-06</v>
+        <v>1.203176113757009e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>1.140610955841542</v>
+        <v>1.140610955841645</v>
       </c>
       <c r="I18" t="n">
-        <v>240.6352227513802</v>
+        <v>240.6352227514018</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.005143544436265349</v>
+        <v>-0.005143544436268916</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.005143544436263927</v>
+        <v>-0.005143544436260579</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.009992639968869803</v>
+        <v>-0.009992639968869796</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0001430013372534397</v>
+        <v>0.0001430013372528314</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0001430013372536887</v>
+        <v>-0.0001430013372543053</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.459828480256998e-16</v>
+        <v>-1.1816844298607e-15</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.001181950344900396</v>
+        <v>-0.001181950344896417</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.005133919027353872</v>
+        <v>-0.005133919027350523</v>
       </c>
       <c r="R18" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="S18" t="n">
-        <v>0.001247154414832138</v>
+        <v>0.00124715441483153</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0008581353759201137</v>
+        <v>-0.0008581353759194087</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.45867092239527e-16</v>
+        <v>-1.181563932377305e-15</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.005143544436263927</v>
+        <v>-0.005143544436260579</v>
       </c>
       <c r="W18" t="n">
-        <v>0.005143544436265349</v>
+        <v>0.005143544436268916</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.009992639968869803</v>
+        <v>-0.009992639968869796</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.0001430013372536887</v>
+        <v>-0.0001430013372543053</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.0001430013372534397</v>
+        <v>-0.0001430013372528314</v>
       </c>
       <c r="AA18" t="n">
-        <v>-2.459828480256998e-16</v>
+        <v>-1.1816844298607e-15</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.005133919027353872</v>
+        <v>-0.005133919027350523</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.001181950344900396</v>
+        <v>0.001181950344896417</v>
       </c>
       <c r="AD18" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0008581353759201137</v>
+        <v>-0.0008581353759194087</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.001247154414832138</v>
+        <v>-0.00124715441483153</v>
       </c>
       <c r="AG18" t="n">
-        <v>-2.45867092239527e-16</v>
+        <v>-1.181563932377305e-15</v>
       </c>
       <c r="AH18" t="n">
         <v>-1.140610955841566</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.4122533851324607</v>
+        <v>0.412253385132467</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0.4606973814495045</v>
+        <v>-0.4606973814500098</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.001526536120999484</v>
+        <v>0.001526536120996663</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.455594483854196</v>
+        <v>2.455594483856218</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529868</v>
       </c>
       <c r="AN18" t="n">
         <v>1.140610955841566</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.4122533851324607</v>
+        <v>-0.412253385132467</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.4606973814495045</v>
+        <v>0.4606973814500098</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0.001526536120999484</v>
+        <v>-0.001526536120996663</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.229984567741841</v>
+        <v>1.229984567743863</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529868</v>
       </c>
     </row>
     <row r="19">
@@ -6354,124 +6354,124 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>9.625408910055207e-06</v>
+        <v>9.62540891005564e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>1.203176113756901e-06</v>
+        <v>1.203176113756955e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.140610955841542</v>
+        <v>1.140610955841593</v>
       </c>
       <c r="I19" t="n">
-        <v>240.6352227513802</v>
+        <v>240.635222751391</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.001181950344900396</v>
+        <v>-0.001181950344896417</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.005133919027353872</v>
+        <v>-0.005133919027350523</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="M19" t="n">
-        <v>0.001247154414832138</v>
+        <v>0.00124715441483153</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0008581353759201137</v>
+        <v>-0.0008581353759194087</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.45867092239527e-16</v>
+        <v>-1.181563932377305e-15</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.001172324935990341</v>
+        <v>-0.001172324935986361</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.001172324935992853</v>
+        <v>-0.001172324935996923</v>
       </c>
       <c r="R19" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="S19" t="n">
-        <v>0.00196228845349925</v>
+        <v>0.001962288453499951</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.001962288453498811</v>
+        <v>-0.001962288453498106</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.459196944341733e-16</v>
+        <v>-1.18166403535008e-15</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.001181950344900396</v>
+        <v>-0.001181950344896417</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.005133919027353872</v>
+        <v>-0.005133919027350523</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.894976628351932e-06</v>
+        <v>-4.894976628352089e-06</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.001247154414832138</v>
+        <v>0.00124715441483153</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.0008581353759201137</v>
+        <v>-0.0008581353759194087</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.45867092239527e-16</v>
+        <v>-1.181563932377305e-15</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.001172324935990341</v>
+        <v>-0.001172324935986361</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.001172324935992853</v>
+        <v>-0.001172324935996923</v>
       </c>
       <c r="AD19" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.00196228845349925</v>
+        <v>0.001962288453499951</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.001962288453498811</v>
+        <v>-0.001962288453498106</v>
       </c>
       <c r="AG19" t="n">
-        <v>-2.459196944341733e-16</v>
+        <v>-1.18166403535008e-15</v>
       </c>
       <c r="AH19" t="n">
-        <v>-1.140610955841538</v>
+        <v>-1.140610955841595</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.4122533851324608</v>
+        <v>-0.4122533851324677</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1326141717189501</v>
+        <v>0.1326141717183632</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.00152653612100095</v>
+        <v>-0.001526536121003745</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.08234827118037735</v>
+        <v>0.08234827118272525</v>
       </c>
       <c r="AM19" t="n">
-        <v>-1.649013540529843</v>
+        <v>-1.649013540529871</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.140610955841538</v>
+        <v>1.140610955841595</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.4122533851324608</v>
+        <v>0.4122533851324677</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.1326141717189501</v>
+        <v>-0.1326141717183632</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.00152653612100095</v>
+        <v>0.001526536121003745</v>
       </c>
       <c r="AR19" t="n">
-        <v>-1.143261644931977</v>
+        <v>-1.143261644929629</v>
       </c>
       <c r="AS19" t="n">
-        <v>-1.649013540529843</v>
+        <v>-1.649013540529871</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>9.625408910055207e-06</v>
+        <v>9.625408910055424e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>1.203176113756901e-06</v>
+        <v>1.203176113756928e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>1.140610955841542</v>
+        <v>1.140610955841568</v>
       </c>
       <c r="I20" t="n">
-        <v>240.6352227513802</v>
+        <v>240.6352227513856</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.001172324935990341</v>
+        <v>-0.001172324935986361</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.001172324935992853</v>
+        <v>-0.001172324935996923</v>
       </c>
       <c r="L20" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="M20" t="n">
-        <v>0.00196228845349925</v>
+        <v>0.001962288453499951</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.001962288453498811</v>
+        <v>-0.001962288453498106</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.459196944341733e-16</v>
+        <v>-1.18166403535008e-15</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.005133919027355294</v>
+        <v>-0.005133919027358861</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.001181950344902908</v>
+        <v>-0.001181950344906979</v>
       </c>
       <c r="R20" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0008581353759205526</v>
+        <v>0.000858135375921254</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.001247154414832387</v>
+        <v>-0.001247154414833003</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.45883799833235e-16</v>
+        <v>-1.18139457602318e-15</v>
       </c>
       <c r="V20" t="n">
-        <v>0.001172324935992853</v>
+        <v>0.001172324935996923</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.001172324935990341</v>
+        <v>-0.001172324935986361</v>
       </c>
       <c r="X20" t="n">
         <v>0.01000242992212651</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.001962288453498811</v>
+        <v>0.001962288453498106</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.00196228845349925</v>
+        <v>0.001962288453499951</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.459196944341733e-16</v>
+        <v>-1.18166403535008e-15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.001181950344902908</v>
+        <v>0.001181950344906979</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.005133919027355294</v>
+        <v>-0.005133919027358861</v>
       </c>
       <c r="AD20" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.001247154414832387</v>
+        <v>0.001247154414833003</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0008581353759205526</v>
+        <v>0.000858135375921254</v>
       </c>
       <c r="AG20" t="n">
-        <v>-2.45883799833235e-16</v>
+        <v>-1.18139457602318e-15</v>
       </c>
       <c r="AH20" t="n">
-        <v>-1.140610955841538</v>
+        <v>-1.140610955841566</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.4122533851324607</v>
+        <v>0.4122533851324672</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.1326141717193148</v>
+        <v>-0.1326141717198984</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.001526536120999483</v>
+        <v>0.001526536120996663</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.143261644933435</v>
+        <v>1.14326164493577</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529868</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.140610955841538</v>
+        <v>1.140610955841566</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.4122533851324607</v>
+        <v>-0.4122533851324672</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.1326141717193148</v>
+        <v>0.1326141717198984</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.001526536120999483</v>
+        <v>-0.001526536120996663</v>
       </c>
       <c r="AR20" t="n">
-        <v>-0.08234827117891852</v>
+        <v>-0.08234827117658372</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529868</v>
       </c>
     </row>
     <row r="21">
@@ -6644,112 +6644,112 @@
         <v>240.6352227513802</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.005133919027355294</v>
+        <v>-0.005133919027358861</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001181950344902908</v>
+        <v>-0.001181950344906979</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.894976628356553e-06</v>
+        <v>-4.894976628360052e-06</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0008581353759205526</v>
+        <v>0.000858135375921254</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.001247154414832387</v>
+        <v>-0.001247154414833003</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.45883799833235e-16</v>
+        <v>-1.18139457602318e-15</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.005143544436265349</v>
+        <v>-0.005143544436268916</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.005143544436263927</v>
+        <v>-0.005143544436260579</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.009992639968869803</v>
+        <v>-0.009992639968869796</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0001430013372534397</v>
+        <v>0.0001430013372528314</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0001430013372536887</v>
+        <v>-0.0001430013372543053</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.459828480256998e-16</v>
+        <v>-1.1816844298607e-15</v>
       </c>
       <c r="V21" t="n">
-        <v>0.005133919027355294</v>
+        <v>0.005133919027358861</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.001181950344902908</v>
+        <v>-0.001181950344906979</v>
       </c>
       <c r="X21" t="n">
-        <v>4.894976628356553e-06</v>
+        <v>4.894976628360052e-06</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.0008581353759205526</v>
+        <v>-0.000858135375921254</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.001247154414832387</v>
+        <v>-0.001247154414833003</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.45883799833235e-16</v>
+        <v>1.18139457602318e-15</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.005143544436265349</v>
+        <v>0.005143544436268916</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.005143544436263927</v>
+        <v>-0.005143544436260579</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.009992639968869803</v>
+        <v>0.009992639968869796</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.0001430013372534397</v>
+        <v>-0.0001430013372528314</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.0001430013372536887</v>
+        <v>-0.0001430013372543053</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.459828480256998e-16</v>
+        <v>1.1816844298607e-15</v>
       </c>
       <c r="AH21" t="n">
-        <v>-1.140610955841566</v>
+        <v>-1.140610955841453</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.4122533851324608</v>
+        <v>0.4122533851324676</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0.4606973814492966</v>
+        <v>-0.4606973814487824</v>
       </c>
       <c r="AK21" t="n">
-        <v>-0.001526536121000953</v>
+        <v>-0.001526536121003748</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.22998456774101</v>
+        <v>1.229984567738952</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529871</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.140610955841566</v>
+        <v>1.140610955841453</v>
       </c>
       <c r="AO21" t="n">
-        <v>-0.4122533851324608</v>
+        <v>-0.4122533851324676</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.4606973814492966</v>
+        <v>0.4606973814487824</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.001526536121000953</v>
+        <v>0.001526536121003748</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.455594483853365</v>
+        <v>2.455594483851307</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.649013540529843</v>
+        <v>1.649013540529871</v>
       </c>
     </row>
     <row r="22">
@@ -6783,112 +6783,112 @@
         <v>-81.45562862063582</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.01030576096285544</v>
+        <v>-0.01030576096286427</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.01030576096285178</v>
+        <v>-0.01030576096284246</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.009991111550163018</v>
+        <v>-0.009991111550163006</v>
       </c>
       <c r="M22" t="n">
-        <v>0.001241092037800776</v>
+        <v>0.00124109203779992</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.001241092037801047</v>
+        <v>-0.001241092037801604</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.320011768432583e-16</v>
+        <v>-3.055103843794704e-15</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.009634190035139751</v>
+        <v>-0.009634190035129281</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.0103090191879966</v>
+        <v>-0.01030901918798729</v>
       </c>
       <c r="R22" t="n">
-        <v>-6.034816844245296e-06</v>
+        <v>-6.034816844246121e-06</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0009979940318743741</v>
+        <v>0.0009979940318735161</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.001439162794334948</v>
+        <v>-0.00143916279433412</v>
       </c>
       <c r="U22" t="n">
-        <v>-6.325385275155652e-16</v>
+        <v>-3.05495934852082e-15</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.01030576096285178</v>
+        <v>-0.01030576096284246</v>
       </c>
       <c r="W22" t="n">
-        <v>0.01030576096285544</v>
+        <v>0.01030576096286427</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.009991111550163018</v>
+        <v>-0.009991111550163006</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.001241092037801047</v>
+        <v>-0.001241092037801604</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.001241092037800776</v>
+        <v>-0.00124109203779992</v>
       </c>
       <c r="AA22" t="n">
-        <v>-6.320011768432583e-16</v>
+        <v>-3.055103843794704e-15</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.0103090191879966</v>
+        <v>-0.01030901918798729</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.009634190035139751</v>
+        <v>0.009634190035129281</v>
       </c>
       <c r="AD22" t="n">
-        <v>-6.034816844245296e-06</v>
+        <v>-6.034816844246121e-06</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.001439162794334948</v>
+        <v>-0.00143916279433412</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.0009979940318743741</v>
+        <v>-0.0009979940318735161</v>
       </c>
       <c r="AG22" t="n">
-        <v>-6.325385275155652e-16</v>
+        <v>-3.05495934852082e-15</v>
       </c>
       <c r="AH22" t="n">
         <v>0.386099679661811</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.06988534966488702</v>
+        <v>0.0698853496648788</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0.1070524710587034</v>
+        <v>-0.1070524710594157</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.0004228048841396726</v>
+        <v>0.0004228048841367167</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.2932904909456604</v>
+        <v>0.2932904909485095</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.2795413986595481</v>
+        <v>0.2795413986595152</v>
       </c>
       <c r="AN22" t="n">
         <v>-0.386099679661811</v>
       </c>
       <c r="AO22" t="n">
-        <v>-0.06988534966488702</v>
+        <v>-0.0698853496648788</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.1070524710587034</v>
+        <v>0.1070524710594157</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-0.0004228048841396726</v>
+        <v>-0.0004228048841367167</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.5631292775239671</v>
+        <v>0.5631292775268171</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.2795413986595481</v>
+        <v>0.2795413986595152</v>
       </c>
     </row>
     <row r="23">
@@ -6910,124 +6910,124 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.258225144827168e-06</v>
+        <v>-3.258225144825433e-06</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.07278143103396e-07</v>
+        <v>-4.072781431031791e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3860996796620194</v>
+        <v>-0.3860996796618138</v>
       </c>
       <c r="I23" t="n">
-        <v>-81.45562862067918</v>
+        <v>-81.45562862063582</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.009634190035139751</v>
+        <v>-0.009634190035129281</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0103090191879966</v>
+        <v>-0.01030901918798729</v>
       </c>
       <c r="L23" t="n">
-        <v>-6.034816844245296e-06</v>
+        <v>-6.034816844246121e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0009979940318743741</v>
+        <v>0.0009979940318735161</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.001439162794334948</v>
+        <v>-0.00143916279433412</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.325385275155652e-16</v>
+        <v>-3.05495934852082e-15</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.009637448260284578</v>
+        <v>-0.009637448260274106</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.00963744826029103</v>
+        <v>-0.009637448260301185</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01000318118385151</v>
+        <v>0.0100031811838515</v>
       </c>
       <c r="S23" t="n">
-        <v>0.00119606478840903</v>
+        <v>0.001196064788409722</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.001196064788408546</v>
+        <v>-0.001196064788407717</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.310766232131836e-16</v>
+        <v>-3.054790642029308e-15</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.009634190035139751</v>
+        <v>-0.009634190035129281</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0103090191879966</v>
+        <v>-0.01030901918798729</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.034816844245296e-06</v>
+        <v>-6.034816844246121e-06</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.0009979940318743741</v>
+        <v>0.0009979940318735161</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.001439162794334948</v>
+        <v>-0.00143916279433412</v>
       </c>
       <c r="AA23" t="n">
-        <v>-6.325385275155652e-16</v>
+        <v>-3.05495934852082e-15</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.009637448260284578</v>
+        <v>-0.009637448260274106</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.00963744826029103</v>
+        <v>-0.009637448260301185</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.01000318118385151</v>
+        <v>0.0100031811838515</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.00119606478840903</v>
+        <v>0.001196064788409722</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.001196064788408546</v>
+        <v>-0.001196064788407717</v>
       </c>
       <c r="AG23" t="n">
-        <v>-6.310766232131836e-16</v>
+        <v>-3.054790642029308e-15</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.3860996796620384</v>
+        <v>0.386099679661811</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.06988534966488746</v>
+        <v>-0.06988534966487836</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.05532944124457745</v>
+        <v>0.0553294412438885</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.0004228048841412851</v>
+        <v>-0.0004228048841445928</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.3562371582674621</v>
+        <v>-0.3562371582647073</v>
       </c>
       <c r="AM23" t="n">
-        <v>-0.2795413986595507</v>
+        <v>-0.2795413986595134</v>
       </c>
       <c r="AN23" t="n">
-        <v>-0.3860996796620384</v>
+        <v>-0.386099679661811</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.06988534966488746</v>
+        <v>0.06988534966487836</v>
       </c>
       <c r="AP23" t="n">
-        <v>-0.05532944124457745</v>
+        <v>-0.0553294412438885</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.0004228048841412851</v>
+        <v>0.0004228048841445928</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.08639837168915587</v>
+        <v>-0.08639837168639986</v>
       </c>
       <c r="AS23" t="n">
-        <v>-0.279541398659549</v>
+        <v>-0.2795413986595126</v>
       </c>
     </row>
     <row r="24">
@@ -7061,112 +7061,112 @@
         <v>-81.45562862063582</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.009637448260284578</v>
+        <v>-0.009637448260274106</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.00963744826029103</v>
+        <v>-0.009637448260301185</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01000318118385151</v>
+        <v>0.0100031811838515</v>
       </c>
       <c r="M24" t="n">
-        <v>0.00119606478840903</v>
+        <v>0.001196064788409722</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.001196064788408546</v>
+        <v>-0.001196064788407717</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.310766232131836e-16</v>
+        <v>-3.054790642029308e-15</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.01030901918800026</v>
+        <v>-0.01030901918800909</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.009634190035146204</v>
+        <v>-0.00963419003515636</v>
       </c>
       <c r="R24" t="n">
-        <v>-6.034816844253537e-06</v>
+        <v>-6.034816844260094e-06</v>
       </c>
       <c r="S24" t="n">
-        <v>0.001439162794335432</v>
+        <v>0.001439162794336123</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0009979940318746456</v>
+        <v>-0.0009979940318752018</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.323352839555595e-16</v>
+        <v>-3.054355086044638e-15</v>
       </c>
       <c r="V24" t="n">
-        <v>0.00963744826029103</v>
+        <v>0.009637448260301185</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.009637448260284578</v>
+        <v>-0.009637448260274106</v>
       </c>
       <c r="X24" t="n">
-        <v>0.01000318118385151</v>
+        <v>0.0100031811838515</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.001196064788408546</v>
+        <v>0.001196064788407717</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.00119606478840903</v>
+        <v>0.001196064788409722</v>
       </c>
       <c r="AA24" t="n">
-        <v>-6.310766232131836e-16</v>
+        <v>-3.054790642029308e-15</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.009634190035146204</v>
+        <v>0.00963419003515636</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.01030901918800026</v>
+        <v>-0.01030901918800909</v>
       </c>
       <c r="AD24" t="n">
-        <v>-6.034816844253537e-06</v>
+        <v>-6.034816844260094e-06</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.0009979940318746456</v>
+        <v>0.0009979940318752018</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.001439162794335432</v>
+        <v>0.001439162794336123</v>
       </c>
       <c r="AG24" t="n">
-        <v>-6.323352839555595e-16</v>
+        <v>-3.054355086044638e-15</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.386099679661811</v>
+        <v>0.3860996796620384</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.06988534966488746</v>
+        <v>0.06988534966487858</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-0.05532944124497974</v>
+        <v>-0.05532944124555528</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.0004228048841396713</v>
+        <v>0.0004228048841367154</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.0863983716907657</v>
+        <v>0.08639837169306763</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.2795413986595507</v>
+        <v>0.2795413986595152</v>
       </c>
       <c r="AN24" t="n">
-        <v>-0.386099679661811</v>
+        <v>-0.3860996796620384</v>
       </c>
       <c r="AO24" t="n">
-        <v>-0.06988534966488746</v>
+        <v>-0.06988534966487858</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.05532944124497974</v>
+        <v>0.05532944124555528</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-0.0004228048841396713</v>
+        <v>-0.0004228048841367154</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.3562371582690712</v>
+        <v>0.3562371582713735</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.2795413986595481</v>
+        <v>0.2795413986595152</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.258225144825433e-06</v>
+        <v>-3.258225144823698e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.072781431031791e-07</v>
+        <v>-4.072781431029623e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3860996796618138</v>
+        <v>-0.3860996796616082</v>
       </c>
       <c r="I25" t="n">
-        <v>-81.45562862063582</v>
+        <v>-81.45562862059245</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.01030901918800026</v>
+        <v>-0.01030901918800909</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.009634190035146204</v>
+        <v>-0.00963419003515636</v>
       </c>
       <c r="L25" t="n">
-        <v>-6.034816844253537e-06</v>
+        <v>-6.034816844260094e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>0.001439162794335432</v>
+        <v>0.001439162794336123</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0009979940318746456</v>
+        <v>-0.0009979940318752018</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.323352839555595e-16</v>
+        <v>-3.054355086044638e-15</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01030576096285544</v>
+        <v>-0.01030576096286427</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.01030576096285178</v>
+        <v>-0.01030576096284246</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.009991111550163018</v>
+        <v>-0.009991111550163006</v>
       </c>
       <c r="S25" t="n">
-        <v>0.001241092037800776</v>
+        <v>0.00124109203779992</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.001241092037801047</v>
+        <v>-0.001241092037801604</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.320011768432583e-16</v>
+        <v>-3.055103843794704e-15</v>
       </c>
       <c r="V25" t="n">
-        <v>0.01030901918800026</v>
+        <v>0.01030901918800909</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.009634190035146204</v>
+        <v>-0.00963419003515636</v>
       </c>
       <c r="X25" t="n">
-        <v>6.034816844253537e-06</v>
+        <v>6.034816844260094e-06</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.001439162794335432</v>
+        <v>-0.001439162794336123</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.0009979940318746456</v>
+        <v>-0.0009979940318752018</v>
       </c>
       <c r="AA25" t="n">
-        <v>6.323352839555595e-16</v>
+        <v>3.054355086044638e-15</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.01030576096285544</v>
+        <v>0.01030576096286427</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.01030576096285178</v>
+        <v>-0.01030576096284246</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.009991111550163018</v>
+        <v>0.009991111550163006</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.001241092037800776</v>
+        <v>-0.00124109203779992</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.001241092037801047</v>
+        <v>-0.001241092037801604</v>
       </c>
       <c r="AG25" t="n">
-        <v>6.320011768432583e-16</v>
+        <v>3.055103843794704e-15</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.386099679661811</v>
+        <v>0.3860996796615837</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.06988534966488746</v>
+        <v>0.06988534966487814</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-0.1070524710584768</v>
+        <v>-0.1070524710580115</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.0004228048841412838</v>
+        <v>-0.0004228048841445884</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.563129277523061</v>
+        <v>0.5631292775211996</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.2795413986595507</v>
+        <v>0.2795413986595117</v>
       </c>
       <c r="AN25" t="n">
-        <v>-0.386099679661811</v>
+        <v>-0.3860996796615837</v>
       </c>
       <c r="AO25" t="n">
-        <v>-0.06988534966488746</v>
+        <v>-0.06988534966487814</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.1070524710584768</v>
+        <v>0.1070524710580115</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.0004228048841412838</v>
+        <v>0.0004228048841445884</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.2932904909447553</v>
+        <v>0.2932904909428933</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.2795413986595499</v>
+        <v>0.2795413986595126</v>
       </c>
     </row>
     <row r="26">
@@ -7339,112 +7339,112 @@
         <v>17.30173732009815</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.01737007367943667</v>
+        <v>-0.01737007367944867</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0173700736794309</v>
+        <v>-0.01737007367941414</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.009990938226026593</v>
+        <v>-0.009990938226026575</v>
       </c>
       <c r="M26" t="n">
-        <v>0.001204350062741668</v>
+        <v>0.001204350062740928</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.001204350062741899</v>
+        <v>-0.001204350062742015</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.012366336751686e-15</v>
+        <v>-4.803761237550783e-15</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01735361784201489</v>
+        <v>-0.01735361784199784</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.01736938160993809</v>
+        <v>-0.01736938160992134</v>
       </c>
       <c r="R26" t="n">
-        <v>-6.146923437965993e-06</v>
+        <v>-6.146923437967343e-06</v>
       </c>
       <c r="S26" t="n">
-        <v>0.001259379183022008</v>
+        <v>0.00125937918302127</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.001230060733708419</v>
+        <v>-0.00123006073370777</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.012110102286476e-15</v>
+        <v>-4.803892303683812e-15</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.0173700736794309</v>
+        <v>-0.01737007367941414</v>
       </c>
       <c r="W26" t="n">
-        <v>0.01737007367943667</v>
+        <v>0.01737007367944867</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.009990938226026593</v>
+        <v>-0.009990938226026575</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.001204350062741899</v>
+        <v>-0.001204350062742015</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.001204350062741668</v>
+        <v>-0.001204350062740928</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.012366336751686e-15</v>
+        <v>-4.803761237550783e-15</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.01736938160993809</v>
+        <v>-0.01736938160992134</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.01735361784201489</v>
+        <v>0.01735361784199784</v>
       </c>
       <c r="AD26" t="n">
-        <v>-6.146923437965993e-06</v>
+        <v>-6.146923437967343e-06</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.001230060733708419</v>
+        <v>-0.00123006073370777</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.001259379183022008</v>
+        <v>-0.00125937918302127</v>
       </c>
       <c r="AG26" t="n">
-        <v>-1.012110102286476e-15</v>
+        <v>-4.803892303683812e-15</v>
       </c>
       <c r="AH26" t="n">
         <v>-0.08201023489709769</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.001712435580860427</v>
+        <v>0.001712435580727645</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-0.01351504637649903</v>
+        <v>-0.01351504637711198</v>
       </c>
       <c r="AK26" t="n">
-        <v>5.488239379391937e-05</v>
+        <v>5.488239379228569e-05</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.08460134726158497</v>
+        <v>0.08460134726403878</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.00684974232344171</v>
+        <v>0.006849742322909691</v>
       </c>
       <c r="AN26" t="n">
         <v>0.08201023489709769</v>
       </c>
       <c r="AO26" t="n">
-        <v>-0.001712435580860427</v>
+        <v>-0.001712435580727645</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.01351504637649903</v>
+        <v>0.01351504637711198</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-5.488239379391937e-05</v>
+        <v>-5.488239379228569e-05</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.02351902375040749</v>
+        <v>0.02351902375285864</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.00684974232344171</v>
+        <v>0.006849742322910579</v>
       </c>
     </row>
     <row r="27">
@@ -7478,112 +7478,112 @@
         <v>17.30173732001142</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.01735361784201489</v>
+        <v>-0.01735361784199784</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.01736938160993809</v>
+        <v>-0.01736938160992134</v>
       </c>
       <c r="L27" t="n">
-        <v>-6.146923437965993e-06</v>
+        <v>-6.146923437967343e-06</v>
       </c>
       <c r="M27" t="n">
-        <v>0.001259379183022008</v>
+        <v>0.00125937918302127</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.001230060733708419</v>
+        <v>-0.00123006073370777</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.012110102286476e-15</v>
+        <v>-4.803892303683812e-15</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.01735292577252209</v>
+        <v>-0.01735292577250504</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.01735292577253253</v>
+        <v>-0.01735292577254737</v>
       </c>
       <c r="R27" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="S27" t="n">
-        <v>0.001285089853989261</v>
+        <v>0.001285089853989626</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.001285089853988761</v>
+        <v>-0.001285089853988111</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.012571952175807e-15</v>
+        <v>-4.803309957801465e-15</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.01735361784201489</v>
+        <v>-0.01735361784199784</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.01736938160993809</v>
+        <v>-0.01736938160992134</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.146923437965993e-06</v>
+        <v>-6.146923437967343e-06</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.001259379183022008</v>
+        <v>0.00125937918302127</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.001230060733708419</v>
+        <v>-0.00123006073370777</v>
       </c>
       <c r="AA27" t="n">
-        <v>-1.012110102286476e-15</v>
+        <v>-4.803892303683812e-15</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.01735292577252209</v>
+        <v>-0.01735292577250504</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.01735292577253253</v>
+        <v>-0.01735292577254737</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.001285089853989261</v>
+        <v>0.001285089853989626</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001285089853988761</v>
+        <v>-0.001285089853988111</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1.012571952175807e-15</v>
+        <v>-4.803309957801465e-15</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.08201023489664294</v>
+        <v>-0.08201023489709769</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.001712435580859539</v>
+        <v>-0.001712435580726535</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.005330430322269208</v>
+        <v>0.005330430321729085</v>
       </c>
       <c r="AK27" t="n">
-        <v>-5.488239379548322e-05</v>
+        <v>-5.488239379783637e-05</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.009219440466513129</v>
+        <v>0.009219440468673401</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0.006849742323438157</v>
+        <v>-0.006849742322907026</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.08201023489664294</v>
+        <v>0.08201023489709769</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.001712435580859539</v>
+        <v>0.001712435580726535</v>
       </c>
       <c r="AP27" t="n">
-        <v>-0.005330430322269208</v>
+        <v>-0.005330430321729085</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.488239379548322e-05</v>
+        <v>5.488239379783637e-05</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.05186288304466569</v>
+        <v>-0.05186288304250564</v>
       </c>
       <c r="AS27" t="n">
-        <v>-0.006849742323439045</v>
+        <v>-0.006849742322907026</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>6.920694928039262e-07</v>
+        <v>6.920694928073956e-07</v>
       </c>
       <c r="G28" t="n">
-        <v>8.650868660049077e-08</v>
+        <v>8.650868660092445e-08</v>
       </c>
       <c r="H28" t="n">
-        <v>0.08201023489726525</v>
+        <v>0.08201023489767638</v>
       </c>
       <c r="I28" t="n">
-        <v>17.30173732009815</v>
+        <v>17.30173732018489</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.01735292577252209</v>
+        <v>-0.01735292577250504</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.01735292577253253</v>
+        <v>-0.01735292577254737</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="M28" t="n">
-        <v>0.001285089853989261</v>
+        <v>0.001285089853989626</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.001285089853988761</v>
+        <v>-0.001285089853988111</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.012571952175807e-15</v>
+        <v>-4.803309957801465e-15</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.01736938160994386</v>
+        <v>-0.01736938160995587</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.01735361784202533</v>
+        <v>-0.01735361784204018</v>
       </c>
       <c r="R28" t="n">
-        <v>-6.146923437976757e-06</v>
+        <v>-6.146923437985668e-06</v>
       </c>
       <c r="S28" t="n">
-        <v>0.001230060733708922</v>
+        <v>0.001230060733709285</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.001259379183022239</v>
+        <v>-0.001259379183022356</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.013382782898572e-15</v>
+        <v>-4.804447417211208e-15</v>
       </c>
       <c r="V28" t="n">
-        <v>0.01735292577253253</v>
+        <v>0.01735292577254737</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.01735292577252209</v>
+        <v>-0.01735292577250504</v>
       </c>
       <c r="X28" t="n">
-        <v>0.01000323207290252</v>
+        <v>0.01000323207290251</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.001285089853988761</v>
+        <v>0.001285089853988111</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.001285089853989261</v>
+        <v>0.001285089853989626</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.012571952175807e-15</v>
+        <v>-4.803309957801465e-15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.01735361784202533</v>
+        <v>0.01735361784204018</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.01736938160994386</v>
+        <v>-0.01736938160995587</v>
       </c>
       <c r="AD28" t="n">
-        <v>-6.146923437976757e-06</v>
+        <v>-6.146923437985668e-06</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.001259379183022239</v>
+        <v>0.001259379183022356</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.001230060733708922</v>
+        <v>0.001230060733709285</v>
       </c>
       <c r="AG28" t="n">
-        <v>-1.013382782898572e-15</v>
+        <v>-4.804447417211208e-15</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.08201023489709769</v>
+        <v>-0.08201023489755244</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.001712435580859539</v>
+        <v>0.001712435580726979</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0.005330430322685431</v>
+        <v>-0.005330430322988522</v>
       </c>
       <c r="AK28" t="n">
-        <v>5.488239379392197e-05</v>
+        <v>5.488239379228569e-05</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.05186288304632969</v>
+        <v>0.05186288304754272</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.006849742323439045</v>
+        <v>0.006849742322908803</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.08201023489709769</v>
+        <v>0.08201023489755244</v>
       </c>
       <c r="AO28" t="n">
-        <v>-0.001712435580859539</v>
+        <v>-0.001712435580726979</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.005330430322685431</v>
+        <v>0.005330430322988522</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-5.488239379392197e-05</v>
+        <v>-5.488239379228569e-05</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.009219440464847573</v>
+        <v>-0.009219440463635209</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.006849742323438157</v>
+        <v>0.006849742322907026</v>
       </c>
     </row>
     <row r="29">
@@ -7756,112 +7756,112 @@
         <v>17.30173732009815</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.01736938160994386</v>
+        <v>-0.01736938160995587</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.01735361784202533</v>
+        <v>-0.01735361784204018</v>
       </c>
       <c r="L29" t="n">
-        <v>-6.146923437976757e-06</v>
+        <v>-6.146923437985668e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>0.001230060733708922</v>
+        <v>0.001230060733709285</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.001259379183022239</v>
+        <v>-0.001259379183022356</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.013382782898572e-15</v>
+        <v>-4.804447417211208e-15</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.01737007367943667</v>
+        <v>-0.01737007367944867</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.0173700736794309</v>
+        <v>-0.01737007367941414</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.009990938226026593</v>
+        <v>-0.009990938226026575</v>
       </c>
       <c r="S29" t="n">
-        <v>0.001204350062741668</v>
+        <v>0.001204350062740928</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.001204350062741899</v>
+        <v>-0.001204350062742015</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.012366336751686e-15</v>
+        <v>-4.803761237550783e-15</v>
       </c>
       <c r="V29" t="n">
-        <v>0.01736938160994386</v>
+        <v>0.01736938160995587</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.01735361784202533</v>
+        <v>-0.01735361784204018</v>
       </c>
       <c r="X29" t="n">
-        <v>6.146923437976757e-06</v>
+        <v>6.146923437985668e-06</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.001230060733708922</v>
+        <v>-0.001230060733709285</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.001259379183022239</v>
+        <v>-0.001259379183022356</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.013382782898572e-15</v>
+        <v>4.804447417211208e-15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.01737007367943667</v>
+        <v>0.01737007367944867</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.0173700736794309</v>
+        <v>-0.01737007367941414</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009990938226026593</v>
+        <v>0.009990938226026575</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.001204350062741668</v>
+        <v>-0.001204350062740928</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001204350062741899</v>
+        <v>-0.001204350062742015</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.012366336751686e-15</v>
+        <v>4.803761237550783e-15</v>
       </c>
       <c r="AH29" t="n">
         <v>-0.08201023489755244</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.001712435580860205</v>
+        <v>0.001712435580726979</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-0.01351504637630585</v>
+        <v>-0.01351504637620604</v>
       </c>
       <c r="AK29" t="n">
-        <v>-5.488239379548366e-05</v>
+        <v>-5.488239379784028e-05</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.02351902374963499</v>
+        <v>0.02351902374923509</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.006849742323440822</v>
+        <v>0.006849742322907915</v>
       </c>
       <c r="AN29" t="n">
         <v>0.08201023489755244</v>
       </c>
       <c r="AO29" t="n">
-        <v>-0.001712435580860205</v>
+        <v>-0.001712435580726979</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.01351504637630585</v>
+        <v>0.01351504637620604</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.488239379548366e-05</v>
+        <v>5.488239379784028e-05</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.08460134726081225</v>
+        <v>0.08460134726041391</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.006849742323439045</v>
+        <v>0.006849742322907026</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.089616051795639e-07</v>
+        <v>-1.089616051830333e-07</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.362020064744549e-08</v>
+        <v>-1.362020064787917e-08</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.01291195021377832</v>
+        <v>-0.01291195021418945</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.724040129489097</v>
+        <v>-2.724040129575833</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.02482398266158013</v>
+        <v>-0.02482398266159128</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.02482398266157276</v>
+        <v>-0.0248239826615519</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.009990935978426577</v>
+        <v>-0.009990935978426553</v>
       </c>
       <c r="M30" t="n">
-        <v>0.001257818715765601</v>
+        <v>0.001257818715765292</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.001257818715765732</v>
+        <v>-0.001257818715765604</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.358705779577601e-15</v>
+        <v>-5.674836422945595e-15</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.02485967309715188</v>
+        <v>-0.02485967309713104</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.02482409162317794</v>
+        <v>-0.02482409162315708</v>
       </c>
       <c r="R30" t="n">
-        <v>-6.139754862707143e-06</v>
+        <v>-6.139754862708566e-06</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001237953768590565</v>
+        <v>0.001237953768590255</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.001259528070805485</v>
+        <v>-0.001259528070805193</v>
       </c>
       <c r="U30" t="n">
-        <v>-1.357769995309901e-15</v>
+        <v>-5.67899907152334e-15</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.02482398266157276</v>
+        <v>-0.0248239826615519</v>
       </c>
       <c r="W30" t="n">
-        <v>0.02482398266158013</v>
+        <v>0.02482398266159128</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.009990935978426577</v>
+        <v>-0.009990935978426553</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.001257818715765732</v>
+        <v>-0.001257818715765604</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.001257818715765601</v>
+        <v>-0.001257818715765292</v>
       </c>
       <c r="AA30" t="n">
-        <v>-1.358705779577601e-15</v>
+        <v>-5.674836422945595e-15</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.02482409162317794</v>
+        <v>-0.02482409162315708</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.02485967309715188</v>
+        <v>0.02485967309713104</v>
       </c>
       <c r="AD30" t="n">
-        <v>-6.139754862707143e-06</v>
+        <v>-6.139754862708566e-06</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.001259528070805485</v>
+        <v>-0.001259528070805193</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.001237953768590565</v>
+        <v>-0.001237953768590255</v>
       </c>
       <c r="AG30" t="n">
-        <v>-1.357769995309901e-15</v>
+        <v>-5.67899907152334e-15</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.01291195021349267</v>
+        <v>0.01291195021440217</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.003714035952816719</v>
+        <v>-0.003714035953082284</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0.0001775604013612986</v>
+        <v>-0.0001775604016159837</v>
       </c>
       <c r="AK30" t="n">
-        <v>3.648815565626944e-06</v>
+        <v>3.648815565276964e-06</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.01031480407669871</v>
+        <v>-0.01031480407568131</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.0148561438112651</v>
+        <v>-0.01485614381232736</v>
       </c>
       <c r="AN30" t="n">
-        <v>-0.01291195021349267</v>
+        <v>-0.01291195021440217</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.003714035952816719</v>
+        <v>0.003714035953082284</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.0001775604013612986</v>
+        <v>0.0001775604016159837</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-3.648815565626944e-06</v>
+        <v>-3.648815565276964e-06</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.01173528728759021</v>
+        <v>0.01173528728861006</v>
       </c>
       <c r="AS30" t="n">
-        <v>-0.0148561438112651</v>
+        <v>-0.01485614381233091</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.089616051760944e-07</v>
+        <v>-1.089616051795639e-07</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.36202006470118e-08</v>
+        <v>-1.362020064744549e-08</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.01291195021336719</v>
+        <v>-0.01291195021377832</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.724040129402361</v>
+        <v>-2.724040129489097</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.02485967309715188</v>
+        <v>-0.02485967309713104</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.02482409162317794</v>
+        <v>-0.02482409162315708</v>
       </c>
       <c r="L31" t="n">
-        <v>-6.139754862707143e-06</v>
+        <v>-6.139754862708566e-06</v>
       </c>
       <c r="M31" t="n">
-        <v>0.001237953768590565</v>
+        <v>0.001237953768590255</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.001259528070805485</v>
+        <v>-0.001259528070805193</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.357769995309901e-15</v>
+        <v>-5.67899907152334e-15</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="R31" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001239663123630794</v>
+        <v>0.001239663123630873</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.001239663123630448</v>
+        <v>-0.001239663123630155</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.357742617260905e-15</v>
+        <v>-5.676397154560981e-15</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.02485967309715188</v>
+        <v>-0.02485967309713104</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.02482409162317794</v>
+        <v>-0.02482409162315708</v>
       </c>
       <c r="X31" t="n">
-        <v>-6.139754862707143e-06</v>
+        <v>-6.139754862708566e-06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.001237953768590565</v>
+        <v>0.001237953768590255</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.001259528070805485</v>
+        <v>-0.001259528070805193</v>
       </c>
       <c r="AA31" t="n">
-        <v>-1.357769995309901e-15</v>
+        <v>-5.67899907152334e-15</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.001239663123630794</v>
+        <v>0.001239663123630873</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001239663123630448</v>
+        <v>-0.001239663123630155</v>
       </c>
       <c r="AG31" t="n">
-        <v>-1.357742617260905e-15</v>
+        <v>-5.676397154560981e-15</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.01291195021349267</v>
+        <v>0.01291195021394742</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.003714035952815387</v>
+        <v>0.003714035953081396</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-0.001310195292259397</v>
+        <v>-0.001310195292502869</v>
       </c>
       <c r="AK31" t="n">
-        <v>-3.648815566643059e-06</v>
+        <v>-3.648815567473124e-06</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.005784264513107429</v>
+        <v>-0.005784264512133763</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.01485614381126332</v>
+        <v>0.01485614381232558</v>
       </c>
       <c r="AN31" t="n">
-        <v>-0.01291195021349267</v>
+        <v>-0.01291195021394742</v>
       </c>
       <c r="AO31" t="n">
-        <v>-0.003714035952815387</v>
+        <v>-0.003714035953081396</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.001310195292259397</v>
+        <v>0.001310195292502869</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.648815566643059e-06</v>
+        <v>3.648815567473124e-06</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.01626582685118416</v>
+        <v>0.01626582685215805</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.01485614381126332</v>
+        <v>0.01485614381232736</v>
       </c>
     </row>
     <row r="32">
@@ -8161,124 +8161,124 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.089616051691555e-07</v>
+        <v>-1.089616051760944e-07</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.362020064614444e-08</v>
+        <v>-1.36202006470118e-08</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.01291195021254493</v>
+        <v>-0.01291195021336719</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.724040129228888</v>
+        <v>-2.724040129402361</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.02485978205877142</v>
+        <v>-0.02485978205878767</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
       <c r="M32" t="n">
-        <v>0.001239663123630794</v>
+        <v>0.001239663123630873</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.001239663123630448</v>
+        <v>-0.001239663123630155</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.357742617260905e-15</v>
+        <v>-5.676397154560981e-15</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.0248240916231853</v>
+        <v>-0.02482409162319647</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.02485967309716625</v>
+        <v>-0.0248596730971825</v>
       </c>
       <c r="R32" t="n">
-        <v>-6.139754862719022e-06</v>
+        <v>-6.139754862729007e-06</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00125952807080583</v>
+        <v>0.001259528070805909</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.001237953768590698</v>
+        <v>-0.001237953768590568</v>
       </c>
       <c r="U32" t="n">
-        <v>-1.357962856859783e-15</v>
+        <v>-5.677821559011737e-15</v>
       </c>
       <c r="V32" t="n">
-        <v>0.02485978205877142</v>
+        <v>0.02485978205878767</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.02485978205875706</v>
+        <v>-0.02485978205873622</v>
       </c>
       <c r="X32" t="n">
-        <v>0.01000321548815199</v>
+        <v>0.01000321548815198</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.001239663123630448</v>
+        <v>0.001239663123630155</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.001239663123630794</v>
+        <v>0.001239663123630873</v>
       </c>
       <c r="AA32" t="n">
-        <v>-1.357742617260905e-15</v>
+        <v>-5.676397154560981e-15</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.02485967309716625</v>
+        <v>0.0248596730971825</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.0248240916231853</v>
+        <v>-0.02482409162319647</v>
       </c>
       <c r="AD32" t="n">
-        <v>-6.139754862719022e-06</v>
+        <v>-6.139754862729007e-06</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.001237953768590698</v>
+        <v>0.001237953768590568</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.00125952807080583</v>
+        <v>0.001259528070805909</v>
       </c>
       <c r="AG32" t="n">
-        <v>-1.357962856859783e-15</v>
+        <v>-5.677821559011737e-15</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.01291195021258318</v>
+        <v>0.01291195021349267</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.003714035952815831</v>
+        <v>-0.003714035953082284</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.001310195291973071</v>
+        <v>0.00131019529190779</v>
       </c>
       <c r="AK32" t="n">
-        <v>3.648815565620439e-06</v>
+        <v>3.648815565272193e-06</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.01626582685003797</v>
+        <v>-0.01626582684977684</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.01485614381126332</v>
+        <v>-0.01485614381232736</v>
       </c>
       <c r="AN32" t="n">
-        <v>-0.01291195021258318</v>
+        <v>-0.01291195021349267</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.003714035952815831</v>
+        <v>0.003714035953082284</v>
       </c>
       <c r="AP32" t="n">
-        <v>-0.001310195291973071</v>
+        <v>-0.00131019529190779</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-3.648815565620439e-06</v>
+        <v>-3.648815565272193e-06</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.005784264514252069</v>
+        <v>0.005784264514513193</v>
       </c>
       <c r="AS32" t="n">
-        <v>-0.01485614381126155</v>
+        <v>-0.01485614381232914</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.089616051795639e-07</v>
+        <v>-1.089616051830333e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.362020064744549e-08</v>
+        <v>-1.362020064787917e-08</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.01291195021377832</v>
+        <v>-0.01291195021418945</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.724040129489097</v>
+        <v>-2.724040129575833</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.0248240916231853</v>
+        <v>-0.02482409162319647</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.02485967309716625</v>
+        <v>-0.0248596730971825</v>
       </c>
       <c r="L33" t="n">
-        <v>-6.139754862719022e-06</v>
+        <v>-6.139754862729007e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>0.00125952807080583</v>
+        <v>0.001259528070805909</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.001237953768590698</v>
+        <v>-0.001237953768590568</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.357962856859783e-15</v>
+        <v>-5.677821559011737e-15</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.02482398266158013</v>
+        <v>-0.02482398266159128</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.02482398266157276</v>
+        <v>-0.0248239826615519</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.009990935978426577</v>
+        <v>-0.009990935978426553</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001257818715765601</v>
+        <v>0.001257818715765292</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.001257818715765732</v>
+        <v>-0.001257818715765604</v>
       </c>
       <c r="U33" t="n">
-        <v>-1.358705779577601e-15</v>
+        <v>-5.674836422945595e-15</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0248240916231853</v>
+        <v>0.02482409162319647</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.02485967309716625</v>
+        <v>-0.0248596730971825</v>
       </c>
       <c r="X33" t="n">
-        <v>6.139754862719022e-06</v>
+        <v>6.139754862729007e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.00125952807080583</v>
+        <v>-0.001259528070805909</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.001237953768590698</v>
+        <v>-0.001237953768590568</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.357962856859783e-15</v>
+        <v>5.677821559011737e-15</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.02482398266158013</v>
+        <v>0.02482398266159128</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.02482398266157276</v>
+        <v>-0.0248239826615519</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.009990935978426577</v>
+        <v>0.009990935978426553</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.001257818715765601</v>
+        <v>-0.001257818715765292</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001257818715765732</v>
+        <v>-0.001257818715765604</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.358705779577601e-15</v>
+        <v>5.674836422945595e-15</v>
       </c>
       <c r="AH33" t="n">
         <v>0.01291195021394742</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.003714035952815831</v>
+        <v>-0.003714035953083616</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.0001775604012499432</v>
+        <v>-0.0001775604013539711</v>
       </c>
       <c r="AK33" t="n">
-        <v>-3.648815566643926e-06</v>
+        <v>-3.648815567470955e-06</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.01173528728714435</v>
+        <v>0.01173528728756135</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.0148561438112651</v>
+        <v>-0.01485614381233269</v>
       </c>
       <c r="AN33" t="n">
         <v>-0.01291195021394742</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.003714035952815831</v>
+        <v>0.003714035953083616</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.0001775604012499432</v>
+        <v>0.0001775604013539711</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.648815566643926e-06</v>
+        <v>3.648815567470955e-06</v>
       </c>
       <c r="AR33" t="n">
-        <v>-0.01031480407714414</v>
+        <v>-0.01031480407672802</v>
       </c>
       <c r="AS33" t="n">
-        <v>-0.01485614381126332</v>
+        <v>-0.01485614381233624</v>
       </c>
     </row>
   </sheetData>
